--- a/research/traditional_assets/database/data/israel/israel_entertainment.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_entertainment.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,127 +581,133 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
+      </c>
+      <c r="D2">
+        <v>-0.0265</v>
+      </c>
+      <c r="E2">
+        <v>0.7</v>
       </c>
       <c r="F2">
         <v>0.0594</v>
       </c>
       <c r="G2">
-        <v>0.4449525010840001</v>
+        <v>0.4409638318670576</v>
       </c>
       <c r="H2">
-        <v>0.2715518940439118</v>
+        <v>0.2684516129032258</v>
       </c>
       <c r="I2">
-        <v>0.1940948070480984</v>
+        <v>0.1912817657870267</v>
       </c>
       <c r="J2">
-        <v>0.1211761400051946</v>
+        <v>0.1660078606338456</v>
       </c>
       <c r="K2">
-        <v>216.2</v>
+        <v>240.87</v>
       </c>
       <c r="L2">
-        <v>0.08522212148685403</v>
+        <v>0.09418181818181817</v>
       </c>
       <c r="M2">
-        <v>77.7</v>
+        <v>78.742</v>
       </c>
       <c r="N2">
-        <v>0.03003943400603109</v>
+        <v>0.02977553582502685</v>
       </c>
       <c r="O2">
-        <v>0.3593894542090657</v>
+        <v>0.3269066301324366</v>
       </c>
       <c r="P2">
-        <v>74.3</v>
+        <v>74.92099999999999</v>
       </c>
       <c r="Q2">
-        <v>0.02872496713832831</v>
+        <v>0.02833066114077413</v>
       </c>
       <c r="R2">
-        <v>0.3436632747456059</v>
+        <v>0.311043301365882</v>
       </c>
       <c r="S2">
-        <v>3.400000000000006</v>
+        <v>3.821000000000006</v>
       </c>
       <c r="T2">
-        <v>0.04375804375804383</v>
+        <v>0.04852556450179073</v>
       </c>
       <c r="U2">
-        <v>1145.9</v>
+        <v>1149.44</v>
       </c>
       <c r="V2">
-        <v>0.4430139952060621</v>
+        <v>0.4346497663091979</v>
       </c>
       <c r="W2">
         <v>-0.7669386307201136</v>
       </c>
       <c r="X2">
-        <v>0.1605330298942484</v>
+        <v>0.1212641996107605</v>
       </c>
       <c r="Y2">
-        <v>-0.927471660614362</v>
+        <v>-0.8882028303308741</v>
       </c>
       <c r="Z2">
-        <v>7.353239126651773</v>
+        <v>6.714723520663775</v>
       </c>
       <c r="AA2">
-        <v>0.89103713390283</v>
+        <v>-0.02099601929093462</v>
       </c>
       <c r="AB2">
-        <v>0.1133699791003923</v>
+        <v>0.1115262919232666</v>
       </c>
       <c r="AC2">
-        <v>0.7776671548024376</v>
+        <v>-0.1325223112142012</v>
       </c>
       <c r="AD2">
-        <v>2407.8</v>
+        <v>2409.587</v>
       </c>
       <c r="AE2">
         <v>91.00441999839509</v>
       </c>
       <c r="AF2">
-        <v>2498.804419998395</v>
+        <v>2500.591419998395</v>
       </c>
       <c r="AG2">
-        <v>1352.904419998395</v>
+        <v>1351.151419998395</v>
       </c>
       <c r="AH2">
-        <v>0.4913678861354323</v>
+        <v>0.4860130745233064</v>
       </c>
       <c r="AI2">
-        <v>1.040819651606633</v>
+        <v>1.010808647995266</v>
       </c>
       <c r="AJ2">
-        <v>0.3434199522992149</v>
+        <v>0.3381537864289496</v>
       </c>
       <c r="AK2">
-        <v>1.078093596961054</v>
+        <v>1.020189330450429</v>
       </c>
       <c r="AL2">
-        <v>155.1</v>
+        <v>156.454</v>
       </c>
       <c r="AM2">
-        <v>98.59999999999999</v>
+        <v>99.91400000000002</v>
       </c>
       <c r="AN2">
-        <v>3.773981191222571</v>
+        <v>3.788998385075392</v>
       </c>
       <c r="AO2">
-        <v>3.136041263700838</v>
+        <v>3.088473289273524</v>
       </c>
       <c r="AP2">
-        <v>2.120539843257673</v>
+        <v>2.124642334294732</v>
       </c>
       <c r="AQ2">
-        <v>4.933062880324544</v>
+        <v>4.836199131252876</v>
       </c>
     </row>
     <row r="3">
@@ -775,10 +781,10 @@
         <v>-0.7669386307201136</v>
       </c>
       <c r="X3">
-        <v>0.1605330298942484</v>
+        <v>0.160501987568469</v>
       </c>
       <c r="Y3">
-        <v>-0.927471660614362</v>
+        <v>-0.9274406182885826</v>
       </c>
       <c r="Z3">
         <v>7.353239126651773</v>
@@ -787,10 +793,10 @@
         <v>0.89103713390283</v>
       </c>
       <c r="AB3">
-        <v>0.1133699791003923</v>
+        <v>0.1133541899766119</v>
       </c>
       <c r="AC3">
-        <v>0.7776671548024376</v>
+        <v>0.7776829439262181</v>
       </c>
       <c r="AD3">
         <v>2407.8</v>
@@ -833,6 +839,250 @@
       </c>
       <c r="AQ3">
         <v>4.933062880324544</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Taya Investment Co., Ltd. (TASE:TAYA)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0265</v>
+      </c>
+      <c r="E4">
+        <v>0.7</v>
+      </c>
+      <c r="G4">
+        <v>0.02451456310679612</v>
+      </c>
+      <c r="H4">
+        <v>0.02451456310679612</v>
+      </c>
+      <c r="I4">
+        <v>-0.0362135922330097</v>
+      </c>
+      <c r="J4">
+        <v>-0.03546390734116845</v>
+      </c>
+      <c r="K4">
+        <v>27.2</v>
+      </c>
+      <c r="L4">
+        <v>1.320388349514563</v>
+      </c>
+      <c r="M4">
+        <v>1.042</v>
+      </c>
+      <c r="N4">
+        <v>0.02015473887814313</v>
+      </c>
+      <c r="O4">
+        <v>0.03830882352941177</v>
+      </c>
+      <c r="P4">
+        <v>0.621</v>
+      </c>
+      <c r="Q4">
+        <v>0.01201160541586073</v>
+      </c>
+      <c r="R4">
+        <v>0.02283088235294118</v>
+      </c>
+      <c r="S4">
+        <v>0.421</v>
+      </c>
+      <c r="T4">
+        <v>0.4040307101727447</v>
+      </c>
+      <c r="U4">
+        <v>2.52</v>
+      </c>
+      <c r="V4">
+        <v>0.04874274661508704</v>
+      </c>
+      <c r="W4">
+        <v>0.7331536388140161</v>
+      </c>
+      <c r="X4">
+        <v>0.1121594403199511</v>
+      </c>
+      <c r="Y4">
+        <v>0.620994198494065</v>
+      </c>
+      <c r="Z4">
+        <v>0.5920390860755855</v>
+      </c>
+      <c r="AA4">
+        <v>-0.02099601929093462</v>
+      </c>
+      <c r="AB4">
+        <v>0.1115262919232666</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1325223112142012</v>
+      </c>
+      <c r="AD4">
+        <v>0.597</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.597</v>
+      </c>
+      <c r="AG4">
+        <v>-1.923</v>
+      </c>
+      <c r="AH4">
+        <v>0.01141556877067518</v>
+      </c>
+      <c r="AI4">
+        <v>0.008396978775475759</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.03863230005825984</v>
+      </c>
+      <c r="AK4">
+        <v>-0.02804147163043003</v>
+      </c>
+      <c r="AL4">
+        <v>1.23</v>
+      </c>
+      <c r="AM4">
+        <v>1.23</v>
+      </c>
+      <c r="AN4">
+        <v>2.186813186813187</v>
+      </c>
+      <c r="AO4">
+        <v>-0.6065040650406505</v>
+      </c>
+      <c r="AP4">
+        <v>-7.043956043956044</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.6065040650406505</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wilk Technologies Ltd (TASE:WILK)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>-2.53</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1.02</v>
+      </c>
+      <c r="V5">
+        <v>0.1639871382636656</v>
+      </c>
+      <c r="W5">
+        <v>-0.7857142857142856</v>
+      </c>
+      <c r="X5">
+        <v>0.1212641996107605</v>
+      </c>
+      <c r="Y5">
+        <v>-0.9069784853250461</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>-1</v>
+      </c>
+      <c r="AB5">
+        <v>0.1108949239550081</v>
+      </c>
+      <c r="AC5">
+        <v>-1.110894923955008</v>
+      </c>
+      <c r="AD5">
+        <v>1.19</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1.19</v>
+      </c>
+      <c r="AG5">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.1605937921727395</v>
+      </c>
+      <c r="AI5">
+        <v>0.6099436186570989</v>
+      </c>
+      <c r="AJ5">
+        <v>0.02660406885758998</v>
+      </c>
+      <c r="AK5">
+        <v>0.1825993555316863</v>
+      </c>
+      <c r="AL5">
+        <v>0.124</v>
+      </c>
+      <c r="AM5">
+        <v>0.08399999999999999</v>
+      </c>
+      <c r="AN5">
+        <v>-0.5107296137339056</v>
+      </c>
+      <c r="AO5">
+        <v>-19.75806451612904</v>
+      </c>
+      <c r="AP5">
+        <v>-0.0729613733905579</v>
+      </c>
+      <c r="AQ5">
+        <v>-29.16666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1127,49 +1377,49 @@
         <v>3.29206963249516</v>
       </c>
       <c r="F2">
-        <v>4.58246885031975</v>
+        <v>4.51826278842867</v>
       </c>
       <c r="G2">
         <v>3.91662134795987</v>
       </c>
       <c r="H2">
-        <v>3.10863279592378</v>
+        <v>3.26804986238141</v>
       </c>
       <c r="I2">
         <v>0.491367886135432</v>
       </c>
       <c r="J2">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="K2">
         <v>2586.6</v>
       </c>
       <c r="L2">
-        <v>3255.14953128675</v>
+        <v>3196.18026033015</v>
       </c>
       <c r="M2">
         <v>3939.50441999839</v>
       </c>
       <c r="N2">
-        <v>4092.55725508612</v>
+        <v>4135.29607252949</v>
       </c>
       <c r="O2">
         <v>2498.8044199984</v>
       </c>
       <c r="P2">
-        <v>1983.30772379937</v>
+        <v>2085.01581219934</v>
       </c>
       <c r="Q2">
-        <v>0.113369979100392</v>
+        <v>0.113354189976612</v>
       </c>
       <c r="R2">
-        <v>0.109970240709309</v>
+        <v>0.109050110434302</v>
       </c>
       <c r="S2">
         <v>0.0645498528804033</v>
       </c>
       <c r="T2">
-        <v>0.0567728528804033</v>
+        <v>0.0547708528804033</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1432,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.160533029894248</v>
+        <v>0.160501987568469</v>
       </c>
       <c r="X2">
-        <v>0.143981685386806</v>
+        <v>0.146769594497181</v>
       </c>
       <c r="Y2">
         <v>1.77440326808082</v>
       </c>
       <c r="Z2">
-        <v>1.51842850813413</v>
+        <v>1.56196751469234</v>
       </c>
       <c r="AA2">
         <v>2407.8</v>
@@ -1224,7 +1474,7 @@
         <v>2586.6</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823122</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1409,13 +1659,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1115924069932459</v>
+        <v>0.1115746061094587</v>
       </c>
       <c r="C2">
-        <v>5163.97249457393</v>
+        <v>5164.064326869958</v>
       </c>
       <c r="D2">
-        <v>4018.07249457393</v>
+        <v>4018.164326869958</v>
       </c>
       <c r="E2">
         <v>-2498.804419998395</v>
@@ -1460,19 +1710,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1115924069932459</v>
+        <v>0.1115746061094587</v>
       </c>
       <c r="T2">
         <v>1.017512237681883</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V2">
         <v>0.23</v>
       </c>
       <c r="W2">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1491,13 +1741,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1115030729859654</v>
+        <v>0.111474533044211</v>
       </c>
       <c r="C3">
-        <v>5117.149771394274</v>
+        <v>5117.727033998523</v>
       </c>
       <c r="D3">
-        <v>4022.103815594259</v>
+        <v>4022.681078198508</v>
       </c>
       <c r="E3">
         <v>-2447.950375798411</v>
@@ -1524,37 +1774,37 @@
         <v>670.1</v>
       </c>
       <c r="M3">
-        <v>3.434223328218823</v>
+        <v>3.363027666338846</v>
       </c>
       <c r="N3">
-        <v>666.6657766717811</v>
+        <v>666.7369723336611</v>
       </c>
       <c r="O3">
-        <v>153.3331286345097</v>
+        <v>153.3495036367421</v>
       </c>
       <c r="P3">
-        <v>513.3326480372715</v>
+        <v>513.3874686969191</v>
       </c>
       <c r="Q3">
-        <v>640.7326480372715</v>
+        <v>640.7874686969191</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1121041257143044</v>
+        <v>0.112086186379199</v>
       </c>
       <c r="T3">
         <v>1.025426221752742</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V3">
         <v>0.23</v>
       </c>
       <c r="W3">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1562,7 +1812,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>195.1241768390033</v>
+        <v>199.2549769087993</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,13 +1823,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.111413738978685</v>
+        <v>0.1113744599789633</v>
       </c>
       <c r="C4">
-        <v>5070.335145565127</v>
+        <v>5071.399906963617</v>
       </c>
       <c r="D4">
-        <v>4026.143233965095</v>
+        <v>4027.207995363585</v>
       </c>
       <c r="E4">
         <v>-2397.096331598427</v>
@@ -1606,37 +1856,37 @@
         <v>670.1</v>
       </c>
       <c r="M4">
-        <v>6.868446656437646</v>
+        <v>6.726055332677691</v>
       </c>
       <c r="N4">
-        <v>663.2315533435624</v>
+        <v>663.3739446673223</v>
       </c>
       <c r="O4">
-        <v>152.5432572690194</v>
+        <v>152.5760072734842</v>
       </c>
       <c r="P4">
-        <v>510.688296074543</v>
+        <v>510.7979373938382</v>
       </c>
       <c r="Q4">
-        <v>638.088296074543</v>
+        <v>638.1979373938382</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1126262876745683</v>
+        <v>0.1126082070626074</v>
       </c>
       <c r="T4">
         <v>1.033501715702598</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V4">
         <v>0.23</v>
       </c>
       <c r="W4">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1644,7 +1894,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>97.56208841950163</v>
+        <v>99.62748845439967</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,13 +1905,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1113244049714045</v>
+        <v>0.1112743869137155</v>
       </c>
       <c r="C5">
-        <v>5023.528641507643</v>
+        <v>5025.082980124222</v>
       </c>
       <c r="D5">
-        <v>4030.190774107594</v>
+        <v>4031.745112724173</v>
       </c>
       <c r="E5">
         <v>-2346.242287398443</v>
@@ -1688,37 +1938,37 @@
         <v>670.1</v>
       </c>
       <c r="M5">
-        <v>10.30266998465647</v>
+        <v>10.08908299901654</v>
       </c>
       <c r="N5">
-        <v>659.7973300153435</v>
+        <v>660.0109170009835</v>
       </c>
       <c r="O5">
-        <v>151.753385903529</v>
+        <v>151.8025109102262</v>
       </c>
       <c r="P5">
-        <v>508.0439441118145</v>
+        <v>508.2084060907573</v>
       </c>
       <c r="Q5">
-        <v>635.4439441118145</v>
+        <v>635.6084060907572</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.113159215860817</v>
+        <v>0.1131409910590757</v>
       </c>
       <c r="T5">
         <v>1.041743714682348</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V5">
         <v>0.23</v>
       </c>
       <c r="W5">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1726,7 +1976,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.04139227966775</v>
+        <v>66.41832563626645</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,13 +1987,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1112350709641241</v>
+        <v>0.1111743138484678</v>
       </c>
       <c r="C6">
-        <v>4976.73028374127</v>
+        <v>4978.776287994335</v>
       </c>
       <c r="D6">
-        <v>4034.246460541206</v>
+        <v>4036.292464794271</v>
       </c>
       <c r="E6">
         <v>-2295.388243198459</v>
@@ -1770,37 +2020,37 @@
         <v>670.1</v>
       </c>
       <c r="M6">
-        <v>13.73689331287529</v>
+        <v>13.45211066535538</v>
       </c>
       <c r="N6">
-        <v>656.3631066871247</v>
+        <v>656.6478893346447</v>
       </c>
       <c r="O6">
-        <v>150.9635145380387</v>
+        <v>151.0290145469683</v>
       </c>
       <c r="P6">
-        <v>505.3995921490861</v>
+        <v>505.6188747876764</v>
       </c>
       <c r="Q6">
-        <v>632.799592149086</v>
+        <v>633.0188747876764</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1137032467176125</v>
+        <v>0.1136848747221372</v>
       </c>
       <c r="T6">
         <v>1.050157421974176</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V6">
         <v>0.23</v>
       </c>
       <c r="W6">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1808,7 +2058,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.78104420975082</v>
+        <v>49.81374422719984</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,13 +2069,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1111457369568437</v>
+        <v>0.1110742407832201</v>
       </c>
       <c r="C7">
-        <v>4929.940096884264</v>
+        <v>4932.479865243842</v>
       </c>
       <c r="D7">
-        <v>4038.310317884183</v>
+        <v>4040.850086243762</v>
       </c>
       <c r="E7">
         <v>-2244.534198998475</v>
@@ -1852,37 +2102,37 @@
         <v>670.1</v>
       </c>
       <c r="M7">
-        <v>17.17111664109412</v>
+        <v>16.81513833169423</v>
       </c>
       <c r="N7">
-        <v>652.9288833589059</v>
+        <v>653.2848616683058</v>
       </c>
       <c r="O7">
-        <v>150.1736431725484</v>
+        <v>150.2555181837103</v>
       </c>
       <c r="P7">
-        <v>502.7552401863575</v>
+        <v>503.0293434845954</v>
       </c>
       <c r="Q7">
-        <v>630.1552401863574</v>
+        <v>630.4293434845954</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1142587308556037</v>
+        <v>0.1142402085675789</v>
       </c>
       <c r="T7">
         <v>1.058748259945833</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V7">
         <v>0.23</v>
       </c>
       <c r="W7">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1890,7 +2140,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.02483536780065</v>
+        <v>39.85099538175987</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,13 +2151,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1110564029495632</v>
+        <v>0.1109741677179724</v>
       </c>
       <c r="C8">
-        <v>4883.158105654171</v>
+        <v>4886.193746699398</v>
       </c>
       <c r="D8">
-        <v>4042.382370854075</v>
+        <v>4045.418011899301</v>
       </c>
       <c r="E8">
         <v>-2193.680154798491</v>
@@ -1934,37 +2184,37 @@
         <v>670.1</v>
       </c>
       <c r="M8">
-        <v>20.60533996931294</v>
+        <v>20.17816599803307</v>
       </c>
       <c r="N8">
-        <v>649.4946600306871</v>
+        <v>649.921834001967</v>
       </c>
       <c r="O8">
-        <v>149.3837718070581</v>
+        <v>149.4820218204524</v>
       </c>
       <c r="P8">
-        <v>500.110888223629</v>
+        <v>500.4398121815146</v>
       </c>
       <c r="Q8">
-        <v>627.5108882236291</v>
+        <v>627.8398121815146</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1148260338050415</v>
+        <v>0.1148073580267534</v>
       </c>
       <c r="T8">
         <v>1.06752188170412</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V8">
         <v>0.23</v>
       </c>
       <c r="W8">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1972,7 +2222,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.52069613983387</v>
+        <v>33.20916281813323</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,13 +2233,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1109670689422828</v>
+        <v>0.1108740946527246</v>
       </c>
       <c r="C9">
-        <v>4836.384334868335</v>
+        <v>4839.91796734531</v>
       </c>
       <c r="D9">
-        <v>4046.462644268222</v>
+        <v>4049.996276745197</v>
       </c>
       <c r="E9">
         <v>-2142.826110598508</v>
@@ -2016,37 +2266,37 @@
         <v>670.1</v>
       </c>
       <c r="M9">
-        <v>24.03956329753176</v>
+        <v>23.54119366437192</v>
       </c>
       <c r="N9">
-        <v>646.0604367024682</v>
+        <v>646.5588063356281</v>
       </c>
       <c r="O9">
-        <v>148.5939004415677</v>
+        <v>148.7085254571945</v>
       </c>
       <c r="P9">
-        <v>497.4665362609005</v>
+        <v>497.8502808784336</v>
       </c>
       <c r="Q9">
-        <v>624.8665362609005</v>
+        <v>625.2502808784336</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1154055368179082</v>
+        <v>0.1153867042484908</v>
       </c>
       <c r="T9">
         <v>1.076484183500219</v>
       </c>
       <c r="U9">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V9">
         <v>0.23</v>
       </c>
       <c r="W9">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2054,7 +2304,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.87488240557189</v>
+        <v>28.46499670125704</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,13 +2315,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1108777349350024</v>
+        <v>0.1107740215874769</v>
       </c>
       <c r="C10">
-        <v>4789.618809444402</v>
+        <v>4793.652562324432</v>
       </c>
       <c r="D10">
-        <v>4050.551163044274</v>
+        <v>4054.584915924303</v>
       </c>
       <c r="E10">
         <v>-2091.972066398524</v>
@@ -2098,37 +2348,37 @@
         <v>670.1</v>
       </c>
       <c r="M10">
-        <v>27.47378662575058</v>
+        <v>26.90422133071077</v>
       </c>
       <c r="N10">
-        <v>642.6262133742495</v>
+        <v>643.1957786692892</v>
       </c>
       <c r="O10">
-        <v>147.8040290760774</v>
+        <v>147.9350290939365</v>
       </c>
       <c r="P10">
-        <v>494.8221842981721</v>
+        <v>495.2607495753527</v>
       </c>
       <c r="Q10">
-        <v>622.2221842981721</v>
+        <v>622.6607495753526</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1159976377223588</v>
+        <v>0.1159786449533094</v>
       </c>
       <c r="T10">
         <v>1.085641317944061</v>
       </c>
       <c r="U10">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V10">
         <v>0.23</v>
       </c>
       <c r="W10">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2136,7 +2386,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.39052210487541</v>
+        <v>24.90687211359992</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,13 +2397,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.110788400927722</v>
+        <v>0.1106739485222292</v>
       </c>
       <c r="C11">
-        <v>4742.861554400827</v>
+        <v>4747.397566939076</v>
       </c>
       <c r="D11">
-        <v>4054.647952200682</v>
+        <v>4059.183964738931</v>
       </c>
       <c r="E11">
         <v>-2041.11802219854</v>
@@ -2180,37 +2430,37 @@
         <v>670.1</v>
       </c>
       <c r="M11">
-        <v>30.90800995396941</v>
+        <v>30.26724899704961</v>
       </c>
       <c r="N11">
-        <v>639.1919900460306</v>
+        <v>639.8327510029504</v>
       </c>
       <c r="O11">
-        <v>147.014157710587</v>
+        <v>147.1615327306786</v>
       </c>
       <c r="P11">
-        <v>492.1778323354436</v>
+        <v>492.6712182722719</v>
       </c>
       <c r="Q11">
-        <v>619.5778323354435</v>
+        <v>620.0712182722718</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1166027518335007</v>
+        <v>0.1165835953439483</v>
       </c>
       <c r="T11">
         <v>1.094999708089964</v>
       </c>
       <c r="U11">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V11">
         <v>0.23</v>
       </c>
       <c r="W11">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2218,7 +2468,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.68046409322259</v>
+        <v>22.13944187875548</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,13 +2479,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1106990669204415</v>
+        <v>0.1105738754569815</v>
       </c>
       <c r="C12">
-        <v>4696.112594857382</v>
+        <v>4701.153016651895</v>
       </c>
       <c r="D12">
-        <v>4058.753036857221</v>
+        <v>4063.793458651734</v>
       </c>
       <c r="E12">
         <v>-1990.263977998556</v>
@@ -2262,37 +2512,37 @@
         <v>670.1</v>
       </c>
       <c r="M12">
-        <v>34.34223328218823</v>
+        <v>33.63027666338846</v>
       </c>
       <c r="N12">
-        <v>635.7577667178118</v>
+        <v>636.4697233366115</v>
       </c>
       <c r="O12">
-        <v>146.2242863450967</v>
+        <v>146.3880363674207</v>
       </c>
       <c r="P12">
-        <v>489.5334803727151</v>
+        <v>490.0816869691909</v>
       </c>
       <c r="Q12">
-        <v>616.9334803727151</v>
+        <v>617.4816869691908</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1172213129248902</v>
+        <v>0.1172019890766013</v>
       </c>
       <c r="T12">
         <v>1.104566062461333</v>
       </c>
       <c r="U12">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V12">
         <v>0.23</v>
       </c>
       <c r="W12">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2300,7 +2550,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.51241768390033</v>
+        <v>19.92549769087993</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,13 +2561,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1106097329131611</v>
+        <v>0.1104738023917338</v>
       </c>
       <c r="C13">
-        <v>4649.37195603567</v>
+        <v>4654.918947086818</v>
       </c>
       <c r="D13">
-        <v>4062.866442235493</v>
+        <v>4068.413433286642</v>
       </c>
       <c r="E13">
         <v>-1939.409933798572</v>
@@ -2344,37 +2594,37 @@
         <v>670.1</v>
       </c>
       <c r="M13">
-        <v>37.77645661040705</v>
+        <v>36.9933043297273</v>
       </c>
       <c r="N13">
-        <v>632.3235433895929</v>
+        <v>633.1066956702728</v>
       </c>
       <c r="O13">
-        <v>145.4344149796064</v>
+        <v>145.6145400041627</v>
       </c>
       <c r="P13">
-        <v>486.8891284099866</v>
+        <v>487.49215566611</v>
       </c>
       <c r="Q13">
-        <v>614.2891284099866</v>
+        <v>614.8921556661101</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1178537742655244</v>
+        <v>0.1178342792976285</v>
       </c>
       <c r="T13">
         <v>1.114347391088237</v>
       </c>
       <c r="U13">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V13">
         <v>0.23</v>
       </c>
       <c r="W13">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2382,7 +2632,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.73856153081848</v>
+        <v>18.11408880989085</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,13 +2643,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1105203989058807</v>
+        <v>0.1103737293264861</v>
       </c>
       <c r="C14">
-        <v>4602.639663259648</v>
+        <v>4608.695394029944</v>
       </c>
       <c r="D14">
-        <v>4066.988193659455</v>
+        <v>4073.043924429751</v>
       </c>
       <c r="E14">
         <v>-1888.555889598588</v>
@@ -2426,37 +2676,37 @@
         <v>670.1</v>
       </c>
       <c r="M14">
-        <v>41.21067993862588</v>
+        <v>40.35633199606615</v>
       </c>
       <c r="N14">
-        <v>628.8893200613742</v>
+        <v>629.7436680039339</v>
       </c>
       <c r="O14">
-        <v>144.6445436141161</v>
+        <v>144.8410436409048</v>
       </c>
       <c r="P14">
-        <v>484.2447764472581</v>
+        <v>484.9026243630291</v>
       </c>
       <c r="Q14">
-        <v>611.6447764472581</v>
+        <v>612.3026243630291</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1185006097275367</v>
+        <v>0.1184809397509519</v>
       </c>
       <c r="T14">
         <v>1.12435102263848</v>
       </c>
       <c r="U14">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V14">
         <v>0.23</v>
       </c>
       <c r="W14">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2464,7 +2714,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.26034806991694</v>
+        <v>16.60458140906661</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,13 +2725,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1104310648986002</v>
+        <v>0.1102736562612383</v>
       </c>
       <c r="C15">
-        <v>4555.915741956135</v>
+        <v>4562.48239343049</v>
       </c>
       <c r="D15">
-        <v>4071.118316555926</v>
+        <v>4077.684968030282</v>
       </c>
       <c r="E15">
         <v>-1837.701845398604</v>
@@ -2508,37 +2758,37 @@
         <v>670.1</v>
       </c>
       <c r="M15">
-        <v>44.6449032668447</v>
+        <v>43.71935966240499</v>
       </c>
       <c r="N15">
-        <v>625.4550967331553</v>
+        <v>626.3806403375951</v>
       </c>
       <c r="O15">
-        <v>143.8546722486257</v>
+        <v>144.0675472776469</v>
       </c>
       <c r="P15">
-        <v>481.6004244845296</v>
+        <v>482.3130930599482</v>
       </c>
       <c r="Q15">
-        <v>609.0004244845295</v>
+        <v>609.7130930599482</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1191623149702848</v>
+        <v>0.1191424659618228</v>
       </c>
       <c r="T15">
         <v>1.134584622730108</v>
       </c>
       <c r="U15">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V15">
         <v>0.23</v>
       </c>
       <c r="W15">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2546,7 +2796,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.00955206453871</v>
+        <v>15.32730591606149</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,13 +2807,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1103417308913198</v>
+        <v>0.1101735831959906</v>
       </c>
       <c r="C16">
-        <v>4509.200217655343</v>
+        <v>4516.279981401702</v>
       </c>
       <c r="D16">
-        <v>4075.256836455119</v>
+        <v>4082.336600201476</v>
       </c>
       <c r="E16">
         <v>-1786.84780119862</v>
@@ -2590,37 +2840,37 @@
         <v>670.1</v>
       </c>
       <c r="M16">
-        <v>48.07912659506353</v>
+        <v>47.08238732874385</v>
       </c>
       <c r="N16">
-        <v>622.0208734049365</v>
+        <v>623.0176126712562</v>
       </c>
       <c r="O16">
-        <v>143.0648008831354</v>
+        <v>143.2940509143889</v>
       </c>
       <c r="P16">
-        <v>478.9560725218012</v>
+        <v>479.7235617568673</v>
       </c>
       <c r="Q16">
-        <v>606.3560725218011</v>
+        <v>607.1235617568673</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1198394087070504</v>
+        <v>0.1198193765031792</v>
       </c>
       <c r="T16">
         <v>1.145056213521542</v>
       </c>
       <c r="U16">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V16">
         <v>0.23</v>
       </c>
       <c r="W16">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2628,7 +2878,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.93744120278595</v>
+        <v>14.23249835062852</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,13 +2889,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1102523968840394</v>
+        <v>0.1100735101307429</v>
       </c>
       <c r="C17">
-        <v>4462.493115991404</v>
+        <v>4470.088194221801</v>
       </c>
       <c r="D17">
-        <v>4079.403778991163</v>
+        <v>4086.99885722156</v>
       </c>
       <c r="E17">
         <v>-1735.993756998636</v>
@@ -2672,37 +2922,37 @@
         <v>670.1</v>
       </c>
       <c r="M17">
-        <v>51.51334992328235</v>
+        <v>50.44541499508269</v>
       </c>
       <c r="N17">
-        <v>618.5866500767177</v>
+        <v>619.6545850049173</v>
       </c>
       <c r="O17">
-        <v>142.2749295176451</v>
+        <v>142.520554551131</v>
       </c>
       <c r="P17">
-        <v>476.3117205590726</v>
+        <v>477.1340304537863</v>
       </c>
       <c r="Q17">
-        <v>603.7117205590725</v>
+        <v>604.5340304537863</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1205324340611516</v>
+        <v>0.1205122143513911</v>
       </c>
       <c r="T17">
         <v>1.155774194684539</v>
       </c>
       <c r="U17">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V17">
         <v>0.23</v>
       </c>
       <c r="W17">
-        <v>0.05199885288040334</v>
+        <v>0.05092085288040334</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2710,7 +2960,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.00827845593355</v>
+        <v>13.28366512725329</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,13 +2971,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1102985828767589</v>
+        <v>0.1101582370654952</v>
       </c>
       <c r="C18">
-        <v>4409.494034867354</v>
+        <v>4415.286156028369</v>
       </c>
       <c r="D18">
-        <v>4077.258742067097</v>
+        <v>4083.050863228112</v>
       </c>
       <c r="E18">
         <v>-1685.139712798652</v>
@@ -2754,37 +3004,37 @@
         <v>670.1</v>
       </c>
       <c r="M18">
-        <v>55.84260442942089</v>
+        <v>55.02893972222115</v>
       </c>
       <c r="N18">
-        <v>614.2573955705791</v>
+        <v>615.0710602777789</v>
       </c>
       <c r="O18">
-        <v>141.2792009812332</v>
+        <v>141.4663438638891</v>
       </c>
       <c r="P18">
-        <v>472.9781945893459</v>
+        <v>473.6047164138897</v>
       </c>
       <c r="Q18">
-        <v>600.3781945893459</v>
+        <v>601.0047164138897</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1212419600189219</v>
+        <v>0.121221548338846</v>
       </c>
       <c r="T18">
         <v>1.166747365875225</v>
       </c>
       <c r="U18">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V18">
         <v>0.23</v>
       </c>
       <c r="W18">
-        <v>0.05284585288040334</v>
+        <v>0.05207585288040334</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2792,7 +3042,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.99979848445169</v>
+        <v>12.1772289886481</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,13 +3053,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1102177188694785</v>
+        <v>0.1100697140002474</v>
       </c>
       <c r="C19">
-        <v>4362.397078382487</v>
+        <v>4368.557171612482</v>
       </c>
       <c r="D19">
-        <v>4081.015829782214</v>
+        <v>4087.175923012209</v>
       </c>
       <c r="E19">
         <v>-1634.285668598668</v>
@@ -2836,37 +3086,37 @@
         <v>670.1</v>
       </c>
       <c r="M19">
-        <v>59.3327672062597</v>
+        <v>58.46824845485997</v>
       </c>
       <c r="N19">
-        <v>610.7672327937403</v>
+        <v>611.6317515451401</v>
       </c>
       <c r="O19">
-        <v>140.4764635425603</v>
+        <v>140.6753028553822</v>
       </c>
       <c r="P19">
-        <v>470.29076925118</v>
+        <v>470.9564486897578</v>
       </c>
       <c r="Q19">
-        <v>597.69076925118</v>
+        <v>598.3564486897578</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1219685829877228</v>
+        <v>0.1219479747115408</v>
       </c>
       <c r="T19">
         <v>1.177984950829543</v>
       </c>
       <c r="U19">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V19">
         <v>0.23</v>
       </c>
       <c r="W19">
-        <v>0.05284585288040334</v>
+        <v>0.05207585288040334</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2874,7 +3124,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.29392798536629</v>
+        <v>11.46092140108056</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,13 +3135,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1101368548621981</v>
+        <v>0.1099811909349997</v>
       </c>
       <c r="C20">
-        <v>4315.307052400805</v>
+        <v>4321.836530627706</v>
       </c>
       <c r="D20">
-        <v>4084.779848000517</v>
+        <v>4091.309326227418</v>
       </c>
       <c r="E20">
         <v>-1583.431624398684</v>
@@ -2918,37 +3168,37 @@
         <v>670.1</v>
       </c>
       <c r="M20">
-        <v>62.8229299830985</v>
+        <v>61.90755718749879</v>
       </c>
       <c r="N20">
-        <v>607.2770700169015</v>
+        <v>608.1924428125012</v>
       </c>
       <c r="O20">
-        <v>139.6737261038873</v>
+        <v>139.8842618468753</v>
       </c>
       <c r="P20">
-        <v>467.6033439130141</v>
+        <v>468.3081809656259</v>
       </c>
       <c r="Q20">
-        <v>595.0033439130141</v>
+        <v>595.7081809656258</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1227129284679579</v>
+        <v>0.1226921188006428</v>
       </c>
       <c r="T20">
         <v>1.189496623221771</v>
       </c>
       <c r="U20">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V20">
         <v>0.23</v>
       </c>
       <c r="W20">
-        <v>0.05284585288040334</v>
+        <v>0.05207585288040334</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2956,7 +3206,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.66648754173483</v>
+        <v>10.82420354546497</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,13 +3217,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1100559908549176</v>
+        <v>0.109892667869752</v>
       </c>
       <c r="C21">
-        <v>4268.223976116523</v>
+        <v>4275.124258413062</v>
       </c>
       <c r="D21">
-        <v>4088.550815916218</v>
+        <v>4095.451098212757</v>
       </c>
       <c r="E21">
         <v>-1532.5775801987</v>
@@ -3000,37 +3250,37 @@
         <v>670.1</v>
       </c>
       <c r="M21">
-        <v>66.31309275993731</v>
+        <v>65.34686592013762</v>
       </c>
       <c r="N21">
-        <v>603.7869072400628</v>
+        <v>604.7531340798624</v>
       </c>
       <c r="O21">
-        <v>138.8709886652144</v>
+        <v>139.0932208383684</v>
       </c>
       <c r="P21">
-        <v>464.9159185748483</v>
+        <v>465.6599132414941</v>
       </c>
       <c r="Q21">
-        <v>592.3159185748483</v>
+        <v>593.0599132414941</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1234756528489395</v>
+        <v>0.1234546368178708</v>
       </c>
       <c r="T21">
         <v>1.201292534438499</v>
       </c>
       <c r="U21">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V21">
         <v>0.23</v>
       </c>
       <c r="W21">
-        <v>0.05284585288040334</v>
+        <v>0.05207585288040334</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3038,7 +3288,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.1050934605909</v>
+        <v>10.25450862201945</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,13 +3299,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1103139268476372</v>
+        <v>0.1098041448045043</v>
       </c>
       <c r="C22">
-        <v>4205.36573021165</v>
+        <v>4228.420380410274</v>
       </c>
       <c r="D22">
-        <v>4076.546614211329</v>
+        <v>4099.601264409954</v>
       </c>
       <c r="E22">
         <v>-1481.723535998716</v>
@@ -3082,45 +3332,45 @@
         <v>670.1</v>
       </c>
       <c r="M22">
-        <v>72.0408334815754</v>
+        <v>68.78617465277644</v>
       </c>
       <c r="N22">
-        <v>598.0591665184246</v>
+        <v>601.3138253472235</v>
       </c>
       <c r="O22">
-        <v>137.5536082992377</v>
+        <v>138.3021798298614</v>
       </c>
       <c r="P22">
-        <v>460.5055582191869</v>
+        <v>463.0116455173621</v>
       </c>
       <c r="Q22">
-        <v>587.9055582191869</v>
+        <v>590.4116455173621</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1242574453394457</v>
+        <v>0.1242362177855295</v>
       </c>
       <c r="T22">
         <v>1.213383343435645</v>
       </c>
       <c r="U22">
-        <v>0.07083097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V22">
         <v>0.23</v>
       </c>
       <c r="W22">
-        <v>0.05453985288040333</v>
+        <v>0.05207585288040334</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.301669173099997</v>
+        <v>9.741783190918476</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,13 +3381,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1102500028403568</v>
+        <v>0.1099905117392566</v>
       </c>
       <c r="C23">
-        <v>4157.480099973111</v>
+        <v>4168.838788411072</v>
       </c>
       <c r="D23">
-        <v>4079.515028172774</v>
+        <v>4090.873716610734</v>
       </c>
       <c r="E23">
         <v>-1430.869491798732</v>
@@ -3164,37 +3414,37 @@
         <v>670.1</v>
       </c>
       <c r="M23">
-        <v>75.64287515565417</v>
+        <v>74.04097276335467</v>
       </c>
       <c r="N23">
-        <v>594.4571248443458</v>
+        <v>596.0590272366453</v>
       </c>
       <c r="O23">
-        <v>136.7251387141995</v>
+        <v>137.0935762644284</v>
       </c>
       <c r="P23">
-        <v>457.7319861301463</v>
+        <v>458.9654509722169</v>
       </c>
       <c r="Q23">
-        <v>585.1319861301463</v>
+        <v>586.3654509722169</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1250590300449014</v>
+        <v>0.1250375856131289</v>
       </c>
       <c r="T23">
         <v>1.225780248863098</v>
       </c>
       <c r="U23">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V23">
         <v>0.23</v>
       </c>
       <c r="W23">
-        <v>0.05453985288040333</v>
+        <v>0.05338485288040334</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3202,7 +3452,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.85873254580952</v>
+        <v>9.050394328849967</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,13 +3463,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1101860788330764</v>
+        <v>0.1099150786740088</v>
       </c>
       <c r="C24">
-        <v>4109.598795897477</v>
+        <v>4121.512787996811</v>
       </c>
       <c r="D24">
-        <v>4082.487768297124</v>
+        <v>4094.401760396458</v>
       </c>
       <c r="E24">
         <v>-1380.015447598748</v>
@@ -3246,37 +3496,37 @@
         <v>670.1</v>
       </c>
       <c r="M24">
-        <v>79.24491682973294</v>
+        <v>77.56673337113347</v>
       </c>
       <c r="N24">
-        <v>590.8550831702671</v>
+        <v>592.5332666288666</v>
       </c>
       <c r="O24">
-        <v>135.8966691291614</v>
+        <v>136.2826513246393</v>
       </c>
       <c r="P24">
-        <v>454.9584140411057</v>
+        <v>456.2506153042273</v>
       </c>
       <c r="Q24">
-        <v>582.3584140411057</v>
+        <v>583.6506153042272</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1258811682043431</v>
+        <v>0.1258595013337437</v>
       </c>
       <c r="T24">
         <v>1.238495023660486</v>
       </c>
       <c r="U24">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V24">
         <v>0.23</v>
       </c>
       <c r="W24">
-        <v>0.05453985288040333</v>
+        <v>0.05338485288040334</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3284,7 +3534,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.45606288463636</v>
+        <v>8.639012768447696</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,13 +3545,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1101221548257959</v>
+        <v>0.1098396456087611</v>
       </c>
       <c r="C25">
-        <v>4061.72182744906</v>
+        <v>4074.192878133216</v>
       </c>
       <c r="D25">
-        <v>4085.464844048691</v>
+        <v>4097.935894732846</v>
       </c>
       <c r="E25">
         <v>-1329.161403398764</v>
@@ -3328,37 +3578,37 @@
         <v>670.1</v>
       </c>
       <c r="M25">
-        <v>82.84695850381171</v>
+        <v>81.09249397891226</v>
       </c>
       <c r="N25">
-        <v>587.2530414961883</v>
+        <v>589.0075060210878</v>
       </c>
       <c r="O25">
-        <v>135.0681995441233</v>
+        <v>135.4717263848502</v>
       </c>
       <c r="P25">
-        <v>452.184841952065</v>
+        <v>453.5357796362376</v>
       </c>
       <c r="Q25">
-        <v>579.5848419520649</v>
+        <v>580.9357796362376</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1267246606016924</v>
+        <v>0.1267027655146342</v>
       </c>
       <c r="T25">
         <v>1.251540052348715</v>
       </c>
       <c r="U25">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V25">
         <v>0.23</v>
       </c>
       <c r="W25">
-        <v>0.05453985288040333</v>
+        <v>0.05338485288040334</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3366,7 +3616,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.088407976608693</v>
+        <v>8.263403517645623</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,13 +3627,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1100582308185155</v>
+        <v>0.1097642125435134</v>
       </c>
       <c r="C26">
-        <v>4013.849204119801</v>
+        <v>4026.879074605316</v>
       </c>
       <c r="D26">
-        <v>4088.446264919415</v>
+        <v>4101.476135404931</v>
       </c>
       <c r="E26">
         <v>-1278.30735919878</v>
@@ -3410,37 +3660,37 @@
         <v>670.1</v>
       </c>
       <c r="M26">
-        <v>86.44900017789048</v>
+        <v>84.61825458669105</v>
       </c>
       <c r="N26">
-        <v>583.6509998221095</v>
+        <v>585.481745413309</v>
       </c>
       <c r="O26">
-        <v>134.2397299590852</v>
+        <v>134.6608014450611</v>
       </c>
       <c r="P26">
-        <v>449.4112698630243</v>
+        <v>450.8209439682479</v>
       </c>
       <c r="Q26">
-        <v>576.8112698630243</v>
+        <v>578.2209439682479</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.127590350167393</v>
+        <v>0.1275682208581797</v>
       </c>
       <c r="T26">
         <v>1.264928371265582</v>
       </c>
       <c r="U26">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V26">
         <v>0.23</v>
       </c>
       <c r="W26">
-        <v>0.05453985288040333</v>
+        <v>0.05338485288040334</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3448,7 +3698,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.75139097758333</v>
+        <v>7.919095037743722</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,13 +3709,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.110283056811235</v>
+        <v>0.1096887794782657</v>
       </c>
       <c r="C27">
-        <v>3952.528469396985</v>
+        <v>3979.571393252742</v>
       </c>
       <c r="D27">
-        <v>4077.979574396583</v>
+        <v>4105.02249825234</v>
       </c>
       <c r="E27">
         <v>-1227.453314998796</v>
@@ -3492,45 +3742,45 @@
         <v>670.1</v>
       </c>
       <c r="M27">
-        <v>91.95806850946865</v>
+        <v>88.14401519446984</v>
       </c>
       <c r="N27">
-        <v>578.1419314905314</v>
+        <v>581.9559848055302</v>
       </c>
       <c r="O27">
-        <v>132.9726442428222</v>
+        <v>133.8498765052719</v>
       </c>
       <c r="P27">
-        <v>445.1692872477092</v>
+        <v>448.1061083002583</v>
       </c>
       <c r="Q27">
-        <v>572.5692872477091</v>
+        <v>575.5061083002582</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1284791247881789</v>
+        <v>0.1284567550108864</v>
       </c>
       <c r="T27">
         <v>1.278673712020232</v>
       </c>
       <c r="U27">
-        <v>0.07233097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V27">
         <v>0.23</v>
       </c>
       <c r="W27">
-        <v>0.05569485288040334</v>
+        <v>0.05338485288040334</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.287016907396243</v>
+        <v>7.602331236233973</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,13 +3791,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1102306828039546</v>
+        <v>0.1097735064130179</v>
       </c>
       <c r="C28">
-        <v>3904.107886811124</v>
+        <v>3924.734473984801</v>
       </c>
       <c r="D28">
-        <v>4080.413036010706</v>
+        <v>4101.039623184384</v>
       </c>
       <c r="E28">
         <v>-1176.599270798813</v>
@@ -3574,37 +3824,37 @@
         <v>670.1</v>
       </c>
       <c r="M28">
-        <v>95.63639124984739</v>
+        <v>92.72753992160833</v>
       </c>
       <c r="N28">
-        <v>574.4636087501526</v>
+        <v>577.3724600783917</v>
       </c>
       <c r="O28">
-        <v>132.1266300125351</v>
+        <v>132.7956658180301</v>
       </c>
       <c r="P28">
-        <v>442.3369787376175</v>
+        <v>444.5767942603616</v>
       </c>
       <c r="Q28">
-        <v>569.7369787376175</v>
+        <v>571.9767942603615</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1293919203446618</v>
+        <v>0.1293693036001528</v>
       </c>
       <c r="T28">
         <v>1.292790548470954</v>
       </c>
       <c r="U28">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V28">
         <v>0.23</v>
       </c>
       <c r="W28">
-        <v>0.05569485288040334</v>
+        <v>0.05400085288040334</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3612,7 +3862,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.00674702634254</v>
+        <v>7.226547804098989</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,13 +3873,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1101783087966742</v>
+        <v>0.1097042333477702</v>
       </c>
       <c r="C29">
-        <v>3855.690210209031</v>
+        <v>3877.136266901206</v>
       </c>
       <c r="D29">
-        <v>4082.849403608597</v>
+        <v>4104.295460300772</v>
       </c>
       <c r="E29">
         <v>-1125.745226598829</v>
@@ -3656,37 +3906,37 @@
         <v>670.1</v>
       </c>
       <c r="M29">
-        <v>99.31471399022614</v>
+        <v>96.29398376474711</v>
       </c>
       <c r="N29">
-        <v>570.7852860097739</v>
+        <v>573.8060162352529</v>
       </c>
       <c r="O29">
-        <v>131.280615782248</v>
+        <v>131.9753837341082</v>
       </c>
       <c r="P29">
-        <v>439.5046702275259</v>
+        <v>441.8306325011447</v>
       </c>
       <c r="Q29">
-        <v>566.9046702275259</v>
+        <v>569.2306325011447</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1303297239985826</v>
+        <v>0.130306853520632</v>
       </c>
       <c r="T29">
         <v>1.307294147564161</v>
       </c>
       <c r="U29">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V29">
         <v>0.23</v>
       </c>
       <c r="W29">
-        <v>0.05569485288040334</v>
+        <v>0.05400085288040334</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3694,7 +3944,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.747237877218743</v>
+        <v>6.958897885428656</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,13 +3955,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1101259347893938</v>
+        <v>0.1096349602825225</v>
       </c>
       <c r="C30">
-        <v>3807.275444799207</v>
+        <v>3829.54323357781</v>
       </c>
       <c r="D30">
-        <v>4085.288682398756</v>
+        <v>4107.55647117736</v>
       </c>
       <c r="E30">
         <v>-1074.891182398844</v>
@@ -3738,37 +3988,37 @@
         <v>670.1</v>
       </c>
       <c r="M30">
-        <v>102.9930367306049</v>
+        <v>99.8604276078859</v>
       </c>
       <c r="N30">
-        <v>567.1069632693951</v>
+        <v>570.2395723921142</v>
       </c>
       <c r="O30">
-        <v>130.4346015519609</v>
+        <v>131.1551016501863</v>
       </c>
       <c r="P30">
-        <v>436.6723617174342</v>
+        <v>439.0844707419279</v>
       </c>
       <c r="Q30">
-        <v>564.0723617174342</v>
+        <v>566.4844707419279</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1312935777540011</v>
+        <v>0.1312704464944577</v>
       </c>
       <c r="T30">
         <v>1.322200624409958</v>
       </c>
       <c r="U30">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V30">
         <v>0.23</v>
       </c>
       <c r="W30">
-        <v>0.05569485288040334</v>
+        <v>0.05400085288040334</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3776,7 +4026,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.506265095889502</v>
+        <v>6.710365818091919</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,13 +4037,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1100735607821133</v>
+        <v>0.1095656872172748</v>
       </c>
       <c r="C31">
-        <v>3758.863595802603</v>
+        <v>3781.955386356635</v>
       </c>
       <c r="D31">
-        <v>4087.730877602137</v>
+        <v>4110.822668156169</v>
       </c>
       <c r="E31">
         <v>-1024.037138198861</v>
@@ -3820,37 +4070,37 @@
         <v>670.1</v>
       </c>
       <c r="M31">
-        <v>106.6713594709836</v>
+        <v>103.4268714510247</v>
       </c>
       <c r="N31">
-        <v>563.4286405290164</v>
+        <v>566.6731285489753</v>
       </c>
       <c r="O31">
-        <v>129.5885873216738</v>
+        <v>130.3348195662643</v>
       </c>
       <c r="P31">
-        <v>433.8400532073426</v>
+        <v>436.338308982711</v>
       </c>
       <c r="Q31">
-        <v>561.2400532073426</v>
+        <v>563.738308982711</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1322845823194315</v>
+        <v>0.132261182932335</v>
       </c>
       <c r="T31">
         <v>1.337527002011973</v>
       </c>
       <c r="U31">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V31">
         <v>0.23</v>
       </c>
       <c r="W31">
-        <v>0.05569485288040334</v>
+        <v>0.05400085288040334</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3858,7 +4108,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.281911127065727</v>
+        <v>6.478973893330129</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,13 +4119,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1103445867748329</v>
+        <v>0.1094964141520271</v>
       </c>
       <c r="C32">
-        <v>3695.403077561981</v>
+        <v>3734.372737618995</v>
       </c>
       <c r="D32">
-        <v>4075.124403561499</v>
+        <v>4114.094063618512</v>
       </c>
       <c r="E32">
         <v>-973.1830939988768</v>
@@ -3902,45 +4152,45 @@
         <v>670.1</v>
       </c>
       <c r="M32">
-        <v>112.4855520677617</v>
+        <v>106.9933152941635</v>
       </c>
       <c r="N32">
-        <v>557.6144479322384</v>
+        <v>563.1066847058365</v>
       </c>
       <c r="O32">
-        <v>128.2513230244148</v>
+        <v>129.5145374823424</v>
       </c>
       <c r="P32">
-        <v>429.3631249078235</v>
+        <v>433.5921472234941</v>
       </c>
       <c r="Q32">
-        <v>556.7631249078236</v>
+        <v>560.9921472234942</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.133303901301017</v>
+        <v>0.1332802261255801</v>
       </c>
       <c r="T32">
         <v>1.353291276116904</v>
       </c>
       <c r="U32">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V32">
         <v>0.23</v>
       </c>
       <c r="W32">
-        <v>0.05677285288040334</v>
+        <v>0.05400085288040334</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>5.957209505415677</v>
+        <v>6.26300809688579</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,13 +4201,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1103029927675525</v>
+        <v>0.1096658410867793</v>
       </c>
       <c r="C33">
-        <v>3646.478679287856</v>
+        <v>3675.526755535137</v>
       </c>
       <c r="D33">
-        <v>4077.054049487358</v>
+        <v>4106.10212573464</v>
       </c>
       <c r="E33">
         <v>-922.3290497988928</v>
@@ -3984,37 +4234,37 @@
         <v>670.1</v>
       </c>
       <c r="M33">
-        <v>116.2350704700204</v>
+        <v>112.1362345075017</v>
       </c>
       <c r="N33">
-        <v>553.8649295299796</v>
+        <v>557.9637654924983</v>
       </c>
       <c r="O33">
-        <v>127.3889337918953</v>
+        <v>128.3316660632746</v>
       </c>
       <c r="P33">
-        <v>426.4759957380843</v>
+        <v>429.6320994292237</v>
       </c>
       <c r="Q33">
-        <v>553.8759957380843</v>
+        <v>557.0320994292236</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1343527657603296</v>
+        <v>0.1343288068026874</v>
       </c>
       <c r="T33">
         <v>1.369512485703137</v>
       </c>
       <c r="U33">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V33">
         <v>0.23</v>
       </c>
       <c r="W33">
-        <v>0.05677285288040334</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4022,7 +4272,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.76504145685388</v>
+        <v>5.975766913728242</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,13 +4283,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.110261398760272</v>
+        <v>0.1096042680215316</v>
       </c>
       <c r="C34">
-        <v>3597.556109324735</v>
+        <v>3627.5735438666</v>
       </c>
       <c r="D34">
-        <v>4078.985523724221</v>
+        <v>4109.002958266085</v>
       </c>
       <c r="E34">
         <v>-871.4750055989089</v>
@@ -4066,37 +4316,37 @@
         <v>670.1</v>
       </c>
       <c r="M34">
-        <v>119.9845888722791</v>
+        <v>115.7535323948405</v>
       </c>
       <c r="N34">
-        <v>550.1154111277209</v>
+        <v>554.3464676051595</v>
       </c>
       <c r="O34">
-        <v>126.5265445593758</v>
+        <v>127.4996875491867</v>
       </c>
       <c r="P34">
-        <v>423.5888665683451</v>
+        <v>426.8467800559728</v>
       </c>
       <c r="Q34">
-        <v>550.9888665683451</v>
+        <v>554.2467800559727</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1354324791743279</v>
+        <v>0.1354082280879449</v>
       </c>
       <c r="T34">
         <v>1.386210789688965</v>
       </c>
       <c r="U34">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V34">
         <v>0.23</v>
       </c>
       <c r="W34">
-        <v>0.05677285288040334</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4104,7 +4354,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.584883911327197</v>
+        <v>5.789024197674235</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,13 +4365,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1102198047529916</v>
+        <v>0.1095426949562839</v>
       </c>
       <c r="C35">
-        <v>3548.635370272296</v>
+        <v>3579.624433790342</v>
       </c>
       <c r="D35">
-        <v>4080.918828871766</v>
+        <v>4111.907892389812</v>
       </c>
       <c r="E35">
         <v>-820.6209613989249</v>
@@ -4148,37 +4398,37 @@
         <v>670.1</v>
       </c>
       <c r="M35">
-        <v>123.7341072745379</v>
+        <v>119.3708302821793</v>
       </c>
       <c r="N35">
-        <v>546.3658927254621</v>
+        <v>550.7291697178207</v>
       </c>
       <c r="O35">
-        <v>125.6641553268563</v>
+        <v>126.6677090350988</v>
       </c>
       <c r="P35">
-        <v>420.7017373986058</v>
+        <v>424.0614606827219</v>
       </c>
       <c r="Q35">
-        <v>548.1017373986058</v>
+        <v>551.461460682722</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1365444228394903</v>
+        <v>0.1365198709041057</v>
       </c>
       <c r="T35">
         <v>1.403407550510191</v>
       </c>
       <c r="U35">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V35">
         <v>0.23</v>
       </c>
       <c r="W35">
-        <v>0.05677285288040334</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4186,7 +4436,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.415645004923342</v>
+        <v>5.613599221987136</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,13 +4447,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1101782107457112</v>
+        <v>0.1094811218910362</v>
       </c>
       <c r="C36">
-        <v>3499.716464735149</v>
+        <v>3531.679434011605</v>
       </c>
       <c r="D36">
-        <v>4082.853967534603</v>
+        <v>4114.816936811059</v>
       </c>
       <c r="E36">
         <v>-769.7669171989407</v>
@@ -4230,37 +4480,37 @@
         <v>670.1</v>
       </c>
       <c r="M36">
-        <v>127.4836256767966</v>
+        <v>122.988128169518</v>
       </c>
       <c r="N36">
-        <v>542.6163743232034</v>
+        <v>547.111871830482</v>
       </c>
       <c r="O36">
-        <v>124.8017660943368</v>
+        <v>125.8357305210109</v>
       </c>
       <c r="P36">
-        <v>417.8146082288666</v>
+        <v>421.2761413094711</v>
       </c>
       <c r="Q36">
-        <v>545.2146082288666</v>
+        <v>548.6761413094711</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1376900617672334</v>
+        <v>0.1376651998662107</v>
       </c>
       <c r="T36">
         <v>1.421125425295696</v>
       </c>
       <c r="U36">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V36">
         <v>0.23</v>
       </c>
       <c r="W36">
-        <v>0.05677285288040334</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4268,7 +4518,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.256361328307949</v>
+        <v>5.448493362516926</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,13 +4529,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1101366167384307</v>
+        <v>0.1094195488257884</v>
       </c>
       <c r="C37">
-        <v>3450.799395322844</v>
+        <v>3483.738553260279</v>
       </c>
       <c r="D37">
-        <v>4084.790942322283</v>
+        <v>4117.730100259717</v>
       </c>
       <c r="E37">
         <v>-718.9128729989568</v>
@@ -4312,37 +4562,37 @@
         <v>670.1</v>
       </c>
       <c r="M37">
-        <v>131.2331440790553</v>
+        <v>126.6054260568568</v>
       </c>
       <c r="N37">
-        <v>538.8668559209447</v>
+        <v>543.4945739431432</v>
       </c>
       <c r="O37">
-        <v>123.9393768618173</v>
+        <v>125.003752006923</v>
       </c>
       <c r="P37">
-        <v>414.9274790591274</v>
+        <v>418.4908219362203</v>
       </c>
       <c r="Q37">
-        <v>542.3274790591274</v>
+        <v>545.8908219362203</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1388709511235224</v>
+        <v>0.1388457697194574</v>
       </c>
       <c r="T37">
         <v>1.439388465459217</v>
       </c>
       <c r="U37">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V37">
         <v>0.23</v>
       </c>
       <c r="W37">
-        <v>0.05677285288040334</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4350,7 +4600,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.106179576070579</v>
+        <v>5.292822123587871</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,13 +4611,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1100950227311503</v>
+        <v>0.1093579757605407</v>
       </c>
       <c r="C38">
-        <v>3401.88416464989</v>
+        <v>3435.801800290994</v>
       </c>
       <c r="D38">
-        <v>4086.729755849312</v>
+        <v>4120.647391490416</v>
       </c>
       <c r="E38">
         <v>-668.0588287989731</v>
@@ -4394,37 +4644,37 @@
         <v>670.1</v>
       </c>
       <c r="M38">
-        <v>134.982662481314</v>
+        <v>130.2227239441956</v>
       </c>
       <c r="N38">
-        <v>535.117337518686</v>
+        <v>539.8772760558045</v>
       </c>
       <c r="O38">
-        <v>123.0769876292978</v>
+        <v>124.171773492835</v>
       </c>
       <c r="P38">
-        <v>412.0403498893882</v>
+        <v>415.7055025629695</v>
       </c>
       <c r="Q38">
-        <v>539.4403498893882</v>
+        <v>543.1055025629694</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1400887432721954</v>
+        <v>0.140063232380618</v>
       </c>
       <c r="T38">
         <v>1.458222225627848</v>
       </c>
       <c r="U38">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V38">
         <v>0.23</v>
       </c>
       <c r="W38">
-        <v>0.05677285288040334</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4432,7 +4682,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.964341254513064</v>
+        <v>5.145799286821542</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,13 +4693,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1100534287238699</v>
+        <v>0.109296402695293</v>
       </c>
       <c r="C39">
-        <v>3352.970775335758</v>
+        <v>3387.869183883212</v>
       </c>
       <c r="D39">
-        <v>4088.670410735164</v>
+        <v>4123.568819282618</v>
       </c>
       <c r="E39">
         <v>-617.2047845989891</v>
@@ -4476,37 +4726,37 @@
         <v>670.1</v>
       </c>
       <c r="M39">
-        <v>138.7321808835728</v>
+        <v>133.8400218315343</v>
       </c>
       <c r="N39">
-        <v>531.3678191164272</v>
+        <v>536.2599781684658</v>
       </c>
       <c r="O39">
-        <v>122.2145983967783</v>
+        <v>123.3397949787471</v>
       </c>
       <c r="P39">
-        <v>409.153220719649</v>
+        <v>412.9201831897186</v>
       </c>
       <c r="Q39">
-        <v>536.5532207196489</v>
+        <v>540.3201831897186</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1413451954890804</v>
+        <v>0.1413193446500695</v>
       </c>
       <c r="T39">
         <v>1.47765388294469</v>
       </c>
       <c r="U39">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V39">
         <v>0.23</v>
       </c>
       <c r="W39">
-        <v>0.05677285288040334</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4514,7 +4764,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.830169869255954</v>
+        <v>5.00672363042096</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,13 +4775,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1100118347165894</v>
+        <v>0.1092348296300453</v>
       </c>
       <c r="C40">
-        <v>3304.059230004897</v>
+        <v>3339.940712841304</v>
       </c>
       <c r="D40">
-        <v>4090.612909604286</v>
+        <v>4126.494392440694</v>
       </c>
       <c r="E40">
         <v>-566.3507403990052</v>
@@ -4558,37 +4808,37 @@
         <v>670.1</v>
       </c>
       <c r="M40">
-        <v>142.4816992858315</v>
+        <v>137.4573197188731</v>
       </c>
       <c r="N40">
-        <v>527.6183007141685</v>
+        <v>532.6426802811269</v>
       </c>
       <c r="O40">
-        <v>121.3522091642588</v>
+        <v>122.5078164646592</v>
       </c>
       <c r="P40">
-        <v>406.2660915499098</v>
+        <v>410.1348638164677</v>
       </c>
       <c r="Q40">
-        <v>533.6660915499098</v>
+        <v>537.5348638164677</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.142642178422639</v>
+        <v>0.1426159766701484</v>
       </c>
       <c r="T40">
         <v>1.497712367916913</v>
       </c>
       <c r="U40">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V40">
         <v>0.23</v>
       </c>
       <c r="W40">
-        <v>0.05677285288040334</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4596,7 +4846,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.703060135854481</v>
+        <v>4.874967745409881</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,13 +4857,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.109970240709309</v>
+        <v>0.1091732565647976</v>
       </c>
       <c r="C41">
-        <v>3255.149531286749</v>
+        <v>3292.016395994649</v>
       </c>
       <c r="D41">
-        <v>4092.557255086122</v>
+        <v>4129.424119794022</v>
       </c>
       <c r="E41">
         <v>-515.4966961990212</v>
@@ -4640,37 +4890,37 @@
         <v>670.1</v>
       </c>
       <c r="M41">
-        <v>146.2312176880902</v>
+        <v>141.0746176062119</v>
       </c>
       <c r="N41">
-        <v>523.8687823119099</v>
+        <v>529.0253823937882</v>
       </c>
       <c r="O41">
-        <v>120.4898199317393</v>
+        <v>121.6758379505713</v>
       </c>
       <c r="P41">
-        <v>403.3789623801706</v>
+        <v>407.3495444432169</v>
       </c>
       <c r="Q41">
-        <v>530.7789623801706</v>
+        <v>534.7495444432168</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1439816853868061</v>
+        <v>0.1439551212154759</v>
       </c>
       <c r="T41">
         <v>1.518428508134128</v>
       </c>
       <c r="U41">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V41">
         <v>0.23</v>
       </c>
       <c r="W41">
-        <v>0.05677285288040334</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4678,7 +4928,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.582468850319751</v>
+        <v>4.749968572450654</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,13 +4939,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1107294467020286</v>
+        <v>0.1091116834995498</v>
       </c>
       <c r="C42">
-        <v>3169.094321882119</v>
+        <v>3244.096242197715</v>
       </c>
       <c r="D42">
-        <v>4057.356089881478</v>
+        <v>4132.358010197072</v>
       </c>
       <c r="E42">
         <v>-464.6426519990373</v>
@@ -4722,45 +4972,45 @@
         <v>670.1</v>
       </c>
       <c r="M42">
-        <v>155.2695566871473</v>
+        <v>144.6919154935506</v>
       </c>
       <c r="N42">
-        <v>514.8304433128528</v>
+        <v>525.4080845064494</v>
       </c>
       <c r="O42">
-        <v>118.4110019619562</v>
+        <v>120.8438594364834</v>
       </c>
       <c r="P42">
-        <v>396.4194413508966</v>
+        <v>404.564225069966</v>
       </c>
       <c r="Q42">
-        <v>523.8194413508966</v>
+        <v>531.964225069966</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1453658425831121</v>
+        <v>0.1453389039123142</v>
       </c>
       <c r="T42">
         <v>1.539835186358582</v>
       </c>
       <c r="U42">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V42">
         <v>0.23</v>
       </c>
       <c r="W42">
-        <v>0.05877485288040333</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.315720443191482</v>
+        <v>4.631219358139388</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,13 +5021,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1107078726947481</v>
+        <v>0.1090501104343021</v>
       </c>
       <c r="C43">
-        <v>3119.232211635547</v>
+        <v>3196.180260330152</v>
       </c>
       <c r="D43">
-        <v>4058.348023834889</v>
+        <v>4135.296072529493</v>
       </c>
       <c r="E43">
         <v>-413.7886077990534</v>
@@ -4804,45 +5054,45 @@
         <v>670.1</v>
       </c>
       <c r="M43">
-        <v>159.1512956043259</v>
+        <v>148.3092133808894</v>
       </c>
       <c r="N43">
-        <v>510.9487043956741</v>
+        <v>521.7907866191106</v>
       </c>
       <c r="O43">
-        <v>117.518202011005</v>
+        <v>120.0118809223954</v>
       </c>
       <c r="P43">
-        <v>393.4305023846691</v>
+        <v>401.7789056967151</v>
       </c>
       <c r="Q43">
-        <v>520.830502384669</v>
+        <v>529.1789056967151</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1467969203623437</v>
+        <v>0.1467695944971809</v>
       </c>
       <c r="T43">
         <v>1.561967514692341</v>
       </c>
       <c r="U43">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V43">
         <v>0.23</v>
       </c>
       <c r="W43">
-        <v>0.05877485288040333</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.210458968967299</v>
+        <v>4.51826278842867</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,13 +5103,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1106862986874677</v>
+        <v>0.1097970373690544</v>
       </c>
       <c r="C44">
-        <v>3069.370586519466</v>
+        <v>3109.964985840836</v>
       </c>
       <c r="D44">
-        <v>4059.340442918792</v>
+        <v>4099.934842240161</v>
       </c>
       <c r="E44">
         <v>-362.9345635990694</v>
@@ -4886,37 +5136,37 @@
         <v>670.1</v>
       </c>
       <c r="M44">
-        <v>163.0330345215046</v>
+        <v>157.2661859092264</v>
       </c>
       <c r="N44">
-        <v>507.0669654784954</v>
+        <v>512.8338140907736</v>
       </c>
       <c r="O44">
-        <v>116.6254020600539</v>
+        <v>117.9517772408779</v>
       </c>
       <c r="P44">
-        <v>390.4415634184414</v>
+        <v>394.8820368498957</v>
       </c>
       <c r="Q44">
-        <v>517.8415634184414</v>
+        <v>522.2820368498956</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.148277345651204</v>
+        <v>0.1482496192401465</v>
       </c>
       <c r="T44">
         <v>1.584863026761746</v>
       </c>
       <c r="U44">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V44">
         <v>0.23</v>
       </c>
       <c r="W44">
-        <v>0.05877485288040333</v>
+        <v>0.05669585288040333</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4924,7 +5174,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.110209945896649</v>
+        <v>4.260928667697071</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,13 +5185,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1106647246801873</v>
+        <v>0.1097547143038067</v>
       </c>
       <c r="C45">
-        <v>3019.509446889862</v>
+        <v>3061.098441858706</v>
       </c>
       <c r="D45">
-        <v>4060.333347489172</v>
+        <v>4101.922342458015</v>
       </c>
       <c r="E45">
         <v>-312.0805193990855</v>
@@ -4968,37 +5218,37 @@
         <v>670.1</v>
       </c>
       <c r="M45">
-        <v>166.9147734386833</v>
+        <v>161.0106189070652</v>
       </c>
       <c r="N45">
-        <v>503.1852265613168</v>
+        <v>509.0893810929348</v>
       </c>
       <c r="O45">
-        <v>115.7326021091029</v>
+        <v>117.090557651375</v>
       </c>
       <c r="P45">
-        <v>387.4526244522139</v>
+        <v>391.9988234415598</v>
       </c>
       <c r="Q45">
-        <v>514.8526244522138</v>
+        <v>519.3988234415598</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1498097156870418</v>
+        <v>0.1497815746758478</v>
       </c>
       <c r="T45">
         <v>1.608561890131832</v>
       </c>
       <c r="U45">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V45">
         <v>0.23</v>
       </c>
       <c r="W45">
-        <v>0.05877485288040333</v>
+        <v>0.05669585288040333</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5006,7 +5256,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.0146236680851</v>
+        <v>4.161837303332022</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,13 +5267,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1115579106729069</v>
+        <v>0.109712391238559</v>
       </c>
       <c r="C46">
-        <v>2927.950285952462</v>
+        <v>3012.233825747673</v>
       </c>
       <c r="D46">
-        <v>4019.628230751755</v>
+        <v>4103.911770546966</v>
       </c>
       <c r="E46">
         <v>-261.2264751991015</v>
@@ -5050,45 +5300,45 @@
         <v>670.1</v>
       </c>
       <c r="M46">
-        <v>176.8379728068201</v>
+        <v>164.7550519049039</v>
       </c>
       <c r="N46">
-        <v>493.26202719318</v>
+        <v>505.3449480950961</v>
       </c>
       <c r="O46">
-        <v>113.4502662544314</v>
+        <v>116.2293380618721</v>
       </c>
       <c r="P46">
-        <v>379.8117609387485</v>
+        <v>389.115610033224</v>
       </c>
       <c r="Q46">
-        <v>507.2117609387485</v>
+        <v>516.515610033224</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1513968132241596</v>
+        <v>0.1513682428056812</v>
       </c>
       <c r="T46">
         <v>1.633107141479422</v>
       </c>
       <c r="U46">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V46">
         <v>0.23</v>
       </c>
       <c r="W46">
-        <v>0.06085385288040333</v>
+        <v>0.05669585288040333</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.789344501998026</v>
+        <v>4.067250091892658</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,13 +5349,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1115571266656264</v>
+        <v>0.1108828181733112</v>
       </c>
       <c r="C47">
-        <v>2877.131613394079</v>
+        <v>2907.064781220047</v>
       </c>
       <c r="D47">
-        <v>4019.663602393356</v>
+        <v>4049.596770219324</v>
       </c>
       <c r="E47">
         <v>-210.3724309991176</v>
@@ -5132,37 +5382,37 @@
         <v>670.1</v>
       </c>
       <c r="M47">
-        <v>180.8570176433387</v>
+        <v>176.5089968642401</v>
       </c>
       <c r="N47">
-        <v>489.2429823566613</v>
+        <v>493.5910031357599</v>
       </c>
       <c r="O47">
-        <v>112.5258859420321</v>
+        <v>113.5259307212248</v>
       </c>
       <c r="P47">
-        <v>376.7170964146292</v>
+        <v>380.0650724145352</v>
       </c>
       <c r="Q47">
-        <v>504.1170964146291</v>
+        <v>507.4650724145351</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1530416233989907</v>
+        <v>0.1530126079584177</v>
       </c>
       <c r="T47">
         <v>1.658544947421468</v>
       </c>
       <c r="U47">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V47">
         <v>0.23</v>
       </c>
       <c r="W47">
-        <v>0.06085385288040333</v>
+        <v>0.05939085288040333</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5170,7 +5420,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.705136846398069</v>
+        <v>3.796407049525073</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,13 +5431,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.111556342658346</v>
+        <v>0.1108674451080635</v>
       </c>
       <c r="C48">
-        <v>2826.312941458223</v>
+        <v>2856.914822223761</v>
       </c>
       <c r="D48">
-        <v>4019.698974657484</v>
+        <v>4050.300855423022</v>
       </c>
       <c r="E48">
         <v>-159.5183867991336</v>
@@ -5214,37 +5464,37 @@
         <v>670.1</v>
       </c>
       <c r="M48">
-        <v>184.8760624798574</v>
+        <v>180.4314190167788</v>
       </c>
       <c r="N48">
-        <v>485.2239375201427</v>
+        <v>489.6685809832213</v>
       </c>
       <c r="O48">
-        <v>111.6015056296328</v>
+        <v>112.6237736261409</v>
       </c>
       <c r="P48">
-        <v>373.6224318905099</v>
+        <v>377.0448073570803</v>
       </c>
       <c r="Q48">
-        <v>501.0224318905098</v>
+        <v>504.4448073570803</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.154747352469186</v>
+        <v>0.1547178755242185</v>
       </c>
       <c r="T48">
         <v>1.684924894324332</v>
       </c>
       <c r="U48">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V48">
         <v>0.23</v>
       </c>
       <c r="W48">
-        <v>0.06085385288040333</v>
+        <v>0.05939085288040333</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5252,7 +5502,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.624590393215503</v>
+        <v>3.713876461491919</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,13 +5513,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1115555586510655</v>
+        <v>0.1108520720428158</v>
       </c>
       <c r="C49">
-        <v>2775.49427014491</v>
+        <v>2806.765108102317</v>
       </c>
       <c r="D49">
-        <v>4019.734347544155</v>
+        <v>4051.005185501562</v>
       </c>
       <c r="E49">
         <v>-108.6643425991497</v>
@@ -5296,37 +5546,37 @@
         <v>670.1</v>
       </c>
       <c r="M49">
-        <v>188.895107316376</v>
+        <v>184.3538411693174</v>
       </c>
       <c r="N49">
-        <v>481.2048926836241</v>
+        <v>485.7461588306826</v>
       </c>
       <c r="O49">
-        <v>110.6771253172335</v>
+        <v>111.721616531057</v>
       </c>
       <c r="P49">
-        <v>370.5277673663905</v>
+        <v>374.0245422996256</v>
       </c>
       <c r="Q49">
-        <v>497.9277673663905</v>
+        <v>501.4245422996256</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1565174486741056</v>
+        <v>0.1564874928094834</v>
       </c>
       <c r="T49">
         <v>1.712300310921643</v>
       </c>
       <c r="U49">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V49">
         <v>0.23</v>
       </c>
       <c r="W49">
-        <v>0.06085385288040333</v>
+        <v>0.05939085288040333</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5334,7 +5584,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.547471448679003</v>
+        <v>3.634857813375069</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,13 +5595,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1132918946437851</v>
+        <v>0.1108366989775681</v>
       </c>
       <c r="C50">
-        <v>2647.797027780063</v>
+        <v>2756.61563898348</v>
       </c>
       <c r="D50">
-        <v>3942.891149379293</v>
+        <v>4051.709760582709</v>
       </c>
       <c r="E50">
         <v>-57.81029839916573</v>
@@ -5378,45 +5628,45 @@
         <v>670.1</v>
       </c>
       <c r="M50">
-        <v>204.3868245244111</v>
+        <v>188.2762633218561</v>
       </c>
       <c r="N50">
-        <v>465.713175475589</v>
+        <v>481.8237366781439</v>
       </c>
       <c r="O50">
-        <v>107.1140303593855</v>
+        <v>110.8194594359731</v>
       </c>
       <c r="P50">
-        <v>358.5991451162035</v>
+        <v>371.0042772421708</v>
       </c>
       <c r="Q50">
-        <v>485.9991451162035</v>
+        <v>498.4042772421708</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1583556255022914</v>
+        <v>0.1583251722980278</v>
       </c>
       <c r="T50">
         <v>1.740728628157313</v>
       </c>
       <c r="U50">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V50">
         <v>0.23</v>
       </c>
       <c r="W50">
-        <v>0.06447285288040334</v>
+        <v>0.05939085288040333</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.278587069197145</v>
+        <v>3.559131608929755</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,13 +5677,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1133273006365047</v>
+        <v>0.1118777659123204</v>
       </c>
       <c r="C51">
-        <v>2595.406610758745</v>
+        <v>2658.594879886948</v>
       </c>
       <c r="D51">
-        <v>3941.354776557959</v>
+        <v>4004.543045686161</v>
       </c>
       <c r="E51">
         <v>-6.956254199181785</v>
@@ -5460,37 +5710,37 @@
         <v>670.1</v>
       </c>
       <c r="M51">
-        <v>208.6448833686696</v>
+        <v>199.1758603386326</v>
       </c>
       <c r="N51">
-        <v>461.4551166313304</v>
+        <v>470.9241396613675</v>
       </c>
       <c r="O51">
-        <v>106.134676825206</v>
+        <v>108.3125521221145</v>
       </c>
       <c r="P51">
-        <v>355.3204398061244</v>
+        <v>362.6115875392529</v>
       </c>
       <c r="Q51">
-        <v>482.7204398061244</v>
+        <v>490.0115875392529</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1602658876962883</v>
+        <v>0.1602349176488681</v>
       </c>
       <c r="T51">
         <v>1.770271781363009</v>
       </c>
       <c r="U51">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V51">
         <v>0.23</v>
       </c>
       <c r="W51">
-        <v>0.06447285288040334</v>
+        <v>0.06154685288040335</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5498,7 +5748,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.211677129009448</v>
+        <v>3.364363527089663</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,13 +5759,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1133627066292243</v>
+        <v>0.1118839528470726</v>
       </c>
       <c r="C52">
-        <v>2543.017390586112</v>
+        <v>2607.463811871591</v>
       </c>
       <c r="D52">
-        <v>3939.81960058531</v>
+        <v>4004.266021870788</v>
       </c>
       <c r="E52">
         <v>43.89779000080216</v>
@@ -5542,37 +5792,37 @@
         <v>670.1</v>
       </c>
       <c r="M52">
-        <v>212.9029422129282</v>
+        <v>203.2406738149312</v>
       </c>
       <c r="N52">
-        <v>457.1970577870719</v>
+        <v>466.8593261850688</v>
       </c>
       <c r="O52">
-        <v>105.1553232910265</v>
+        <v>107.3776450225658</v>
       </c>
       <c r="P52">
-        <v>352.0417344960453</v>
+        <v>359.4816811625029</v>
       </c>
       <c r="Q52">
-        <v>479.4417344960453</v>
+        <v>486.8816811625029</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1622525603780452</v>
+        <v>0.1622210528137419</v>
       </c>
       <c r="T52">
         <v>1.800996660696932</v>
       </c>
       <c r="U52">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V52">
         <v>0.23</v>
       </c>
       <c r="W52">
-        <v>0.06447285288040334</v>
+        <v>0.06154685288040335</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5580,7 +5830,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.147443586429259</v>
+        <v>3.297076256547869</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,13 +5841,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1133981126219438</v>
+        <v>0.1118901397818249</v>
       </c>
       <c r="C53">
-        <v>2490.629365864176</v>
+        <v>2556.332782181149</v>
       </c>
       <c r="D53">
-        <v>3938.285620063357</v>
+        <v>4003.98903638033</v>
       </c>
       <c r="E53">
         <v>94.75183420078611</v>
@@ -5624,37 +5874,37 @@
         <v>670.1</v>
       </c>
       <c r="M53">
-        <v>217.1610010571867</v>
+        <v>207.3054872912298</v>
       </c>
       <c r="N53">
-        <v>452.9389989428133</v>
+        <v>462.7945127087702</v>
       </c>
       <c r="O53">
-        <v>104.1759697568471</v>
+        <v>106.4427379230171</v>
       </c>
       <c r="P53">
-        <v>348.7630291859663</v>
+        <v>356.351774785753</v>
       </c>
       <c r="Q53">
-        <v>476.1630291859663</v>
+        <v>483.751774785753</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.16432032174069</v>
+        <v>0.1642882547200392</v>
       </c>
       <c r="T53">
         <v>1.832975616738363</v>
       </c>
       <c r="U53">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V53">
         <v>0.23</v>
       </c>
       <c r="W53">
-        <v>0.06447285288040334</v>
+        <v>0.06154685288040335</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5662,7 +5912,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.085729006303196</v>
+        <v>3.232427702497911</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,13 +5923,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1134335186146634</v>
+        <v>0.1118963267165772</v>
       </c>
       <c r="C54">
-        <v>2438.24253519712</v>
+        <v>2505.20179080767</v>
       </c>
       <c r="D54">
-        <v>3936.752833596284</v>
+        <v>4003.712089206836</v>
       </c>
       <c r="E54">
         <v>145.6058784007701</v>
@@ -5706,37 +5956,37 @@
         <v>670.1</v>
       </c>
       <c r="M54">
-        <v>221.4190599014453</v>
+        <v>211.3703007675285</v>
       </c>
       <c r="N54">
-        <v>448.6809400985547</v>
+        <v>458.7296992324715</v>
       </c>
       <c r="O54">
-        <v>103.1966162226676</v>
+        <v>105.5078308234685</v>
       </c>
       <c r="P54">
-        <v>345.4843238758871</v>
+        <v>353.2218684090031</v>
       </c>
       <c r="Q54">
-        <v>472.8843238758871</v>
+        <v>480.6218684090031</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1664742398267784</v>
+        <v>0.1664415900390989</v>
       </c>
       <c r="T54">
         <v>1.86628702928152</v>
       </c>
       <c r="U54">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V54">
         <v>0.23</v>
       </c>
       <c r="W54">
-        <v>0.06447285288040334</v>
+        <v>0.06154685288040335</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5744,7 +5994,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.026388063874288</v>
+        <v>3.170265631296028</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,13 +6005,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.117264254607383</v>
+        <v>0.1119025136513295</v>
       </c>
       <c r="C55">
-        <v>2228.312478678882</v>
+        <v>2454.070837743203</v>
       </c>
       <c r="D55">
-        <v>3777.676821278031</v>
+        <v>4003.435180342352</v>
       </c>
       <c r="E55">
         <v>196.459922600754</v>
@@ -5788,45 +6038,45 @@
         <v>670.1</v>
       </c>
       <c r="M55">
-        <v>250.7430771318759</v>
+        <v>215.4351142438271</v>
       </c>
       <c r="N55">
-        <v>419.3569228681241</v>
+        <v>454.6648857561729</v>
       </c>
       <c r="O55">
-        <v>96.45209225966855</v>
+        <v>104.5729237239198</v>
       </c>
       <c r="P55">
-        <v>322.9048306084555</v>
+        <v>350.0919620322532</v>
       </c>
       <c r="Q55">
-        <v>450.3048306084555</v>
+        <v>477.4919620322531</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1687198140016366</v>
+        <v>0.1686865566483313</v>
       </c>
       <c r="T55">
         <v>1.901015948741407</v>
       </c>
       <c r="U55">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V55">
         <v>0.23</v>
       </c>
       <c r="W55">
-        <v>0.07163385288040333</v>
+        <v>0.06154685288040335</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.672456634356319</v>
+        <v>3.110449298630066</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,13 +6087,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1173712706001025</v>
+        <v>0.1119087005860817</v>
       </c>
       <c r="C56">
-        <v>2173.198844099767</v>
+        <v>2402.9399229798</v>
       </c>
       <c r="D56">
-        <v>3773.4172308989</v>
+        <v>4003.158309778933</v>
       </c>
       <c r="E56">
         <v>247.3139668007379</v>
@@ -5870,45 +6120,45 @@
         <v>670.1</v>
       </c>
       <c r="M56">
-        <v>255.4740785871943</v>
+        <v>219.4999277201257</v>
       </c>
       <c r="N56">
-        <v>414.6259214128057</v>
+        <v>450.6000722798743</v>
       </c>
       <c r="O56">
-        <v>95.36396192494531</v>
+        <v>103.6380166243711</v>
       </c>
       <c r="P56">
-        <v>319.2619594878604</v>
+        <v>346.9620556555032</v>
       </c>
       <c r="Q56">
-        <v>446.6619594878604</v>
+        <v>474.3620556555032</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1710630218362711</v>
+        <v>0.1710291305014434</v>
       </c>
       <c r="T56">
         <v>1.937254821221289</v>
       </c>
       <c r="U56">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V56">
         <v>0.23</v>
       </c>
       <c r="W56">
-        <v>0.07163385288040333</v>
+        <v>0.06154685288040335</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.622966696683054</v>
+        <v>3.052848385692472</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,13 +6169,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1174782865928221</v>
+        <v>0.115218187520834</v>
       </c>
       <c r="C57">
-        <v>2118.094804663578</v>
+        <v>2209.276832992536</v>
       </c>
       <c r="D57">
-        <v>3769.167235662694</v>
+        <v>3860.349263991653</v>
       </c>
       <c r="E57">
         <v>298.1680110007219</v>
@@ -5952,37 +6202,37 @@
         <v>670.1</v>
       </c>
       <c r="M57">
-        <v>260.2050800425127</v>
+        <v>245.3811261582175</v>
       </c>
       <c r="N57">
-        <v>409.8949199574873</v>
+        <v>424.7188738417826</v>
       </c>
       <c r="O57">
-        <v>94.27583159022208</v>
+        <v>97.68534098360999</v>
       </c>
       <c r="P57">
-        <v>315.6190883672652</v>
+        <v>327.0335328581726</v>
       </c>
       <c r="Q57">
-        <v>443.0190883672652</v>
+        <v>454.4335328581726</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1735103722413339</v>
+        <v>0.1734758187480271</v>
       </c>
       <c r="T57">
         <v>1.975104310255832</v>
       </c>
       <c r="U57">
-        <v>0.09303097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V57">
         <v>0.23</v>
       </c>
       <c r="W57">
-        <v>0.07163385288040333</v>
+        <v>0.06755285288040334</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5990,7 +6240,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.575276393106998</v>
+        <v>2.730853878174523</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,13 +6251,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1175853025855416</v>
+        <v>0.1152844344555863</v>
       </c>
       <c r="C58">
-        <v>2063.000327985791</v>
+        <v>2155.668086627763</v>
       </c>
       <c r="D58">
-        <v>3764.926803184892</v>
+        <v>3857.594561826865</v>
       </c>
       <c r="E58">
         <v>349.0220552007063</v>
@@ -6034,37 +6284,37 @@
         <v>670.1</v>
       </c>
       <c r="M58">
-        <v>264.9360814978312</v>
+        <v>249.842601179276</v>
       </c>
       <c r="N58">
-        <v>405.1639185021688</v>
+        <v>420.257398820724</v>
       </c>
       <c r="O58">
-        <v>93.18770125549884</v>
+        <v>96.65920172876652</v>
       </c>
       <c r="P58">
-        <v>311.97621724667</v>
+        <v>323.5981970919575</v>
       </c>
       <c r="Q58">
-        <v>439.37621724667</v>
+        <v>450.9981970919575</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1760689658466268</v>
+        <v>0.1760337200967283</v>
       </c>
       <c r="T58">
         <v>2.014674230610128</v>
       </c>
       <c r="U58">
-        <v>0.09303097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V58">
         <v>0.23</v>
       </c>
       <c r="W58">
-        <v>0.07163385288040333</v>
+        <v>0.06755285288040334</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6072,7 +6322,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.529289314658659</v>
+        <v>2.682088630349977</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,13 +6333,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1197551485782612</v>
+        <v>0.1153506813903386</v>
       </c>
       <c r="C59">
-        <v>1928.179773595015</v>
+        <v>2102.063268909015</v>
       </c>
       <c r="D59">
-        <v>3680.9602929941</v>
+        <v>3854.8437883081</v>
       </c>
       <c r="E59">
         <v>399.8760994006902</v>
@@ -6116,45 +6366,45 @@
         <v>670.1</v>
       </c>
       <c r="M59">
-        <v>283.2908813943253</v>
+        <v>254.3040762003345</v>
       </c>
       <c r="N59">
-        <v>386.8091186056747</v>
+        <v>415.7959237996655</v>
       </c>
       <c r="O59">
-        <v>88.96609727930519</v>
+        <v>95.63306247392308</v>
       </c>
       <c r="P59">
-        <v>297.8430213263695</v>
+        <v>320.1628613257424</v>
       </c>
       <c r="Q59">
-        <v>425.2430213263695</v>
+        <v>447.5628613257424</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1787465638056542</v>
+        <v>0.178710593601183</v>
       </c>
       <c r="T59">
         <v>2.056084612376251</v>
       </c>
       <c r="U59">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V59">
         <v>0.23</v>
       </c>
       <c r="W59">
-        <v>0.07525285288040333</v>
+        <v>0.06755285288040334</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.36541323427653</v>
+        <v>2.635034443852609</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,13 +6415,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1198983545709808</v>
+        <v>0.1154169283250909</v>
       </c>
       <c r="C60">
-        <v>1871.915642913035</v>
+        <v>2048.46237143796</v>
       </c>
       <c r="D60">
-        <v>3675.550206512104</v>
+        <v>3852.096935037029</v>
       </c>
       <c r="E60">
         <v>450.7301436006737</v>
@@ -6198,45 +6448,45 @@
         <v>670.1</v>
       </c>
       <c r="M60">
-        <v>288.2608968573836</v>
+        <v>258.765551221393</v>
       </c>
       <c r="N60">
-        <v>381.8391031426164</v>
+        <v>411.3344487786071</v>
       </c>
       <c r="O60">
-        <v>87.82299372280178</v>
+        <v>94.60692321907963</v>
       </c>
       <c r="P60">
-        <v>294.0161094198146</v>
+        <v>316.7275255595274</v>
       </c>
       <c r="Q60">
-        <v>421.4161094198146</v>
+        <v>444.1275255595274</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1815516664293973</v>
+        <v>0.1815149372725165</v>
       </c>
       <c r="T60">
         <v>2.099466917083618</v>
       </c>
       <c r="U60">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V60">
         <v>0.23</v>
       </c>
       <c r="W60">
-        <v>0.07525285288040333</v>
+        <v>0.06755285288040334</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.32463024747866</v>
+        <v>2.589602815510323</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,13 +6497,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1200415605637003</v>
+        <v>0.1154831752598431</v>
       </c>
       <c r="C61">
-        <v>1815.667391826828</v>
+        <v>1994.865385840195</v>
       </c>
       <c r="D61">
-        <v>3670.155999625881</v>
+        <v>3849.353993639247</v>
       </c>
       <c r="E61">
         <v>501.5841878006577</v>
@@ -6280,45 +6530,45 @@
         <v>670.1</v>
       </c>
       <c r="M61">
-        <v>293.2309123204419</v>
+        <v>263.2270262424515</v>
       </c>
       <c r="N61">
-        <v>376.8690876795581</v>
+        <v>406.8729737575486</v>
       </c>
       <c r="O61">
-        <v>86.67989016629836</v>
+        <v>93.58078396423618</v>
       </c>
       <c r="P61">
-        <v>290.1891975132597</v>
+        <v>313.2921897933124</v>
       </c>
       <c r="Q61">
-        <v>417.5891975132597</v>
+        <v>440.6921897933124</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1844936033274692</v>
+        <v>0.1844560781961102</v>
       </c>
       <c r="T61">
         <v>2.14496543177671</v>
       </c>
       <c r="U61">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V61">
         <v>0.23</v>
       </c>
       <c r="W61">
-        <v>0.07525285288040333</v>
+        <v>0.06755285288040334</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.28522973480953</v>
+        <v>2.545711242366081</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,13 +6579,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1201847665564199</v>
+        <v>0.1155494221945954</v>
       </c>
       <c r="C62">
-        <v>1759.434950524555</v>
+        <v>1941.272303765144</v>
       </c>
       <c r="D62">
-        <v>3664.777602523593</v>
+        <v>3846.614955764181</v>
       </c>
       <c r="E62">
         <v>552.4382320006416</v>
@@ -6362,45 +6612,45 @@
         <v>670.1</v>
       </c>
       <c r="M62">
-        <v>298.2009277835003</v>
+        <v>267.68850126351</v>
       </c>
       <c r="N62">
-        <v>371.8990722164997</v>
+        <v>402.41149873649</v>
       </c>
       <c r="O62">
-        <v>85.53678660979494</v>
+        <v>92.55464470939272</v>
       </c>
       <c r="P62">
-        <v>286.3622856067048</v>
+        <v>309.8568540270973</v>
       </c>
       <c r="Q62">
-        <v>413.7622856067048</v>
+        <v>437.2568540270973</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1875826370704448</v>
+        <v>0.1875442761658835</v>
       </c>
       <c r="T62">
         <v>2.192738872204457</v>
       </c>
       <c r="U62">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V62">
         <v>0.23</v>
       </c>
       <c r="W62">
-        <v>0.07525285288040333</v>
+        <v>0.06755285288040334</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.247142572562704</v>
+        <v>2.503282721659979</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,13 +6661,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1203279725491395</v>
+        <v>0.1174474991293477</v>
       </c>
       <c r="C63">
-        <v>1703.218249603012</v>
+        <v>1813.563297788368</v>
       </c>
       <c r="D63">
-        <v>3659.414945802033</v>
+        <v>3769.759993987388</v>
       </c>
       <c r="E63">
         <v>603.2922762006256</v>
@@ -6444,37 +6694,37 @@
         <v>670.1</v>
       </c>
       <c r="M63">
-        <v>303.1709432465586</v>
+        <v>284.2481533997446</v>
       </c>
       <c r="N63">
-        <v>366.9290567534414</v>
+        <v>385.8518466002554</v>
       </c>
       <c r="O63">
-        <v>84.39368305329154</v>
+        <v>88.74592471805876</v>
       </c>
       <c r="P63">
-        <v>282.5353737001499</v>
+        <v>297.1059218821967</v>
       </c>
       <c r="Q63">
-        <v>409.9353737001499</v>
+        <v>424.5059218821967</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1908300828002397</v>
+        <v>0.190790843262312</v>
       </c>
       <c r="T63">
         <v>2.24296223265414</v>
       </c>
       <c r="U63">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V63">
         <v>0.23</v>
       </c>
       <c r="W63">
-        <v>0.07525285288040333</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6482,7 +6732,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.210304169733808</v>
+        <v>2.357447153078329</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,13 +6743,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1204711785418591</v>
+        <v>0.1175437760641</v>
       </c>
       <c r="C64">
-        <v>1647.017220064621</v>
+        <v>1758.892664298146</v>
       </c>
       <c r="D64">
-        <v>3654.067960463625</v>
+        <v>3765.94340469715</v>
       </c>
       <c r="E64">
         <v>654.1463204006095</v>
@@ -6526,37 +6776,37 @@
         <v>670.1</v>
       </c>
       <c r="M64">
-        <v>308.1409587096169</v>
+        <v>288.907959193183</v>
       </c>
       <c r="N64">
-        <v>361.9590412903831</v>
+        <v>381.192040806817</v>
       </c>
       <c r="O64">
-        <v>83.25057949678811</v>
+        <v>87.67416938556791</v>
       </c>
       <c r="P64">
-        <v>278.708461793595</v>
+        <v>293.5178714212491</v>
       </c>
       <c r="Q64">
-        <v>406.108461793595</v>
+        <v>420.9178714212491</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1942484467263395</v>
+        <v>0.194208282311184</v>
       </c>
       <c r="T64">
         <v>2.295828927864332</v>
       </c>
       <c r="U64">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V64">
         <v>0.23</v>
       </c>
       <c r="W64">
-        <v>0.07525285288040333</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6564,7 +6814,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.174654102480036</v>
+        <v>2.319423811899646</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,13 +6825,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1206143845345786</v>
+        <v>0.1176400529988523</v>
       </c>
       <c r="C65">
-        <v>1590.831793314485</v>
+        <v>1704.229750992469</v>
       </c>
       <c r="D65">
-        <v>3648.736577913474</v>
+        <v>3762.134535591458</v>
       </c>
       <c r="E65">
         <v>705.0003646005935</v>
@@ -6608,37 +6858,37 @@
         <v>670.1</v>
       </c>
       <c r="M65">
-        <v>313.1109741726753</v>
+        <v>293.5677649866215</v>
       </c>
       <c r="N65">
-        <v>356.9890258273247</v>
+        <v>376.5322350133786</v>
       </c>
       <c r="O65">
-        <v>82.10747594028469</v>
+        <v>86.60241405307707</v>
       </c>
       <c r="P65">
-        <v>274.88154988704</v>
+        <v>289.9298209603015</v>
       </c>
       <c r="Q65">
-        <v>402.28154988704</v>
+        <v>417.3298209603015</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1978515870808771</v>
+        <v>0.1978104477951302</v>
       </c>
       <c r="T65">
         <v>2.351553282275075</v>
       </c>
       <c r="U65">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V65">
         <v>0.23</v>
       </c>
       <c r="W65">
-        <v>0.07525285288040333</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6646,7 +6896,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.140135783393052</v>
+        <v>2.282607560917112</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,13 +6907,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1207575905272982</v>
+        <v>0.1177363299336045</v>
       </c>
       <c r="C66">
-        <v>1534.661901157452</v>
+        <v>1649.57453447046</v>
       </c>
       <c r="D66">
-        <v>3643.420729956425</v>
+        <v>3758.333363269433</v>
       </c>
       <c r="E66">
         <v>755.8544088005774</v>
@@ -6690,37 +6940,37 @@
         <v>670.1</v>
       </c>
       <c r="M66">
-        <v>318.0809896357336</v>
+        <v>298.2275707800599</v>
       </c>
       <c r="N66">
-        <v>352.0190103642664</v>
+        <v>371.8724292199401</v>
       </c>
       <c r="O66">
-        <v>80.96437238378128</v>
+        <v>85.53065872058623</v>
       </c>
       <c r="P66">
-        <v>271.0546379804852</v>
+        <v>286.3417704993539</v>
       </c>
       <c r="Q66">
-        <v>398.4546379804851</v>
+        <v>413.7417704993538</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2016549018995557</v>
+        <v>0.20161273358374</v>
       </c>
       <c r="T66">
         <v>2.410373434153082</v>
       </c>
       <c r="U66">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V66">
         <v>0.23</v>
       </c>
       <c r="W66">
-        <v>0.07525285288040333</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6728,7 +6978,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.106696161777536</v>
+        <v>2.246941817777782</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,13 +6989,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1209007965200178</v>
+        <v>0.1178326068683568</v>
       </c>
       <c r="C67">
-        <v>1478.507475795203</v>
+        <v>1594.926991425717</v>
       </c>
       <c r="D67">
-        <v>3638.12034879416</v>
+        <v>3754.539864424674</v>
       </c>
       <c r="E67">
         <v>806.7084530005613</v>
@@ -6772,37 +7022,37 @@
         <v>670.1</v>
       </c>
       <c r="M67">
-        <v>323.051005098792</v>
+        <v>302.8873765734983</v>
       </c>
       <c r="N67">
-        <v>347.0489949012081</v>
+        <v>367.2126234265017</v>
       </c>
       <c r="O67">
-        <v>79.82126882727786</v>
+        <v>84.45890338809539</v>
       </c>
       <c r="P67">
-        <v>267.2277260739302</v>
+        <v>282.7537200384063</v>
       </c>
       <c r="Q67">
-        <v>394.6277260739301</v>
+        <v>410.1537200384063</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2056755489935874</v>
+        <v>0.2056322928459847</v>
       </c>
       <c r="T67">
         <v>2.472554737566975</v>
       </c>
       <c r="U67">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V67">
         <v>0.23</v>
       </c>
       <c r="W67">
-        <v>0.07525285288040333</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6810,7 +7060,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.074285451596342</v>
+        <v>2.212373482119663</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,13 +7071,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1210440025127373</v>
+        <v>0.1179288838031091</v>
       </c>
       <c r="C68">
-        <v>1422.368449823376</v>
+        <v>1540.287098645846</v>
       </c>
       <c r="D68">
-        <v>3632.835367022317</v>
+        <v>3750.754015844785</v>
       </c>
       <c r="E68">
         <v>857.5624972005453</v>
@@ -6854,37 +7104,37 @@
         <v>670.1</v>
       </c>
       <c r="M68">
-        <v>328.0210205618503</v>
+        <v>307.5471823669368</v>
       </c>
       <c r="N68">
-        <v>342.0789794381497</v>
+        <v>362.5528176330632</v>
       </c>
       <c r="O68">
-        <v>78.67816527077443</v>
+        <v>83.38714805560454</v>
       </c>
       <c r="P68">
-        <v>263.4008141673753</v>
+        <v>279.1656695774587</v>
       </c>
       <c r="Q68">
-        <v>390.8008141673753</v>
+        <v>406.5656695774587</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2099327047402092</v>
+        <v>0.2098882967707144</v>
       </c>
       <c r="T68">
         <v>2.538393764711097</v>
       </c>
       <c r="U68">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V68">
         <v>0.23</v>
       </c>
       <c r="W68">
-        <v>0.07525285288040333</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6892,7 +7142,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.042856884147913</v>
+        <v>2.178852671784516</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,13 +7153,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1211872085054569</v>
+        <v>0.1180251607378613</v>
       </c>
       <c r="C69">
-        <v>1366.244756228706</v>
+        <v>1485.654833011976</v>
       </c>
       <c r="D69">
-        <v>3627.56571762763</v>
+        <v>3746.975794410901</v>
       </c>
       <c r="E69">
         <v>908.4165414005292</v>
@@ -6936,37 +7186,37 @@
         <v>670.1</v>
       </c>
       <c r="M69">
-        <v>332.9910360249086</v>
+        <v>312.2069881603752</v>
       </c>
       <c r="N69">
-        <v>337.1089639750914</v>
+        <v>357.8930118396248</v>
       </c>
       <c r="O69">
-        <v>77.53506171427102</v>
+        <v>82.31539272311372</v>
       </c>
       <c r="P69">
-        <v>259.5739022608204</v>
+        <v>275.5776191165111</v>
       </c>
       <c r="Q69">
-        <v>386.9739022608204</v>
+        <v>402.9776191165111</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2144478699260202</v>
+        <v>0.2144022403272458</v>
       </c>
       <c r="T69">
         <v>2.608223035924559</v>
       </c>
       <c r="U69">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V69">
         <v>0.23</v>
       </c>
       <c r="W69">
-        <v>0.07525285288040333</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6974,7 +7224,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.012366482891974</v>
+        <v>2.146332482653404</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,13 +7235,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1298650944981765</v>
+        <v>0.1181214376726136</v>
       </c>
       <c r="C70">
-        <v>1022.291214139278</v>
+        <v>1431.0301714983</v>
       </c>
       <c r="D70">
-        <v>3334.466219738186</v>
+        <v>3743.205177097209</v>
       </c>
       <c r="E70">
         <v>959.2705856005136</v>
@@ -7018,45 +7268,45 @@
         <v>670.1</v>
       </c>
       <c r="M70">
-        <v>394.3276740792293</v>
+        <v>316.8667939538137</v>
       </c>
       <c r="N70">
-        <v>275.7723259207708</v>
+        <v>353.2332060461864</v>
       </c>
       <c r="O70">
-        <v>63.42763496177728</v>
+        <v>81.24363739062287</v>
       </c>
       <c r="P70">
-        <v>212.3446909589935</v>
+        <v>271.9895686555635</v>
       </c>
       <c r="Q70">
-        <v>339.7446909589935</v>
+        <v>399.3895686555635</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2192452329359444</v>
+        <v>0.2191983053560606</v>
       </c>
       <c r="T70">
         <v>2.682416636588863</v>
       </c>
       <c r="U70">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V70">
         <v>0.23</v>
       </c>
       <c r="W70">
-        <v>0.08780385288040334</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.699348141275425</v>
+        <v>2.114768769673207</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,13 +7317,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.130133810490896</v>
+        <v>0.1182177146073659</v>
       </c>
       <c r="C71">
-        <v>963.1153090083858</v>
+        <v>1376.413091171602</v>
       </c>
       <c r="D71">
-        <v>3326.144358807278</v>
+        <v>3739.442140970495</v>
       </c>
       <c r="E71">
         <v>1010.124629800498</v>
@@ -7100,45 +7350,45 @@
         <v>670.1</v>
       </c>
       <c r="M71">
-        <v>400.1266104627474</v>
+        <v>321.5265997472521</v>
       </c>
       <c r="N71">
-        <v>269.9733895372527</v>
+        <v>348.5734002527479</v>
       </c>
       <c r="O71">
-        <v>62.09387959356812</v>
+        <v>80.17188205813201</v>
       </c>
       <c r="P71">
-        <v>207.8795099436846</v>
+        <v>268.4015181946158</v>
       </c>
       <c r="Q71">
-        <v>335.2795099436845</v>
+        <v>395.8015181946158</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2243521032368314</v>
+        <v>0.2243037939351214</v>
       </c>
       <c r="T71">
         <v>2.761396921166994</v>
       </c>
       <c r="U71">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V71">
         <v>0.23</v>
       </c>
       <c r="W71">
-        <v>0.08780385288040334</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.674719907343897</v>
+        <v>2.08411994692432</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,13 +7399,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1304025264836156</v>
+        <v>0.1183139915421182</v>
       </c>
       <c r="C72">
-        <v>903.9808383732993</v>
+        <v>1321.803569190792</v>
       </c>
       <c r="D72">
-        <v>3317.863932372176</v>
+        <v>3735.686663189669</v>
       </c>
       <c r="E72">
         <v>1060.978674000482</v>
@@ -7182,45 +7432,45 @@
         <v>670.1</v>
       </c>
       <c r="M72">
-        <v>405.9255468462654</v>
+        <v>326.1864055406905</v>
       </c>
       <c r="N72">
-        <v>264.1744531537346</v>
+        <v>343.9135944593095</v>
       </c>
       <c r="O72">
-        <v>60.76012422535896</v>
+        <v>79.10012672564119</v>
       </c>
       <c r="P72">
-        <v>203.4143289283756</v>
+        <v>264.8134677336683</v>
       </c>
       <c r="Q72">
-        <v>330.8143289283756</v>
+        <v>392.2134677336683</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2297994315577776</v>
+        <v>0.2297496484194529</v>
       </c>
       <c r="T72">
         <v>2.845642558050332</v>
       </c>
       <c r="U72">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V72">
         <v>0.23</v>
       </c>
       <c r="W72">
-        <v>0.08780385288040334</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.650795337238985</v>
+        <v>2.054346804825401</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,13 +7481,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1306712424763352</v>
+        <v>0.1184102684768705</v>
       </c>
       <c r="C73">
-        <v>844.8874935493277</v>
+        <v>1267.201582806441</v>
       </c>
       <c r="D73">
-        <v>3309.624631748188</v>
+        <v>3731.938721005301</v>
       </c>
       <c r="E73">
         <v>1111.832718200465</v>
@@ -7264,45 +7514,45 @@
         <v>670.1</v>
       </c>
       <c r="M73">
-        <v>411.7244832297835</v>
+        <v>330.846211334129</v>
       </c>
       <c r="N73">
-        <v>258.3755167702166</v>
+        <v>339.2537886658711</v>
       </c>
       <c r="O73">
-        <v>59.42636885714981</v>
+        <v>78.02837139315035</v>
       </c>
       <c r="P73">
-        <v>198.9491479130668</v>
+        <v>261.2254172727207</v>
       </c>
       <c r="Q73">
-        <v>326.3491479130668</v>
+        <v>388.6254172727207</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2356224376939614</v>
+        <v>0.2355710790751176</v>
       </c>
       <c r="T73">
         <v>2.935698238856659</v>
       </c>
       <c r="U73">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V73">
         <v>0.23</v>
       </c>
       <c r="W73">
-        <v>0.08780385288040334</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.627544698686323</v>
+        <v>2.025412342785606</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,13 +7563,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1309399584690547</v>
+        <v>0.1263790254116227</v>
       </c>
       <c r="C74">
-        <v>785.8349689104307</v>
+        <v>930.2062618117361</v>
       </c>
       <c r="D74">
-        <v>3301.426151309274</v>
+        <v>3445.79744421058</v>
       </c>
       <c r="E74">
         <v>1162.686762400449</v>
@@ -7346,37 +7596,37 @@
         <v>670.1</v>
       </c>
       <c r="M74">
-        <v>417.5234196133015</v>
+        <v>387.499191917631</v>
       </c>
       <c r="N74">
-        <v>252.5765803866985</v>
+        <v>282.600808082369</v>
       </c>
       <c r="O74">
-        <v>58.09261348894065</v>
+        <v>64.99818585894488</v>
       </c>
       <c r="P74">
-        <v>194.4839668977578</v>
+        <v>217.6026222234242</v>
       </c>
       <c r="Q74">
-        <v>321.8839668977578</v>
+        <v>345.0026222234242</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2418613728398726</v>
+        <v>0.2418083262061869</v>
       </c>
       <c r="T74">
         <v>3.032186468292009</v>
       </c>
       <c r="U74">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V74">
         <v>0.23</v>
       </c>
       <c r="W74">
-        <v>0.08780385288040334</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7384,7 +7634,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.604939911204569</v>
+        <v>1.729293928804993</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,13 +7645,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1312086744617743</v>
+        <v>0.126584642346375</v>
       </c>
       <c r="C75">
-        <v>726.8229618514242</v>
+        <v>872.5485092101881</v>
       </c>
       <c r="D75">
-        <v>3293.268188450252</v>
+        <v>3438.993735809016</v>
       </c>
       <c r="E75">
         <v>1213.540806600433</v>
@@ -7428,37 +7678,37 @@
         <v>670.1</v>
       </c>
       <c r="M75">
-        <v>423.3223559968196</v>
+        <v>392.8811251387092</v>
       </c>
       <c r="N75">
-        <v>246.7776440031805</v>
+        <v>277.2188748612908</v>
       </c>
       <c r="O75">
-        <v>56.75885812073151</v>
+        <v>63.76034121809689</v>
       </c>
       <c r="P75">
-        <v>190.018785882449</v>
+        <v>213.4585336431939</v>
       </c>
       <c r="Q75">
-        <v>317.4187858824489</v>
+        <v>340.8585336431939</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2485624513299254</v>
+        <v>0.2485075916432614</v>
       </c>
       <c r="T75">
         <v>3.135821973981831</v>
       </c>
       <c r="U75">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V75">
         <v>0.23</v>
       </c>
       <c r="W75">
-        <v>0.08780385288040334</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7466,7 +7716,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.58295443296889</v>
+        <v>1.705604970876157</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,13 +7727,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1314773904544939</v>
+        <v>0.1267902592811273</v>
       </c>
       <c r="C76">
-        <v>667.8511727507557</v>
+        <v>814.9175714337362</v>
       </c>
       <c r="D76">
-        <v>3285.150443549568</v>
+        <v>3432.216842232548</v>
       </c>
       <c r="E76">
         <v>1264.394850800417</v>
@@ -7510,37 +7760,37 @@
         <v>670.1</v>
       </c>
       <c r="M76">
-        <v>429.1212923803376</v>
+        <v>398.2630583597874</v>
       </c>
       <c r="N76">
-        <v>240.9787076196624</v>
+        <v>271.8369416402126</v>
       </c>
       <c r="O76">
-        <v>55.42510275252235</v>
+        <v>62.5224965772489</v>
       </c>
       <c r="P76">
-        <v>185.55360486714</v>
+        <v>209.3144450629637</v>
       </c>
       <c r="Q76">
-        <v>312.95360486714</v>
+        <v>336.7144450629637</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2557789973961361</v>
+        <v>0.2557221851908801</v>
       </c>
       <c r="T76">
         <v>3.247429441647792</v>
       </c>
       <c r="U76">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V76">
         <v>0.23</v>
       </c>
       <c r="W76">
-        <v>0.08780385288040334</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7548,7 +7798,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.561563156847689</v>
+        <v>1.682556255053507</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,13 +7809,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1317461064472135</v>
+        <v>0.1269958762158796</v>
       </c>
       <c r="C77">
-        <v>608.9193049338155</v>
+        <v>757.3132902699754</v>
       </c>
       <c r="D77">
-        <v>3277.072619932611</v>
+        <v>3425.466605268771</v>
       </c>
       <c r="E77">
         <v>1315.248895000401</v>
@@ -7592,37 +7842,37 @@
         <v>670.1</v>
       </c>
       <c r="M77">
-        <v>434.9202287638557</v>
+        <v>403.6449915808656</v>
       </c>
       <c r="N77">
-        <v>235.1797712361443</v>
+        <v>266.4550084191344</v>
       </c>
       <c r="O77">
-        <v>54.09134738431319</v>
+        <v>61.28465193640091</v>
       </c>
       <c r="P77">
-        <v>181.0884238518311</v>
+        <v>205.1703564827335</v>
       </c>
       <c r="Q77">
-        <v>308.488423851831</v>
+        <v>332.5703564827335</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2635728671476438</v>
+        <v>0.2635139462223083</v>
       </c>
       <c r="T77">
         <v>3.367965506727031</v>
       </c>
       <c r="U77">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V77">
         <v>0.23</v>
       </c>
       <c r="W77">
-        <v>0.08780385288040334</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7630,7 +7880,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.540742314756386</v>
+        <v>1.660122171652793</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,13 +7891,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.132014822439933</v>
+        <v>0.1272014931506319</v>
       </c>
       <c r="C78">
-        <v>550.0270646368008</v>
+        <v>699.7355087487049</v>
       </c>
       <c r="D78">
-        <v>3269.034423835581</v>
+        <v>3418.742867947485</v>
       </c>
       <c r="E78">
         <v>1366.102939200385</v>
@@ -7674,37 +7924,37 @@
         <v>670.1</v>
       </c>
       <c r="M78">
-        <v>440.7191651473738</v>
+        <v>409.0269248019438</v>
       </c>
       <c r="N78">
-        <v>229.3808348526262</v>
+        <v>261.0730751980562</v>
       </c>
       <c r="O78">
-        <v>52.75759201610403</v>
+        <v>60.04680729555292</v>
       </c>
       <c r="P78">
-        <v>176.6232428365222</v>
+        <v>201.0262679025033</v>
       </c>
       <c r="Q78">
-        <v>304.0232428365222</v>
+        <v>328.4262679025032</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2720162260451103</v>
+        <v>0.2719550206730222</v>
       </c>
       <c r="T78">
         <v>3.498546243896206</v>
       </c>
       <c r="U78">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V78">
         <v>0.23</v>
       </c>
       <c r="W78">
-        <v>0.08780385288040334</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7712,7 +7962,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.520469389562223</v>
+        <v>1.638278458867888</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,13 +7973,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1322835384326526</v>
+        <v>0.1274071100853841</v>
       </c>
       <c r="C79">
-        <v>491.174160971098</v>
+        <v>642.1840711297564</v>
       </c>
       <c r="D79">
-        <v>3261.035564369862</v>
+        <v>3412.04547452852</v>
       </c>
       <c r="E79">
         <v>1416.956983400369</v>
@@ -7756,37 +8006,37 @@
         <v>670.1</v>
       </c>
       <c r="M79">
-        <v>446.5181015308919</v>
+        <v>414.408858023022</v>
       </c>
       <c r="N79">
-        <v>223.5818984691081</v>
+        <v>255.691141976978</v>
       </c>
       <c r="O79">
-        <v>51.42383664789487</v>
+        <v>58.80896265470493</v>
       </c>
       <c r="P79">
-        <v>172.1580618212133</v>
+        <v>196.882179322273</v>
       </c>
       <c r="Q79">
-        <v>299.5580618212132</v>
+        <v>324.282179322273</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2811937900640957</v>
+        <v>0.2811301015977112</v>
       </c>
       <c r="T79">
         <v>3.640481827775745</v>
       </c>
       <c r="U79">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V79">
         <v>0.23</v>
       </c>
       <c r="W79">
-        <v>0.08780385288040334</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7794,7 +8044,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.500723033853623</v>
+        <v>1.617002115246227</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,13 +8055,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.174404920422707</v>
+        <v>0.1276127270201364</v>
       </c>
       <c r="C80">
-        <v>-463.7030155345637</v>
+        <v>584.6588228909641</v>
       </c>
       <c r="D80">
-        <v>2357.012432064184</v>
+        <v>3405.374270489712</v>
       </c>
       <c r="E80">
         <v>1467.811027600353</v>
@@ -7838,45 +8088,45 @@
         <v>670.1</v>
       </c>
       <c r="M80">
-        <v>711.7336881873681</v>
+        <v>419.7907912441003</v>
       </c>
       <c r="N80">
-        <v>-41.63368818736808</v>
+        <v>250.3092087558998</v>
       </c>
       <c r="O80">
-        <v>-9.575748283094658</v>
+        <v>57.57111801385695</v>
       </c>
       <c r="P80">
-        <v>-32.05793990427343</v>
+        <v>192.7380907420428</v>
       </c>
       <c r="Q80">
-        <v>95.34206009572655</v>
+        <v>320.1380907420428</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2943440390670036</v>
+        <v>0.2911392807882811</v>
       </c>
       <c r="T80">
-        <v>3.843856957224898</v>
+        <v>3.795320646553423</v>
       </c>
       <c r="U80">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V80">
-        <v>0.2165458830430213</v>
+        <v>0.23</v>
       </c>
       <c r="W80">
-        <v>0.1405759382409823</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.9415038393174839</v>
+        <v>1.596271318896916</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,13 +8137,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1757412302003746</v>
+        <v>0.1278183439548887</v>
       </c>
       <c r="C81">
-        <v>-535.1059114582058</v>
+        <v>527.1596107162959</v>
       </c>
       <c r="D81">
-        <v>2336.463580340526</v>
+        <v>3398.729102515027</v>
       </c>
       <c r="E81">
         <v>1518.665071800337</v>
@@ -7920,45 +8170,45 @@
         <v>670.1</v>
       </c>
       <c r="M81">
-        <v>720.8584790615652</v>
+        <v>425.1727244651785</v>
       </c>
       <c r="N81">
-        <v>-50.75847906156514</v>
+        <v>244.9272755348215</v>
       </c>
       <c r="O81">
-        <v>-11.67445018415998</v>
+        <v>56.33327337300896</v>
       </c>
       <c r="P81">
-        <v>-39.08402887740516</v>
+        <v>188.5940021618126</v>
       </c>
       <c r="Q81">
-        <v>88.31597112259482</v>
+        <v>315.9940021618125</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3061794694987657</v>
+        <v>0.3021017151398575</v>
       </c>
       <c r="T81">
-        <v>4.026897764711799</v>
+        <v>3.964906019500403</v>
       </c>
       <c r="U81">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V81">
-        <v>0.2138047959158944</v>
+        <v>0.23</v>
       </c>
       <c r="W81">
-        <v>0.1410677741843466</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.929586069199541</v>
+        <v>1.57606535283493</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,13 +8219,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1770775399780422</v>
+        <v>0.128023960889641</v>
       </c>
       <c r="C82">
-        <v>-606.1536070258862</v>
+        <v>469.6862824840864</v>
       </c>
       <c r="D82">
-        <v>2316.269928972829</v>
+        <v>3392.109818482802</v>
       </c>
       <c r="E82">
         <v>1569.519116000321</v>
@@ -8002,45 +8252,45 @@
         <v>670.1</v>
       </c>
       <c r="M82">
-        <v>729.9832699357622</v>
+        <v>430.5546576862567</v>
       </c>
       <c r="N82">
-        <v>-59.8832699357622</v>
+        <v>239.5453423137433</v>
       </c>
       <c r="O82">
-        <v>-13.77315208522531</v>
+        <v>55.09542873216097</v>
       </c>
       <c r="P82">
-        <v>-46.11011785053689</v>
+        <v>184.4499135815824</v>
       </c>
       <c r="Q82">
-        <v>81.28988214946308</v>
+        <v>311.8499135815823</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.319198442973704</v>
+        <v>0.3141603929265916</v>
       </c>
       <c r="T82">
-        <v>4.228242652947388</v>
+        <v>4.151449929742082</v>
       </c>
       <c r="U82">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V82">
-        <v>0.2111322359669458</v>
+        <v>0.23</v>
       </c>
       <c r="W82">
-        <v>0.1415473142291267</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.9179662433345468</v>
+        <v>1.556364535924494</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,13 +8301,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1784138497557098</v>
+        <v>0.1282295778243933</v>
       </c>
       <c r="C83">
-        <v>-676.8552331269739</v>
+        <v>412.2386872554525</v>
       </c>
       <c r="D83">
-        <v>2296.422347071726</v>
+        <v>3385.516267454152</v>
       </c>
       <c r="E83">
         <v>1620.373160200304</v>
@@ -8084,45 +8334,45 @@
         <v>670.1</v>
       </c>
       <c r="M83">
-        <v>739.1080608099592</v>
+        <v>435.9365909073348</v>
       </c>
       <c r="N83">
-        <v>-69.00806080995915</v>
+        <v>234.1634090926652</v>
       </c>
       <c r="O83">
-        <v>-15.8718539862906</v>
+        <v>53.85758409131299</v>
       </c>
       <c r="P83">
-        <v>-53.13620682366854</v>
+        <v>180.3058250013522</v>
       </c>
       <c r="Q83">
-        <v>74.26379317633143</v>
+        <v>307.7058250013522</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3335878347091622</v>
+        <v>0.3274884052171925</v>
       </c>
       <c r="T83">
-        <v>4.45078173994462</v>
+        <v>4.357630041061832</v>
       </c>
       <c r="U83">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V83">
-        <v>0.208525665152539</v>
+        <v>0.23</v>
       </c>
       <c r="W83">
-        <v>0.142015013778974</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.9066333267501697</v>
+        <v>1.537150158937771</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,13 +8383,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1797501595333773</v>
+        <v>0.1284351947591455</v>
       </c>
       <c r="C84">
-        <v>-747.219610347825</v>
+        <v>354.8166752628003</v>
       </c>
       <c r="D84">
-        <v>2276.912014050858</v>
+        <v>3378.948299661483</v>
       </c>
       <c r="E84">
         <v>1671.227204400288</v>
@@ -8166,45 +8416,45 @@
         <v>670.1</v>
       </c>
       <c r="M84">
-        <v>748.2328516841562</v>
+        <v>441.3185241284131</v>
       </c>
       <c r="N84">
-        <v>-78.13285168415621</v>
+        <v>228.781475871587</v>
       </c>
       <c r="O84">
-        <v>-17.97055588735593</v>
+        <v>52.619739450465</v>
       </c>
       <c r="P84">
-        <v>-60.16229579680028</v>
+        <v>176.161736421122</v>
       </c>
       <c r="Q84">
-        <v>67.2377042031997</v>
+        <v>303.561736421122</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.34957604774856</v>
+        <v>0.3422973077623045</v>
       </c>
       <c r="T84">
-        <v>4.698047392163765</v>
+        <v>4.586719053639332</v>
       </c>
       <c r="U84">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V84">
-        <v>0.2059826692360447</v>
+        <v>0.23</v>
       </c>
       <c r="W84">
-        <v>0.1424713060227275</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8955768227654115</v>
+        <v>1.518404425292189</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,13 +8465,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1810864693110449</v>
+        <v>0.1286408116938978</v>
       </c>
       <c r="C85">
-        <v>-817.255262042363</v>
+        <v>297.4200978984954</v>
       </c>
       <c r="D85">
-        <v>2257.730406556304</v>
+        <v>3372.405766497163</v>
       </c>
       <c r="E85">
         <v>1722.081248600272</v>
@@ -8248,45 +8498,45 @@
         <v>670.1</v>
       </c>
       <c r="M85">
-        <v>757.3576425583533</v>
+        <v>446.7004573494913</v>
       </c>
       <c r="N85">
-        <v>-87.25764255835327</v>
+        <v>223.3995426505087</v>
       </c>
       <c r="O85">
-        <v>-20.06925778842125</v>
+        <v>51.38189480961702</v>
       </c>
       <c r="P85">
-        <v>-67.18838476993201</v>
+        <v>172.0176478408917</v>
       </c>
       <c r="Q85">
-        <v>60.21161523006796</v>
+        <v>299.4176478408917</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3674452270278872</v>
+        <v>0.3588484341362534</v>
       </c>
       <c r="T85">
-        <v>4.974403121114576</v>
+        <v>4.842759714755362</v>
       </c>
       <c r="U85">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V85">
-        <v>0.2035009503295863</v>
+        <v>0.23</v>
       </c>
       <c r="W85">
-        <v>0.1429166032726556</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.8847867405634186</v>
+        <v>1.500110396071801</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,13 +8547,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1824227790887125</v>
+        <v>0.1671483366274258</v>
       </c>
       <c r="C86">
-        <v>-886.9704267474999</v>
+        <v>-650.8965187800704</v>
       </c>
       <c r="D86">
-        <v>2238.869286051151</v>
+        <v>2474.943194018581</v>
       </c>
       <c r="E86">
         <v>1772.935292800256</v>
@@ -8330,37 +8580,37 @@
         <v>670.1</v>
       </c>
       <c r="M86">
-        <v>766.4824334325504</v>
+        <v>694.7172062575329</v>
       </c>
       <c r="N86">
-        <v>-96.38243343255033</v>
+        <v>-24.61720625753287</v>
       </c>
       <c r="O86">
-        <v>-22.16795968948658</v>
+        <v>-5.661957439232561</v>
       </c>
       <c r="P86">
-        <v>-74.21447374306375</v>
+        <v>-18.95524881830031</v>
       </c>
       <c r="Q86">
-        <v>53.18552625693623</v>
+        <v>108.4447511816997</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.38754805371713</v>
+        <v>0.3802827883340882</v>
       </c>
       <c r="T86">
-        <v>5.285303316184235</v>
+        <v>5.17434235725436</v>
       </c>
       <c r="U86">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V86">
-        <v>0.2010783199685198</v>
+        <v>0.2218499824270458</v>
       </c>
       <c r="W86">
-        <v>0.1433512982071092</v>
+        <v>0.1265512982071091</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8368,7 +8618,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8742535650805207</v>
+        <v>0.9645651409871555</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,13 +8629,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.18375908886638</v>
+        <v>0.1683166464050934</v>
       </c>
       <c r="C87">
-        <v>-956.37306998141</v>
+        <v>-721.5732146231298</v>
       </c>
       <c r="D87">
-        <v>2220.320687017225</v>
+        <v>2455.120542375505</v>
       </c>
       <c r="E87">
         <v>1823.78933700024</v>
@@ -8412,37 +8662,37 @@
         <v>670.1</v>
       </c>
       <c r="M87">
-        <v>775.6072243067473</v>
+        <v>702.9876491891702</v>
       </c>
       <c r="N87">
-        <v>-105.5072243067473</v>
+        <v>-32.88764918917013</v>
       </c>
       <c r="O87">
-        <v>-24.26666159055187</v>
+        <v>-7.564159313509131</v>
       </c>
       <c r="P87">
-        <v>-81.2405627161954</v>
+        <v>-25.323489875661</v>
       </c>
       <c r="Q87">
-        <v>46.15943728380458</v>
+        <v>102.076510124339</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4103312572982719</v>
+        <v>0.4025816408896941</v>
       </c>
       <c r="T87">
-        <v>5.637656870596516</v>
+        <v>5.51929851440465</v>
       </c>
       <c r="U87">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V87">
-        <v>0.1987126926747725</v>
+        <v>0.2192399826337864</v>
       </c>
       <c r="W87">
-        <v>0.1437757650254579</v>
+        <v>0.126975765025458</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8450,7 +8700,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.86396822902075</v>
+        <v>0.9532173157990714</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,13 +8711,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1850953986440476</v>
+        <v>0.169484956182761</v>
       </c>
       <c r="C88">
-        <v>-1025.470895460138</v>
+        <v>-791.9349009282428</v>
       </c>
       <c r="D88">
-        <v>2202.076905738481</v>
+        <v>2435.612900270376</v>
       </c>
       <c r="E88">
         <v>1874.643381200224</v>
@@ -8494,37 +8744,37 @@
         <v>670.1</v>
       </c>
       <c r="M88">
-        <v>784.7320151809444</v>
+        <v>711.2580921208075</v>
       </c>
       <c r="N88">
-        <v>-114.6320151809443</v>
+        <v>-41.15809212080751</v>
       </c>
       <c r="O88">
-        <v>-26.3653634916172</v>
+        <v>-9.466361187785727</v>
       </c>
       <c r="P88">
-        <v>-88.26665168932713</v>
+        <v>-31.69173093302178</v>
       </c>
       <c r="Q88">
-        <v>39.13334831067284</v>
+        <v>95.7082690669782</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4363692042481485</v>
+        <v>0.4280660438103865</v>
       </c>
       <c r="T88">
-        <v>6.040346647067697</v>
+        <v>5.913534122576411</v>
       </c>
       <c r="U88">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V88">
-        <v>0.1964020799692519</v>
+        <v>0.2166906805101377</v>
       </c>
       <c r="W88">
-        <v>0.1441903605224498</v>
+        <v>0.1273903605224498</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8532,7 +8782,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8539220868228342</v>
+        <v>0.9421333935223379</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,13 +8793,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1864317084217152</v>
+        <v>0.1706532659604285</v>
       </c>
       <c r="C89">
-        <v>-1094.271355765728</v>
+        <v>-861.9890274125405</v>
       </c>
       <c r="D89">
-        <v>2184.130489632875</v>
+        <v>2416.412817986063</v>
       </c>
       <c r="E89">
         <v>1925.497425400208</v>
@@ -8576,37 +8826,37 @@
         <v>670.1</v>
       </c>
       <c r="M89">
-        <v>793.8568060551414</v>
+        <v>719.5285350524448</v>
       </c>
       <c r="N89">
-        <v>-123.7568060551414</v>
+        <v>-49.42853505244477</v>
       </c>
       <c r="O89">
-        <v>-28.46406539268252</v>
+        <v>-11.3685630620623</v>
       </c>
       <c r="P89">
-        <v>-95.29274066245887</v>
+        <v>-38.05997199038247</v>
       </c>
       <c r="Q89">
-        <v>32.10725933754111</v>
+        <v>89.3400280096175</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4664129891903138</v>
+        <v>0.4574711241034932</v>
       </c>
       <c r="T89">
-        <v>6.504988696842135</v>
+        <v>6.368421362774597</v>
       </c>
       <c r="U89">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V89">
-        <v>0.1941445847971915</v>
+        <v>0.2141999830330097</v>
       </c>
       <c r="W89">
-        <v>0.1445954250884764</v>
+        <v>0.1277954250884763</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8614,7 +8864,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8441068904225717</v>
+        <v>0.9313042740565639</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,13 +8875,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1877680181993828</v>
+        <v>0.1718215757380961</v>
       </c>
       <c r="C90">
-        <v>-1162.781662496924</v>
+        <v>-931.7428107241858</v>
       </c>
       <c r="D90">
-        <v>2166.474227101663</v>
+        <v>2397.513078874401</v>
       </c>
       <c r="E90">
         <v>1976.351469600192</v>
@@ -8658,37 +8908,37 @@
         <v>670.1</v>
       </c>
       <c r="M90">
-        <v>802.9815969293384</v>
+        <v>727.7989779840821</v>
       </c>
       <c r="N90">
-        <v>-132.8815969293383</v>
+        <v>-57.69897798408203</v>
       </c>
       <c r="O90">
-        <v>-30.56276729374782</v>
+        <v>-13.27076493633887</v>
       </c>
       <c r="P90">
-        <v>-102.3188296355905</v>
+        <v>-44.42821304774316</v>
       </c>
       <c r="Q90">
-        <v>25.08117036440946</v>
+        <v>82.97178695225682</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.50146407162284</v>
+        <v>0.4917770511121178</v>
       </c>
       <c r="T90">
-        <v>7.047071088245648</v>
+        <v>6.899123143005815</v>
       </c>
       <c r="U90">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V90">
-        <v>0.1919383963335871</v>
+        <v>0.2117658923167255</v>
       </c>
       <c r="W90">
-        <v>0.1449912836416386</v>
+        <v>0.1281912836416386</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8696,7 +8946,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8345147666677699</v>
+        <v>0.9207212709422848</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,13 +8957,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1891043279770503</v>
+        <v>0.1729898855157637</v>
       </c>
       <c r="C91">
-        <v>-1231.008795931464</v>
+        <v>-1001.20324348627</v>
       </c>
       <c r="D91">
-        <v>2149.101137867107</v>
+        <v>2378.906690312301</v>
       </c>
       <c r="E91">
         <v>2027.205513800176</v>
@@ -8740,37 +8990,37 @@
         <v>670.1</v>
       </c>
       <c r="M91">
-        <v>812.1063878035354</v>
+        <v>736.0694209157194</v>
       </c>
       <c r="N91">
-        <v>-142.0063878035354</v>
+        <v>-65.96942091571941</v>
       </c>
       <c r="O91">
-        <v>-32.66146919481314</v>
+        <v>-15.17296681061547</v>
       </c>
       <c r="P91">
-        <v>-109.3449186087223</v>
+        <v>-50.79645410510395</v>
       </c>
       <c r="Q91">
-        <v>18.05508139127772</v>
+        <v>76.60354589489603</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5428880781340072</v>
+        <v>0.5323204193950375</v>
       </c>
       <c r="T91">
-        <v>7.687713914449796</v>
+        <v>7.526316156006343</v>
       </c>
       <c r="U91">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V91">
-        <v>0.1897817851388277</v>
+        <v>0.209386500268223</v>
       </c>
       <c r="W91">
-        <v>0.145378246496977</v>
+        <v>0.128578246496977</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8778,7 +9028,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8251381962557724</v>
+        <v>0.9103760881227085</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,13 +9039,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1904406377547179</v>
+        <v>0.1741581952934312</v>
       </c>
       <c r="C92">
-        <v>-1298.959514227186</v>
+        <v>-1070.377102922829</v>
       </c>
       <c r="D92">
-        <v>2132.004463771369</v>
+        <v>2360.586875075726</v>
       </c>
       <c r="E92">
         <v>2078.05955800016</v>
@@ -8822,37 +9072,37 @@
         <v>670.1</v>
       </c>
       <c r="M92">
-        <v>821.2311786777325</v>
+        <v>744.3398638473567</v>
       </c>
       <c r="N92">
-        <v>-151.1311786777325</v>
+        <v>-74.23986384735667</v>
       </c>
       <c r="O92">
-        <v>-34.76017109587847</v>
+        <v>-17.07516868489203</v>
       </c>
       <c r="P92">
-        <v>-116.371007581854</v>
+        <v>-57.16469516246464</v>
       </c>
       <c r="Q92">
-        <v>11.02899241814598</v>
+        <v>70.23530483753534</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.592596885947408</v>
+        <v>0.5809724613345413</v>
       </c>
       <c r="T92">
-        <v>8.456485305894777</v>
+        <v>8.278947771606978</v>
       </c>
       <c r="U92">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V92">
-        <v>0.1876730986372851</v>
+        <v>0.2070599835985761</v>
       </c>
       <c r="W92">
-        <v>0.1457566101777524</v>
+        <v>0.1289566101777524</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8860,7 +9110,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8159699940751527</v>
+        <v>0.9002607982546784</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,13 +9121,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1917769475323855</v>
+        <v>0.1753265050710988</v>
       </c>
       <c r="C93">
-        <v>-1366.640362187409</v>
+        <v>-1139.270959089339</v>
       </c>
       <c r="D93">
-        <v>2115.17766001113</v>
+        <v>2342.5470631092</v>
       </c>
       <c r="E93">
         <v>2128.913602200144</v>
@@ -8904,37 +9154,37 @@
         <v>670.1</v>
       </c>
       <c r="M93">
-        <v>830.3559695519294</v>
+        <v>752.610306778994</v>
       </c>
       <c r="N93">
-        <v>-160.2559695519294</v>
+        <v>-82.51030677899394</v>
       </c>
       <c r="O93">
-        <v>-36.85887299694377</v>
+        <v>-18.97737055916861</v>
       </c>
       <c r="P93">
-        <v>-123.3970965549856</v>
+        <v>-63.53293621982533</v>
       </c>
       <c r="Q93">
-        <v>4.00290344501434</v>
+        <v>63.86706378017465</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.65335209549712</v>
+        <v>0.6404360681494904</v>
       </c>
       <c r="T93">
-        <v>9.396094784327531</v>
+        <v>9.198830857341088</v>
       </c>
       <c r="U93">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V93">
-        <v>0.1856107568940183</v>
+        <v>0.2047845991634269</v>
       </c>
       <c r="W93">
-        <v>0.1461266581732359</v>
+        <v>0.1293266581732359</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8942,7 +9192,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8070032908435577</v>
+        <v>0.890367822449682</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,13 +9203,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2436416023937495</v>
+        <v>0.1764948148487664</v>
       </c>
       <c r="C94">
-        <v>-1913.486269614805</v>
+        <v>-1207.891182728676</v>
       </c>
       <c r="D94">
-        <v>1619.185796783718</v>
+        <v>2324.780883669847</v>
       </c>
       <c r="E94">
         <v>2179.767646400128</v>
@@ -8986,45 +9236,45 @@
         <v>670.1</v>
       </c>
       <c r="M94">
-        <v>1083.702222292129</v>
+        <v>760.8807497106313</v>
       </c>
       <c r="N94">
-        <v>-413.6022222921293</v>
+        <v>-90.78074971063131</v>
       </c>
       <c r="O94">
-        <v>-95.12851112718975</v>
+        <v>-20.8795724334452</v>
       </c>
       <c r="P94">
-        <v>-318.4737111649396</v>
+        <v>-69.90117727718611</v>
       </c>
       <c r="Q94">
-        <v>-191.0737111649396</v>
+        <v>57.49882272281387</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.760600420980465</v>
+        <v>0.7147655766681769</v>
       </c>
       <c r="T94">
-        <v>11.05474338281088</v>
+        <v>10.34868471450873</v>
       </c>
       <c r="U94">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V94">
-        <v>0.1422189572279512</v>
+        <v>0.2025586796073026</v>
       </c>
       <c r="W94">
-        <v>0.1986886616470786</v>
+        <v>0.1296886616470786</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.6183432922954399</v>
+        <v>0.8806899113360984</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,13 +9285,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2454999121714171</v>
+        <v>0.177663124626434</v>
       </c>
       <c r="C95">
-        <v>-1977.831103679861</v>
+        <v>-1276.243952772295</v>
       </c>
       <c r="D95">
-        <v>1605.695006918646</v>
+        <v>2307.282157826212</v>
       </c>
       <c r="E95">
         <v>2230.621690600112</v>
@@ -9068,45 +9318,45 @@
         <v>670.1</v>
       </c>
       <c r="M95">
-        <v>1095.481594273566</v>
+        <v>769.1511926422686</v>
       </c>
       <c r="N95">
-        <v>-425.3815942735656</v>
+        <v>-99.05119264226857</v>
       </c>
       <c r="O95">
-        <v>-97.83776668292009</v>
+        <v>-22.78177430772177</v>
       </c>
       <c r="P95">
-        <v>-327.5438275906455</v>
+        <v>-76.2694183345468</v>
       </c>
       <c r="Q95">
-        <v>-200.1438275906455</v>
+        <v>51.13058166545318</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8627147668348173</v>
+        <v>0.8103320876207738</v>
       </c>
       <c r="T95">
-        <v>12.63399243749815</v>
+        <v>11.82706824515283</v>
       </c>
       <c r="U95">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V95">
-        <v>0.1406897211287259</v>
+        <v>0.2003806292889446</v>
       </c>
       <c r="W95">
-        <v>0.1990428800999784</v>
+        <v>0.1300428800999784</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.6116944396901126</v>
+        <v>0.8712201273432372</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,13 +9367,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2473582219490846</v>
+        <v>0.1788314344041016</v>
       </c>
       <c r="C96">
-        <v>-2041.952989228755</v>
+        <v>-1344.335263505156</v>
       </c>
       <c r="D96">
-        <v>1592.427165569736</v>
+        <v>2290.044891293334</v>
       </c>
       <c r="E96">
         <v>2281.475734800096</v>
@@ -9150,45 +9400,45 @@
         <v>670.1</v>
       </c>
       <c r="M96">
-        <v>1107.260966255002</v>
+        <v>777.4216355739059</v>
       </c>
       <c r="N96">
-        <v>-437.1609662550017</v>
+        <v>-107.3216355739058</v>
       </c>
       <c r="O96">
-        <v>-100.5470222386504</v>
+        <v>-24.68397618199834</v>
       </c>
       <c r="P96">
-        <v>-336.6139440163513</v>
+        <v>-82.63765939190749</v>
       </c>
       <c r="Q96">
-        <v>-209.2139440163513</v>
+        <v>44.76234060809249</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.9988672279739536</v>
+        <v>0.9377541022242362</v>
       </c>
       <c r="T96">
-        <v>14.73965784374784</v>
+        <v>13.79824628601164</v>
       </c>
       <c r="U96">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V96">
-        <v>0.139193021967782</v>
+        <v>0.1982489204667218</v>
       </c>
       <c r="W96">
-        <v>0.1993895619900505</v>
+        <v>0.1303895619900505</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.6051870520338349</v>
+        <v>0.8619518281161815</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,13 +9449,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2492165317267522</v>
+        <v>0.1799997441817691</v>
       </c>
       <c r="C97">
-        <v>-2105.857407632867</v>
+        <v>-1412.170931411883</v>
       </c>
       <c r="D97">
-        <v>1579.376791365608</v>
+        <v>2273.063267586591</v>
       </c>
       <c r="E97">
         <v>2332.32977900008</v>
@@ -9232,45 +9482,45 @@
         <v>670.1</v>
       </c>
       <c r="M97">
-        <v>1119.040338236438</v>
+        <v>785.6920785055431</v>
       </c>
       <c r="N97">
-        <v>-448.9403382364379</v>
+        <v>-115.5920785055431</v>
       </c>
       <c r="O97">
-        <v>-103.2562777943807</v>
+        <v>-26.58617805627491</v>
       </c>
       <c r="P97">
-        <v>-345.6840604420572</v>
+        <v>-89.00590044926818</v>
       </c>
       <c r="Q97">
-        <v>-218.2840604420572</v>
+        <v>38.3940995507318</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.189480673568745</v>
+        <v>1.116144922669084</v>
       </c>
       <c r="T97">
-        <v>17.68758941249742</v>
+        <v>16.55789554321398</v>
       </c>
       <c r="U97">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V97">
-        <v>0.137727832262858</v>
+        <v>0.1961620897249668</v>
       </c>
       <c r="W97">
-        <v>0.1997289453140158</v>
+        <v>0.1307289453140158</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.598816662012426</v>
+        <v>0.8528786509781165</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,13 +9531,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2510748415044198</v>
+        <v>0.1811680539594367</v>
       </c>
       <c r="C98">
-        <v>-2169.549662038855</v>
+        <v>-1479.756601720539</v>
       </c>
       <c r="D98">
-        <v>1566.538581159604</v>
+        <v>2256.33164147792</v>
       </c>
       <c r="E98">
         <v>2383.183823200064</v>
@@ -9314,45 +9564,45 @@
         <v>670.1</v>
       </c>
       <c r="M98">
-        <v>1130.819710217874</v>
+        <v>793.9625214371805</v>
       </c>
       <c r="N98">
-        <v>-460.7197102178742</v>
+        <v>-123.8625214371805</v>
       </c>
       <c r="O98">
-        <v>-105.9655333501111</v>
+        <v>-28.48837993055151</v>
       </c>
       <c r="P98">
-        <v>-354.7541768677631</v>
+        <v>-95.37414150662897</v>
       </c>
       <c r="Q98">
-        <v>-227.3541768677632</v>
+        <v>32.025858493371</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.475400841960928</v>
+        <v>1.383731153336352</v>
       </c>
       <c r="T98">
-        <v>22.10948676562172</v>
+        <v>20.69736942901742</v>
       </c>
       <c r="U98">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V98">
-        <v>0.1362931673434532</v>
+        <v>0.1941187346236651</v>
       </c>
       <c r="W98">
-        <v>0.2000612581520652</v>
+        <v>0.1310612581520652</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5925789884497966</v>
+        <v>0.8439944983637611</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,13 +9613,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2529331512820874</v>
+        <v>0.1823363637371043</v>
       </c>
       <c r="C99">
-        <v>-2233.034884553886</v>
+        <v>-1547.097754659528</v>
       </c>
       <c r="D99">
-        <v>1553.907402844557</v>
+        <v>2239.844532738914</v>
       </c>
       <c r="E99">
         <v>2434.037867400048</v>
@@ -9396,45 +9646,45 @@
         <v>670.1</v>
       </c>
       <c r="M99">
-        <v>1142.59908219931</v>
+        <v>802.2329643688178</v>
       </c>
       <c r="N99">
-        <v>-472.4990821993102</v>
+        <v>-132.1329643688177</v>
       </c>
       <c r="O99">
-        <v>-108.6747889058414</v>
+        <v>-30.39058180482808</v>
       </c>
       <c r="P99">
-        <v>-363.8242932934689</v>
+        <v>-101.7423825639897</v>
       </c>
       <c r="Q99">
-        <v>-236.4242932934689</v>
+        <v>25.65761743601033</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.951934455947904</v>
+        <v>1.829708204448469</v>
       </c>
       <c r="T99">
-        <v>29.47931568749563</v>
+        <v>27.59649257202323</v>
       </c>
       <c r="U99">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V99">
-        <v>0.1348880831440362</v>
+        <v>0.1921175105553798</v>
       </c>
       <c r="W99">
-        <v>0.2003867191790208</v>
+        <v>0.1313867191790208</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.5864699267132008</v>
+        <v>0.8352935241538254</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,13 +9695,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2547914610597549</v>
+        <v>0.1835046735147719</v>
       </c>
       <c r="C100">
-        <v>-2296.31804308603</v>
+        <v>-1614.199711442163</v>
       </c>
       <c r="D100">
-        <v>1541.478288512396</v>
+        <v>2223.596620156263</v>
       </c>
       <c r="E100">
         <v>2484.891911600032</v>
@@ -9478,45 +9728,45 @@
         <v>670.1</v>
       </c>
       <c r="M100">
-        <v>1154.378454180747</v>
+        <v>810.503407300455</v>
       </c>
       <c r="N100">
-        <v>-484.2784541807465</v>
+        <v>-140.403407300455</v>
       </c>
       <c r="O100">
-        <v>-111.3840444615717</v>
+        <v>-32.29278367910465</v>
       </c>
       <c r="P100">
-        <v>-372.8944097191748</v>
+        <v>-108.1106236213504</v>
       </c>
       <c r="Q100">
-        <v>-245.4944097191748</v>
+        <v>19.28937637864962</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.905001683921856</v>
+        <v>2.721662306672704</v>
       </c>
       <c r="T100">
-        <v>44.21897353124345</v>
+        <v>41.39473885803485</v>
       </c>
       <c r="U100">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V100">
-        <v>0.1335116741323623</v>
+        <v>0.1901571277946107</v>
       </c>
       <c r="W100">
-        <v>0.2007055381442018</v>
+        <v>0.1317055381442018</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5804855397059232</v>
+        <v>0.8267701208461333</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9527,13 +9777,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2566497708374225</v>
+        <v>0.1846729832924394</v>
       </c>
       <c r="C101">
-        <v>-2359.403947858988</v>
+        <v>-1681.06763999263</v>
       </c>
       <c r="D101">
-        <v>1529.246427939422</v>
+        <v>2207.582735805781</v>
       </c>
       <c r="E101">
         <v>2535.745955800016</v>
@@ -9560,45 +9810,45 @@
         <v>670.1</v>
       </c>
       <c r="M101">
-        <v>1166.157826162183</v>
+        <v>818.7738502320924</v>
       </c>
       <c r="N101">
-        <v>-496.0578261621828</v>
+        <v>-148.6738502320924</v>
       </c>
       <c r="O101">
-        <v>-114.093300017302</v>
+        <v>-34.19498555338125</v>
       </c>
       <c r="P101">
-        <v>-381.9645261448807</v>
+        <v>-114.4788646787111</v>
       </c>
       <c r="Q101">
-        <v>-254.5645261448807</v>
+        <v>12.92113532128886</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.764203367843712</v>
+        <v>5.397524613345408</v>
       </c>
       <c r="T101">
-        <v>88.4379470624869</v>
+        <v>82.7894777160697</v>
       </c>
       <c r="U101">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V101">
-        <v>0.1321630713633486</v>
+        <v>0.1882363487259782</v>
       </c>
       <c r="W101">
-        <v>0.2010179163222074</v>
+        <v>0.1320179163222074</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.5746220494058634</v>
+        <v>0.8184189075042532</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/israel/israel_entertainment.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_entertainment.xlsx
@@ -1519,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1656,22 +1656,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1115746061094587</v>
+        <v>0.111474533044211</v>
       </c>
       <c r="C2">
-        <v>5164.064326869958</v>
+        <v>5117.727033998523</v>
       </c>
       <c r="D2">
-        <v>4018.164326869958</v>
+        <v>4022.681078198508</v>
       </c>
       <c r="E2">
-        <v>-2498.804419998395</v>
+        <v>-2447.950375798411</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>50.85404419998395</v>
       </c>
       <c r="G2">
         <v>1145.9</v>
@@ -1692,28 +1692,28 @@
         <v>670.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.363027666338846</v>
       </c>
       <c r="N2">
-        <v>670.1</v>
+        <v>666.7369723336611</v>
       </c>
       <c r="O2">
-        <v>154.123</v>
+        <v>153.3495036367421</v>
       </c>
       <c r="P2">
-        <v>515.977</v>
+        <v>513.3874686969191</v>
       </c>
       <c r="Q2">
-        <v>643.377</v>
+        <v>640.7874686969191</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1115746061094587</v>
+        <v>0.112086186379199</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.025426221752742</v>
       </c>
       <c r="U2">
         <v>0.06613097776675758</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>199.2549769087993</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1738,22 +1738,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.111474533044211</v>
+        <v>0.1113744599789633</v>
       </c>
       <c r="C3">
-        <v>5117.727033998523</v>
+        <v>5071.399906963617</v>
       </c>
       <c r="D3">
-        <v>4022.681078198508</v>
+        <v>4027.207995363585</v>
       </c>
       <c r="E3">
-        <v>-2447.950375798411</v>
+        <v>-2397.096331598427</v>
       </c>
       <c r="F3">
-        <v>50.85404419998395</v>
+        <v>101.7080883999679</v>
       </c>
       <c r="G3">
         <v>1145.9</v>
@@ -1774,28 +1774,28 @@
         <v>670.1</v>
       </c>
       <c r="M3">
-        <v>3.363027666338846</v>
+        <v>6.726055332677691</v>
       </c>
       <c r="N3">
-        <v>666.7369723336611</v>
+        <v>663.3739446673223</v>
       </c>
       <c r="O3">
-        <v>153.3495036367421</v>
+        <v>152.5760072734842</v>
       </c>
       <c r="P3">
-        <v>513.3874686969191</v>
+        <v>510.7979373938382</v>
       </c>
       <c r="Q3">
-        <v>640.7874686969191</v>
+        <v>638.1979373938382</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.112086186379199</v>
+        <v>0.1126082070626074</v>
       </c>
       <c r="T3">
-        <v>1.025426221752742</v>
+        <v>1.033501715702598</v>
       </c>
       <c r="U3">
         <v>0.06613097776675758</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>199.2549769087993</v>
+        <v>99.62748845439967</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1820,22 +1820,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1113744599789633</v>
+        <v>0.1112743869137155</v>
       </c>
       <c r="C4">
-        <v>5071.399906963617</v>
+        <v>5025.082980124222</v>
       </c>
       <c r="D4">
-        <v>4027.207995363585</v>
+        <v>4031.745112724173</v>
       </c>
       <c r="E4">
-        <v>-2397.096331598427</v>
+        <v>-2346.242287398443</v>
       </c>
       <c r="F4">
-        <v>101.7080883999679</v>
+        <v>152.5621325999518</v>
       </c>
       <c r="G4">
         <v>1145.9</v>
@@ -1856,28 +1856,28 @@
         <v>670.1</v>
       </c>
       <c r="M4">
-        <v>6.726055332677691</v>
+        <v>10.08908299901654</v>
       </c>
       <c r="N4">
-        <v>663.3739446673223</v>
+        <v>660.0109170009835</v>
       </c>
       <c r="O4">
-        <v>152.5760072734842</v>
+        <v>151.8025109102262</v>
       </c>
       <c r="P4">
-        <v>510.7979373938382</v>
+        <v>508.2084060907573</v>
       </c>
       <c r="Q4">
-        <v>638.1979373938382</v>
+        <v>635.6084060907572</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1126082070626074</v>
+        <v>0.1131409910590757</v>
       </c>
       <c r="T4">
-        <v>1.033501715702598</v>
+        <v>1.041743714682348</v>
       </c>
       <c r="U4">
         <v>0.06613097776675758</v>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>99.62748845439967</v>
+        <v>66.41832563626645</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1902,22 +1902,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1112743869137155</v>
+        <v>0.1111743138484678</v>
       </c>
       <c r="C5">
-        <v>5025.082980124222</v>
+        <v>4978.776287994335</v>
       </c>
       <c r="D5">
-        <v>4031.745112724173</v>
+        <v>4036.292464794271</v>
       </c>
       <c r="E5">
-        <v>-2346.242287398443</v>
+        <v>-2295.388243198459</v>
       </c>
       <c r="F5">
-        <v>152.5621325999518</v>
+        <v>203.4161767999358</v>
       </c>
       <c r="G5">
         <v>1145.9</v>
@@ -1938,28 +1938,28 @@
         <v>670.1</v>
       </c>
       <c r="M5">
-        <v>10.08908299901654</v>
+        <v>13.45211066535538</v>
       </c>
       <c r="N5">
-        <v>660.0109170009835</v>
+        <v>656.6478893346447</v>
       </c>
       <c r="O5">
-        <v>151.8025109102262</v>
+        <v>151.0290145469683</v>
       </c>
       <c r="P5">
-        <v>508.2084060907573</v>
+        <v>505.6188747876764</v>
       </c>
       <c r="Q5">
-        <v>635.6084060907572</v>
+        <v>633.0188747876764</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1131409910590757</v>
+        <v>0.1136848747221372</v>
       </c>
       <c r="T5">
-        <v>1.041743714682348</v>
+        <v>1.050157421974176</v>
       </c>
       <c r="U5">
         <v>0.06613097776675758</v>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.41832563626645</v>
+        <v>49.81374422719984</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1984,22 +1984,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1111743138484678</v>
+        <v>0.1110742407832201</v>
       </c>
       <c r="C6">
-        <v>4978.776287994335</v>
+        <v>4932.479865243842</v>
       </c>
       <c r="D6">
-        <v>4036.292464794271</v>
+        <v>4040.850086243762</v>
       </c>
       <c r="E6">
-        <v>-2295.388243198459</v>
+        <v>-2244.534198998475</v>
       </c>
       <c r="F6">
-        <v>203.4161767999358</v>
+        <v>254.2702209999197</v>
       </c>
       <c r="G6">
         <v>1145.9</v>
@@ -2020,28 +2020,28 @@
         <v>670.1</v>
       </c>
       <c r="M6">
-        <v>13.45211066535538</v>
+        <v>16.81513833169423</v>
       </c>
       <c r="N6">
-        <v>656.6478893346447</v>
+        <v>653.2848616683058</v>
       </c>
       <c r="O6">
-        <v>151.0290145469683</v>
+        <v>150.2555181837103</v>
       </c>
       <c r="P6">
-        <v>505.6188747876764</v>
+        <v>503.0293434845954</v>
       </c>
       <c r="Q6">
-        <v>633.0188747876764</v>
+        <v>630.4293434845954</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1136848747221372</v>
+        <v>0.1142402085675789</v>
       </c>
       <c r="T6">
-        <v>1.050157421974176</v>
+        <v>1.058748259945833</v>
       </c>
       <c r="U6">
         <v>0.06613097776675758</v>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.81374422719984</v>
+        <v>39.85099538175987</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2066,22 +2066,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1110742407832201</v>
+        <v>0.1109741677179724</v>
       </c>
       <c r="C7">
-        <v>4932.479865243842</v>
+        <v>4886.193746699397</v>
       </c>
       <c r="D7">
-        <v>4040.850086243762</v>
+        <v>4045.4180118993</v>
       </c>
       <c r="E7">
-        <v>-2244.534198998475</v>
+        <v>-2193.680154798491</v>
       </c>
       <c r="F7">
-        <v>254.2702209999197</v>
+        <v>305.1242651999037</v>
       </c>
       <c r="G7">
         <v>1145.9</v>
@@ -2102,28 +2102,28 @@
         <v>670.1</v>
       </c>
       <c r="M7">
-        <v>16.81513833169423</v>
+        <v>20.17816599803307</v>
       </c>
       <c r="N7">
-        <v>653.2848616683058</v>
+        <v>649.921834001967</v>
       </c>
       <c r="O7">
-        <v>150.2555181837103</v>
+        <v>149.4820218204524</v>
       </c>
       <c r="P7">
-        <v>503.0293434845954</v>
+        <v>500.4398121815146</v>
       </c>
       <c r="Q7">
-        <v>630.4293434845954</v>
+        <v>627.8398121815146</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1142402085675789</v>
+        <v>0.1148073580267534</v>
       </c>
       <c r="T7">
-        <v>1.058748259945833</v>
+        <v>1.06752188170412</v>
       </c>
       <c r="U7">
         <v>0.06613097776675758</v>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.85099538175987</v>
+        <v>33.20916281813323</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2148,22 +2148,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1109741677179724</v>
+        <v>0.1108740946527246</v>
       </c>
       <c r="C8">
-        <v>4886.193746699398</v>
+        <v>4839.917967345309</v>
       </c>
       <c r="D8">
-        <v>4045.418011899301</v>
+        <v>4049.996276745197</v>
       </c>
       <c r="E8">
-        <v>-2193.680154798491</v>
+        <v>-2142.826110598508</v>
       </c>
       <c r="F8">
-        <v>305.1242651999037</v>
+        <v>355.9783093998876</v>
       </c>
       <c r="G8">
         <v>1145.9</v>
@@ -2184,28 +2184,28 @@
         <v>670.1</v>
       </c>
       <c r="M8">
-        <v>20.17816599803307</v>
+        <v>23.54119366437192</v>
       </c>
       <c r="N8">
-        <v>649.921834001967</v>
+        <v>646.5588063356281</v>
       </c>
       <c r="O8">
-        <v>149.4820218204524</v>
+        <v>148.7085254571945</v>
       </c>
       <c r="P8">
-        <v>500.4398121815146</v>
+        <v>497.8502808784336</v>
       </c>
       <c r="Q8">
-        <v>627.8398121815146</v>
+        <v>625.2502808784336</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1148073580267534</v>
+        <v>0.1153867042484908</v>
       </c>
       <c r="T8">
-        <v>1.06752188170412</v>
+        <v>1.076484183500219</v>
       </c>
       <c r="U8">
         <v>0.06613097776675758</v>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.20916281813323</v>
+        <v>28.46499670125705</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2230,22 +2230,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1108740946527246</v>
+        <v>0.1107740215874769</v>
       </c>
       <c r="C9">
-        <v>4839.91796734531</v>
+        <v>4793.652562324432</v>
       </c>
       <c r="D9">
-        <v>4049.996276745197</v>
+        <v>4054.584915924303</v>
       </c>
       <c r="E9">
-        <v>-2142.826110598508</v>
+        <v>-2091.972066398524</v>
       </c>
       <c r="F9">
-        <v>355.9783093998877</v>
+        <v>406.8323535998716</v>
       </c>
       <c r="G9">
         <v>1145.9</v>
@@ -2266,28 +2266,28 @@
         <v>670.1</v>
       </c>
       <c r="M9">
-        <v>23.54119366437192</v>
+        <v>26.90422133071077</v>
       </c>
       <c r="N9">
-        <v>646.5588063356281</v>
+        <v>643.1957786692892</v>
       </c>
       <c r="O9">
-        <v>148.7085254571945</v>
+        <v>147.9350290939365</v>
       </c>
       <c r="P9">
-        <v>497.8502808784336</v>
+        <v>495.2607495753527</v>
       </c>
       <c r="Q9">
-        <v>625.2502808784336</v>
+        <v>622.6607495753526</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1153867042484908</v>
+        <v>0.1159786449533094</v>
       </c>
       <c r="T9">
-        <v>1.076484183500219</v>
+        <v>1.085641317944061</v>
       </c>
       <c r="U9">
         <v>0.06613097776675758</v>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.46499670125704</v>
+        <v>24.90687211359992</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2312,22 +2312,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1107740215874769</v>
+        <v>0.1106739485222292</v>
       </c>
       <c r="C10">
-        <v>4793.652562324432</v>
+        <v>4747.397566939076</v>
       </c>
       <c r="D10">
-        <v>4054.584915924303</v>
+        <v>4059.183964738931</v>
       </c>
       <c r="E10">
-        <v>-2091.972066398524</v>
+        <v>-2041.11802219854</v>
       </c>
       <c r="F10">
-        <v>406.8323535998716</v>
+        <v>457.6863977998555</v>
       </c>
       <c r="G10">
         <v>1145.9</v>
@@ -2348,28 +2348,28 @@
         <v>670.1</v>
       </c>
       <c r="M10">
-        <v>26.90422133071077</v>
+        <v>30.26724899704961</v>
       </c>
       <c r="N10">
-        <v>643.1957786692892</v>
+        <v>639.8327510029504</v>
       </c>
       <c r="O10">
-        <v>147.9350290939365</v>
+        <v>147.1615327306786</v>
       </c>
       <c r="P10">
-        <v>495.2607495753527</v>
+        <v>492.6712182722719</v>
       </c>
       <c r="Q10">
-        <v>622.6607495753526</v>
+        <v>620.0712182722718</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1159786449533094</v>
+        <v>0.1165835953439483</v>
       </c>
       <c r="T10">
-        <v>1.085641317944061</v>
+        <v>1.094999708089964</v>
       </c>
       <c r="U10">
         <v>0.06613097776675758</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.90687211359992</v>
+        <v>22.13944187875548</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2394,22 +2394,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1106739485222292</v>
+        <v>0.1105738754569815</v>
       </c>
       <c r="C11">
-        <v>4747.397566939076</v>
+        <v>4701.153016651895</v>
       </c>
       <c r="D11">
-        <v>4059.183964738931</v>
+        <v>4063.793458651734</v>
       </c>
       <c r="E11">
-        <v>-2041.11802219854</v>
+        <v>-1990.263977998556</v>
       </c>
       <c r="F11">
-        <v>457.6863977998555</v>
+        <v>508.5404419998394</v>
       </c>
       <c r="G11">
         <v>1145.9</v>
@@ -2430,28 +2430,28 @@
         <v>670.1</v>
       </c>
       <c r="M11">
-        <v>30.26724899704961</v>
+        <v>33.63027666338845</v>
       </c>
       <c r="N11">
-        <v>639.8327510029504</v>
+        <v>636.4697233366115</v>
       </c>
       <c r="O11">
-        <v>147.1615327306786</v>
+        <v>146.3880363674207</v>
       </c>
       <c r="P11">
-        <v>492.6712182722719</v>
+        <v>490.0816869691909</v>
       </c>
       <c r="Q11">
-        <v>620.0712182722718</v>
+        <v>617.4816869691908</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1165835953439483</v>
+        <v>0.1172019890766013</v>
       </c>
       <c r="T11">
-        <v>1.094999708089964</v>
+        <v>1.104566062461333</v>
       </c>
       <c r="U11">
         <v>0.06613097776675758</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.13944187875548</v>
+        <v>19.92549769087994</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2476,22 +2476,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1105738754569815</v>
+        <v>0.1104738023917338</v>
       </c>
       <c r="C12">
-        <v>4701.153016651895</v>
+        <v>4654.918947086818</v>
       </c>
       <c r="D12">
-        <v>4063.793458651734</v>
+        <v>4068.413433286642</v>
       </c>
       <c r="E12">
-        <v>-1990.263977998556</v>
+        <v>-1939.409933798572</v>
       </c>
       <c r="F12">
-        <v>508.5404419998395</v>
+        <v>559.3944861998234</v>
       </c>
       <c r="G12">
         <v>1145.9</v>
@@ -2512,28 +2512,28 @@
         <v>670.1</v>
       </c>
       <c r="M12">
-        <v>33.63027666338846</v>
+        <v>36.9933043297273</v>
       </c>
       <c r="N12">
-        <v>636.4697233366115</v>
+        <v>633.1066956702728</v>
       </c>
       <c r="O12">
-        <v>146.3880363674207</v>
+        <v>145.6145400041627</v>
       </c>
       <c r="P12">
-        <v>490.0816869691909</v>
+        <v>487.49215566611</v>
       </c>
       <c r="Q12">
-        <v>617.4816869691908</v>
+        <v>614.8921556661101</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1172019890766013</v>
+        <v>0.1178342792976285</v>
       </c>
       <c r="T12">
-        <v>1.104566062461333</v>
+        <v>1.114347391088237</v>
       </c>
       <c r="U12">
         <v>0.06613097776675758</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.92549769087993</v>
+        <v>18.11408880989085</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2558,22 +2558,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1104738023917338</v>
+        <v>0.1103737293264861</v>
       </c>
       <c r="C13">
-        <v>4654.918947086818</v>
+        <v>4608.695394029944</v>
       </c>
       <c r="D13">
-        <v>4068.413433286642</v>
+        <v>4073.043924429751</v>
       </c>
       <c r="E13">
-        <v>-1939.409933798572</v>
+        <v>-1888.555889598588</v>
       </c>
       <c r="F13">
-        <v>559.3944861998234</v>
+        <v>610.2485303998074</v>
       </c>
       <c r="G13">
         <v>1145.9</v>
@@ -2594,28 +2594,28 @@
         <v>670.1</v>
       </c>
       <c r="M13">
-        <v>36.9933043297273</v>
+        <v>40.35633199606615</v>
       </c>
       <c r="N13">
-        <v>633.1066956702728</v>
+        <v>629.7436680039339</v>
       </c>
       <c r="O13">
-        <v>145.6145400041627</v>
+        <v>144.8410436409048</v>
       </c>
       <c r="P13">
-        <v>487.49215566611</v>
+        <v>484.9026243630291</v>
       </c>
       <c r="Q13">
-        <v>614.8921556661101</v>
+        <v>612.3026243630291</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1178342792976285</v>
+        <v>0.1184809397509519</v>
       </c>
       <c r="T13">
-        <v>1.114347391088237</v>
+        <v>1.12435102263848</v>
       </c>
       <c r="U13">
         <v>0.06613097776675758</v>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.11408880989085</v>
+        <v>16.60458140906661</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2640,22 +2640,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1103737293264861</v>
+        <v>0.1102736562612383</v>
       </c>
       <c r="C14">
-        <v>4608.695394029944</v>
+        <v>4562.48239343049</v>
       </c>
       <c r="D14">
-        <v>4073.043924429751</v>
+        <v>4077.684968030282</v>
       </c>
       <c r="E14">
-        <v>-1888.555889598588</v>
+        <v>-1837.701845398604</v>
       </c>
       <c r="F14">
-        <v>610.2485303998074</v>
+        <v>661.1025745997913</v>
       </c>
       <c r="G14">
         <v>1145.9</v>
@@ -2676,28 +2676,28 @@
         <v>670.1</v>
       </c>
       <c r="M14">
-        <v>40.35633199606615</v>
+        <v>43.71935966240499</v>
       </c>
       <c r="N14">
-        <v>629.7436680039339</v>
+        <v>626.3806403375951</v>
       </c>
       <c r="O14">
-        <v>144.8410436409048</v>
+        <v>144.0675472776469</v>
       </c>
       <c r="P14">
-        <v>484.9026243630291</v>
+        <v>482.3130930599482</v>
       </c>
       <c r="Q14">
-        <v>612.3026243630291</v>
+        <v>609.7130930599482</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1184809397509519</v>
+        <v>0.1191424659618228</v>
       </c>
       <c r="T14">
-        <v>1.12435102263848</v>
+        <v>1.134584622730108</v>
       </c>
       <c r="U14">
         <v>0.06613097776675758</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.60458140906661</v>
+        <v>15.32730591606149</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2722,22 +2722,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1102736562612383</v>
+        <v>0.1101735831959906</v>
       </c>
       <c r="C15">
-        <v>4562.48239343049</v>
+        <v>4516.279981401702</v>
       </c>
       <c r="D15">
-        <v>4077.684968030282</v>
+        <v>4082.336600201476</v>
       </c>
       <c r="E15">
-        <v>-1837.701845398604</v>
+        <v>-1786.84780119862</v>
       </c>
       <c r="F15">
-        <v>661.1025745997913</v>
+        <v>711.9566187997754</v>
       </c>
       <c r="G15">
         <v>1145.9</v>
@@ -2758,28 +2758,28 @@
         <v>670.1</v>
       </c>
       <c r="M15">
-        <v>43.71935966240499</v>
+        <v>47.08238732874385</v>
       </c>
       <c r="N15">
-        <v>626.3806403375951</v>
+        <v>623.0176126712562</v>
       </c>
       <c r="O15">
-        <v>144.0675472776469</v>
+        <v>143.2940509143889</v>
       </c>
       <c r="P15">
-        <v>482.3130930599482</v>
+        <v>479.7235617568673</v>
       </c>
       <c r="Q15">
-        <v>609.7130930599482</v>
+        <v>607.1235617568673</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1191424659618228</v>
+        <v>0.1198193765031792</v>
       </c>
       <c r="T15">
-        <v>1.134584622730108</v>
+        <v>1.145056213521542</v>
       </c>
       <c r="U15">
         <v>0.06613097776675758</v>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.32730591606149</v>
+        <v>14.23249835062852</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2804,22 +2804,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1101735831959906</v>
+        <v>0.1100735101307429</v>
       </c>
       <c r="C16">
-        <v>4516.279981401702</v>
+        <v>4470.088194221801</v>
       </c>
       <c r="D16">
-        <v>4082.336600201476</v>
+        <v>4086.99885722156</v>
       </c>
       <c r="E16">
-        <v>-1786.84780119862</v>
+        <v>-1735.993756998636</v>
       </c>
       <c r="F16">
-        <v>711.9566187997754</v>
+        <v>762.8106629997593</v>
       </c>
       <c r="G16">
         <v>1145.9</v>
@@ -2840,28 +2840,28 @@
         <v>670.1</v>
       </c>
       <c r="M16">
-        <v>47.08238732874385</v>
+        <v>50.44541499508269</v>
       </c>
       <c r="N16">
-        <v>623.0176126712562</v>
+        <v>619.6545850049173</v>
       </c>
       <c r="O16">
-        <v>143.2940509143889</v>
+        <v>142.520554551131</v>
       </c>
       <c r="P16">
-        <v>479.7235617568673</v>
+        <v>477.1340304537863</v>
       </c>
       <c r="Q16">
-        <v>607.1235617568673</v>
+        <v>604.5340304537863</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1198193765031792</v>
+        <v>0.1205122143513911</v>
       </c>
       <c r="T16">
-        <v>1.145056213521542</v>
+        <v>1.155774194684539</v>
       </c>
       <c r="U16">
         <v>0.06613097776675758</v>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.23249835062852</v>
+        <v>13.28366512725329</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2886,22 +2886,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1100735101307429</v>
+        <v>0.1101582370654952</v>
       </c>
       <c r="C17">
-        <v>4470.088194221801</v>
+        <v>4415.286156028369</v>
       </c>
       <c r="D17">
-        <v>4086.99885722156</v>
+        <v>4083.050863228112</v>
       </c>
       <c r="E17">
-        <v>-1735.993756998636</v>
+        <v>-1685.139712798652</v>
       </c>
       <c r="F17">
-        <v>762.8106629997592</v>
+        <v>813.6647071997431</v>
       </c>
       <c r="G17">
         <v>1145.9</v>
@@ -2922,45 +2922,45 @@
         <v>670.1</v>
       </c>
       <c r="M17">
-        <v>50.44541499508269</v>
+        <v>55.02893972222115</v>
       </c>
       <c r="N17">
-        <v>619.6545850049173</v>
+        <v>615.0710602777789</v>
       </c>
       <c r="O17">
-        <v>142.520554551131</v>
+        <v>141.4663438638891</v>
       </c>
       <c r="P17">
-        <v>477.1340304537863</v>
+        <v>473.6047164138897</v>
       </c>
       <c r="Q17">
-        <v>604.5340304537863</v>
+        <v>601.0047164138897</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1205122143513911</v>
+        <v>0.121221548338846</v>
       </c>
       <c r="T17">
-        <v>1.155774194684539</v>
+        <v>1.166747365875225</v>
       </c>
       <c r="U17">
-        <v>0.06613097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V17">
         <v>0.23</v>
       </c>
       <c r="W17">
-        <v>0.05092085288040334</v>
+        <v>0.05207585288040334</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.28366512725329</v>
+        <v>12.1772289886481</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2968,22 +2968,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1101582370654952</v>
+        <v>0.1100697140002474</v>
       </c>
       <c r="C18">
-        <v>4415.286156028369</v>
+        <v>4368.557171612482</v>
       </c>
       <c r="D18">
-        <v>4083.050863228112</v>
+        <v>4087.175923012209</v>
       </c>
       <c r="E18">
-        <v>-1685.139712798652</v>
+        <v>-1634.285668598668</v>
       </c>
       <c r="F18">
-        <v>813.6647071997431</v>
+        <v>864.5187513997272</v>
       </c>
       <c r="G18">
         <v>1145.9</v>
@@ -3004,28 +3004,28 @@
         <v>670.1</v>
       </c>
       <c r="M18">
-        <v>55.02893972222115</v>
+        <v>58.46824845485997</v>
       </c>
       <c r="N18">
-        <v>615.0710602777789</v>
+        <v>611.6317515451401</v>
       </c>
       <c r="O18">
-        <v>141.4663438638891</v>
+        <v>140.6753028553822</v>
       </c>
       <c r="P18">
-        <v>473.6047164138897</v>
+        <v>470.9564486897578</v>
       </c>
       <c r="Q18">
-        <v>601.0047164138897</v>
+        <v>598.3564486897578</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.121221548338846</v>
+        <v>0.1219479747115408</v>
       </c>
       <c r="T18">
-        <v>1.166747365875225</v>
+        <v>1.177984950829543</v>
       </c>
       <c r="U18">
         <v>0.06763097776675758</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.1772289886481</v>
+        <v>11.46092140108056</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3050,22 +3050,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1100697140002474</v>
+        <v>0.1099811909349997</v>
       </c>
       <c r="C19">
-        <v>4368.557171612482</v>
+        <v>4321.836530627707</v>
       </c>
       <c r="D19">
-        <v>4087.175923012209</v>
+        <v>4091.309326227418</v>
       </c>
       <c r="E19">
-        <v>-1634.285668598668</v>
+        <v>-1583.431624398684</v>
       </c>
       <c r="F19">
-        <v>864.5187513997272</v>
+        <v>915.3727955997111</v>
       </c>
       <c r="G19">
         <v>1145.9</v>
@@ -3086,28 +3086,28 @@
         <v>670.1</v>
       </c>
       <c r="M19">
-        <v>58.46824845485997</v>
+        <v>61.9075571874988</v>
       </c>
       <c r="N19">
-        <v>611.6317515451401</v>
+        <v>608.1924428125012</v>
       </c>
       <c r="O19">
-        <v>140.6753028553822</v>
+        <v>139.8842618468753</v>
       </c>
       <c r="P19">
-        <v>470.9564486897578</v>
+        <v>468.3081809656259</v>
       </c>
       <c r="Q19">
-        <v>598.3564486897578</v>
+        <v>595.7081809656258</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1219479747115408</v>
+        <v>0.1226921188006428</v>
       </c>
       <c r="T19">
-        <v>1.177984950829543</v>
+        <v>1.189496623221771</v>
       </c>
       <c r="U19">
         <v>0.06763097776675758</v>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.46092140108056</v>
+        <v>10.82420354546497</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3132,22 +3132,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1099811909349997</v>
+        <v>0.109892667869752</v>
       </c>
       <c r="C20">
-        <v>4321.836530627706</v>
+        <v>4275.124258413062</v>
       </c>
       <c r="D20">
-        <v>4091.309326227418</v>
+        <v>4095.451098212757</v>
       </c>
       <c r="E20">
-        <v>-1583.431624398684</v>
+        <v>-1532.5775801987</v>
       </c>
       <c r="F20">
-        <v>915.372795599711</v>
+        <v>966.226839799695</v>
       </c>
       <c r="G20">
         <v>1145.9</v>
@@ -3168,28 +3168,28 @@
         <v>670.1</v>
       </c>
       <c r="M20">
-        <v>61.90755718749879</v>
+        <v>65.34686592013762</v>
       </c>
       <c r="N20">
-        <v>608.1924428125012</v>
+        <v>604.7531340798624</v>
       </c>
       <c r="O20">
-        <v>139.8842618468753</v>
+        <v>139.0932208383684</v>
       </c>
       <c r="P20">
-        <v>468.3081809656259</v>
+        <v>465.6599132414941</v>
       </c>
       <c r="Q20">
-        <v>595.7081809656258</v>
+        <v>593.0599132414941</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1226921188006428</v>
+        <v>0.1234546368178708</v>
       </c>
       <c r="T20">
-        <v>1.189496623221771</v>
+        <v>1.201292534438499</v>
       </c>
       <c r="U20">
         <v>0.06763097776675758</v>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.82420354546497</v>
+        <v>10.25450862201945</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3214,22 +3214,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.109892667869752</v>
+        <v>0.1098041448045043</v>
       </c>
       <c r="C21">
-        <v>4275.124258413062</v>
+        <v>4228.420380410274</v>
       </c>
       <c r="D21">
-        <v>4095.451098212757</v>
+        <v>4099.601264409954</v>
       </c>
       <c r="E21">
-        <v>-1532.5775801987</v>
+        <v>-1481.723535998716</v>
       </c>
       <c r="F21">
-        <v>966.226839799695</v>
+        <v>1017.080883999679</v>
       </c>
       <c r="G21">
         <v>1145.9</v>
@@ -3250,28 +3250,28 @@
         <v>670.1</v>
       </c>
       <c r="M21">
-        <v>65.34686592013762</v>
+        <v>68.78617465277644</v>
       </c>
       <c r="N21">
-        <v>604.7531340798624</v>
+        <v>601.3138253472235</v>
       </c>
       <c r="O21">
-        <v>139.0932208383684</v>
+        <v>138.3021798298614</v>
       </c>
       <c r="P21">
-        <v>465.6599132414941</v>
+        <v>463.0116455173621</v>
       </c>
       <c r="Q21">
-        <v>593.0599132414941</v>
+        <v>590.4116455173621</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1234546368178708</v>
+        <v>0.1242362177855295</v>
       </c>
       <c r="T21">
-        <v>1.201292534438499</v>
+        <v>1.213383343435645</v>
       </c>
       <c r="U21">
         <v>0.06763097776675758</v>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.25450862201945</v>
+        <v>9.741783190918476</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3296,22 +3296,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1098041448045043</v>
+        <v>0.1099905117392566</v>
       </c>
       <c r="C22">
-        <v>4228.420380410274</v>
+        <v>4168.838788411072</v>
       </c>
       <c r="D22">
-        <v>4099.601264409954</v>
+        <v>4090.873716610734</v>
       </c>
       <c r="E22">
-        <v>-1481.723535998716</v>
+        <v>-1430.869491798732</v>
       </c>
       <c r="F22">
-        <v>1017.080883999679</v>
+        <v>1067.934928199663</v>
       </c>
       <c r="G22">
         <v>1145.9</v>
@@ -3332,45 +3332,45 @@
         <v>670.1</v>
       </c>
       <c r="M22">
-        <v>68.78617465277644</v>
+        <v>74.04097276335467</v>
       </c>
       <c r="N22">
-        <v>601.3138253472235</v>
+        <v>596.0590272366453</v>
       </c>
       <c r="O22">
-        <v>138.3021798298614</v>
+        <v>137.0935762644284</v>
       </c>
       <c r="P22">
-        <v>463.0116455173621</v>
+        <v>458.9654509722169</v>
       </c>
       <c r="Q22">
-        <v>590.4116455173621</v>
+        <v>586.3654509722169</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1242362177855295</v>
+        <v>0.1250375856131289</v>
       </c>
       <c r="T22">
-        <v>1.213383343435645</v>
+        <v>1.225780248863098</v>
       </c>
       <c r="U22">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V22">
         <v>0.23</v>
       </c>
       <c r="W22">
-        <v>0.05207585288040334</v>
+        <v>0.05338485288040334</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.741783190918476</v>
+        <v>9.050394328849967</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3378,22 +3378,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1099905117392566</v>
+        <v>0.1099150786740088</v>
       </c>
       <c r="C23">
-        <v>4168.838788411072</v>
+        <v>4121.512787996811</v>
       </c>
       <c r="D23">
-        <v>4090.873716610734</v>
+        <v>4094.401760396458</v>
       </c>
       <c r="E23">
-        <v>-1430.869491798732</v>
+        <v>-1380.015447598748</v>
       </c>
       <c r="F23">
-        <v>1067.934928199663</v>
+        <v>1118.788972399647</v>
       </c>
       <c r="G23">
         <v>1145.9</v>
@@ -3414,28 +3414,28 @@
         <v>670.1</v>
       </c>
       <c r="M23">
-        <v>74.04097276335467</v>
+        <v>77.56673337113347</v>
       </c>
       <c r="N23">
-        <v>596.0590272366453</v>
+        <v>592.5332666288666</v>
       </c>
       <c r="O23">
-        <v>137.0935762644284</v>
+        <v>136.2826513246393</v>
       </c>
       <c r="P23">
-        <v>458.9654509722169</v>
+        <v>456.2506153042273</v>
       </c>
       <c r="Q23">
-        <v>586.3654509722169</v>
+        <v>583.6506153042272</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1250375856131289</v>
+        <v>0.1258595013337437</v>
       </c>
       <c r="T23">
-        <v>1.225780248863098</v>
+        <v>1.238495023660486</v>
       </c>
       <c r="U23">
         <v>0.06933097776675758</v>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.050394328849967</v>
+        <v>8.639012768447696</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3460,22 +3460,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1099150786740088</v>
+        <v>0.1098396456087611</v>
       </c>
       <c r="C24">
-        <v>4121.512787996811</v>
+        <v>4074.192878133216</v>
       </c>
       <c r="D24">
-        <v>4094.401760396458</v>
+        <v>4097.935894732846</v>
       </c>
       <c r="E24">
-        <v>-1380.015447598748</v>
+        <v>-1329.161403398764</v>
       </c>
       <c r="F24">
-        <v>1118.788972399647</v>
+        <v>1169.643016599631</v>
       </c>
       <c r="G24">
         <v>1145.9</v>
@@ -3496,28 +3496,28 @@
         <v>670.1</v>
       </c>
       <c r="M24">
-        <v>77.56673337113347</v>
+        <v>81.09249397891226</v>
       </c>
       <c r="N24">
-        <v>592.5332666288666</v>
+        <v>589.0075060210878</v>
       </c>
       <c r="O24">
-        <v>136.2826513246393</v>
+        <v>135.4717263848502</v>
       </c>
       <c r="P24">
-        <v>456.2506153042273</v>
+        <v>453.5357796362376</v>
       </c>
       <c r="Q24">
-        <v>583.6506153042272</v>
+        <v>580.9357796362376</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1258595013337437</v>
+        <v>0.1267027655146342</v>
       </c>
       <c r="T24">
-        <v>1.238495023660486</v>
+        <v>1.251540052348715</v>
       </c>
       <c r="U24">
         <v>0.06933097776675758</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.639012768447696</v>
+        <v>8.263403517645623</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3542,22 +3542,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1098396456087611</v>
+        <v>0.1097642125435134</v>
       </c>
       <c r="C25">
-        <v>4074.192878133216</v>
+        <v>4026.879074605316</v>
       </c>
       <c r="D25">
-        <v>4097.935894732846</v>
+        <v>4101.476135404931</v>
       </c>
       <c r="E25">
-        <v>-1329.161403398764</v>
+        <v>-1278.30735919878</v>
       </c>
       <c r="F25">
-        <v>1169.643016599631</v>
+        <v>1220.497060799615</v>
       </c>
       <c r="G25">
         <v>1145.9</v>
@@ -3578,28 +3578,28 @@
         <v>670.1</v>
       </c>
       <c r="M25">
-        <v>81.09249397891226</v>
+        <v>84.61825458669105</v>
       </c>
       <c r="N25">
-        <v>589.0075060210878</v>
+        <v>585.481745413309</v>
       </c>
       <c r="O25">
-        <v>135.4717263848502</v>
+        <v>134.6608014450611</v>
       </c>
       <c r="P25">
-        <v>453.5357796362376</v>
+        <v>450.8209439682479</v>
       </c>
       <c r="Q25">
-        <v>580.9357796362376</v>
+        <v>578.2209439682479</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1267027655146342</v>
+        <v>0.1275682208581797</v>
       </c>
       <c r="T25">
-        <v>1.251540052348715</v>
+        <v>1.264928371265582</v>
       </c>
       <c r="U25">
         <v>0.06933097776675758</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.263403517645623</v>
+        <v>7.919095037743722</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3624,22 +3624,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1097642125435134</v>
+        <v>0.1096887794782657</v>
       </c>
       <c r="C26">
-        <v>4026.879074605316</v>
+        <v>3979.571393252742</v>
       </c>
       <c r="D26">
-        <v>4101.476135404931</v>
+        <v>4105.02249825234</v>
       </c>
       <c r="E26">
-        <v>-1278.30735919878</v>
+        <v>-1227.453314998796</v>
       </c>
       <c r="F26">
-        <v>1220.497060799615</v>
+        <v>1271.351104999599</v>
       </c>
       <c r="G26">
         <v>1145.9</v>
@@ -3660,28 +3660,28 @@
         <v>670.1</v>
       </c>
       <c r="M26">
-        <v>84.61825458669105</v>
+        <v>88.14401519446984</v>
       </c>
       <c r="N26">
-        <v>585.481745413309</v>
+        <v>581.9559848055302</v>
       </c>
       <c r="O26">
-        <v>134.6608014450611</v>
+        <v>133.8498765052719</v>
       </c>
       <c r="P26">
-        <v>450.8209439682479</v>
+        <v>448.1061083002583</v>
       </c>
       <c r="Q26">
-        <v>578.2209439682479</v>
+        <v>575.5061083002582</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1275682208581797</v>
+        <v>0.1284567550108864</v>
       </c>
       <c r="T26">
-        <v>1.264928371265582</v>
+        <v>1.278673712020232</v>
       </c>
       <c r="U26">
         <v>0.06933097776675758</v>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.919095037743722</v>
+        <v>7.602331236233973</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3706,22 +3706,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1096887794782657</v>
+        <v>0.1097735064130179</v>
       </c>
       <c r="C27">
-        <v>3979.571393252742</v>
+        <v>3924.734473984801</v>
       </c>
       <c r="D27">
-        <v>4105.02249825234</v>
+        <v>4101.039623184384</v>
       </c>
       <c r="E27">
-        <v>-1227.453314998796</v>
+        <v>-1176.599270798813</v>
       </c>
       <c r="F27">
-        <v>1271.351104999599</v>
+        <v>1322.205149199583</v>
       </c>
       <c r="G27">
         <v>1145.9</v>
@@ -3742,45 +3742,45 @@
         <v>670.1</v>
       </c>
       <c r="M27">
-        <v>88.14401519446984</v>
+        <v>92.72753992160833</v>
       </c>
       <c r="N27">
-        <v>581.9559848055302</v>
+        <v>577.3724600783917</v>
       </c>
       <c r="O27">
-        <v>133.8498765052719</v>
+        <v>132.7956658180301</v>
       </c>
       <c r="P27">
-        <v>448.1061083002583</v>
+        <v>444.5767942603616</v>
       </c>
       <c r="Q27">
-        <v>575.5061083002582</v>
+        <v>571.9767942603615</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1284567550108864</v>
+        <v>0.1293693036001528</v>
       </c>
       <c r="T27">
-        <v>1.278673712020232</v>
+        <v>1.292790548470954</v>
       </c>
       <c r="U27">
-        <v>0.06933097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V27">
         <v>0.23</v>
       </c>
       <c r="W27">
-        <v>0.05338485288040334</v>
+        <v>0.05400085288040334</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.602331236233973</v>
+        <v>7.226547804098989</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3788,22 +3788,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1097735064130179</v>
+        <v>0.1097042333477702</v>
       </c>
       <c r="C28">
-        <v>3924.734473984801</v>
+        <v>3877.136266901206</v>
       </c>
       <c r="D28">
-        <v>4101.039623184384</v>
+        <v>4104.295460300772</v>
       </c>
       <c r="E28">
-        <v>-1176.599270798813</v>
+        <v>-1125.745226598829</v>
       </c>
       <c r="F28">
-        <v>1322.205149199583</v>
+        <v>1373.059193399567</v>
       </c>
       <c r="G28">
         <v>1145.9</v>
@@ -3824,28 +3824,28 @@
         <v>670.1</v>
       </c>
       <c r="M28">
-        <v>92.72753992160833</v>
+        <v>96.29398376474711</v>
       </c>
       <c r="N28">
-        <v>577.3724600783917</v>
+        <v>573.8060162352529</v>
       </c>
       <c r="O28">
-        <v>132.7956658180301</v>
+        <v>131.9753837341082</v>
       </c>
       <c r="P28">
-        <v>444.5767942603616</v>
+        <v>441.8306325011447</v>
       </c>
       <c r="Q28">
-        <v>571.9767942603615</v>
+        <v>569.2306325011447</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1293693036001528</v>
+        <v>0.130306853520632</v>
       </c>
       <c r="T28">
-        <v>1.292790548470954</v>
+        <v>1.307294147564161</v>
       </c>
       <c r="U28">
         <v>0.07013097776675759</v>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.226547804098989</v>
+        <v>6.958897885428656</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3870,22 +3870,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1097042333477702</v>
+        <v>0.1096349602825225</v>
       </c>
       <c r="C29">
-        <v>3877.136266901206</v>
+        <v>3829.54323357781</v>
       </c>
       <c r="D29">
-        <v>4104.295460300772</v>
+        <v>4107.55647117736</v>
       </c>
       <c r="E29">
-        <v>-1125.745226598829</v>
+        <v>-1074.891182398844</v>
       </c>
       <c r="F29">
-        <v>1373.059193399567</v>
+        <v>1423.913237599551</v>
       </c>
       <c r="G29">
         <v>1145.9</v>
@@ -3906,28 +3906,28 @@
         <v>670.1</v>
       </c>
       <c r="M29">
-        <v>96.29398376474711</v>
+        <v>99.8604276078859</v>
       </c>
       <c r="N29">
-        <v>573.8060162352529</v>
+        <v>570.2395723921142</v>
       </c>
       <c r="O29">
-        <v>131.9753837341082</v>
+        <v>131.1551016501863</v>
       </c>
       <c r="P29">
-        <v>441.8306325011447</v>
+        <v>439.0844707419279</v>
       </c>
       <c r="Q29">
-        <v>569.2306325011447</v>
+        <v>566.4844707419279</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.130306853520632</v>
+        <v>0.1312704464944577</v>
       </c>
       <c r="T29">
-        <v>1.307294147564161</v>
+        <v>1.322200624409958</v>
       </c>
       <c r="U29">
         <v>0.07013097776675759</v>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.958897885428656</v>
+        <v>6.710365818091919</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3952,22 +3952,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1096349602825225</v>
+        <v>0.1095656872172748</v>
       </c>
       <c r="C30">
-        <v>3829.54323357781</v>
+        <v>3781.955386356635</v>
       </c>
       <c r="D30">
-        <v>4107.55647117736</v>
+        <v>4110.822668156169</v>
       </c>
       <c r="E30">
-        <v>-1074.891182398844</v>
+        <v>-1024.03713819886</v>
       </c>
       <c r="F30">
-        <v>1423.913237599551</v>
+        <v>1474.767281799535</v>
       </c>
       <c r="G30">
         <v>1145.9</v>
@@ -3988,28 +3988,28 @@
         <v>670.1</v>
       </c>
       <c r="M30">
-        <v>99.8604276078859</v>
+        <v>103.4268714510247</v>
       </c>
       <c r="N30">
-        <v>570.2395723921142</v>
+        <v>566.6731285489753</v>
       </c>
       <c r="O30">
-        <v>131.1551016501863</v>
+        <v>130.3348195662643</v>
       </c>
       <c r="P30">
-        <v>439.0844707419279</v>
+        <v>436.338308982711</v>
       </c>
       <c r="Q30">
-        <v>566.4844707419279</v>
+        <v>563.738308982711</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1312704464944577</v>
+        <v>0.132261182932335</v>
       </c>
       <c r="T30">
-        <v>1.322200624409958</v>
+        <v>1.337527002011973</v>
       </c>
       <c r="U30">
         <v>0.07013097776675759</v>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.710365818091919</v>
+        <v>6.478973893330128</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4034,22 +4034,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1095656872172748</v>
+        <v>0.1094964141520271</v>
       </c>
       <c r="C31">
-        <v>3781.955386356635</v>
+        <v>3734.372737618995</v>
       </c>
       <c r="D31">
-        <v>4110.822668156169</v>
+        <v>4114.094063618512</v>
       </c>
       <c r="E31">
-        <v>-1024.037138198861</v>
+        <v>-973.1830939988768</v>
       </c>
       <c r="F31">
-        <v>1474.767281799534</v>
+        <v>1525.621325999518</v>
       </c>
       <c r="G31">
         <v>1145.9</v>
@@ -4070,28 +4070,28 @@
         <v>670.1</v>
       </c>
       <c r="M31">
-        <v>103.4268714510247</v>
+        <v>106.9933152941635</v>
       </c>
       <c r="N31">
-        <v>566.6731285489753</v>
+        <v>563.1066847058365</v>
       </c>
       <c r="O31">
-        <v>130.3348195662643</v>
+        <v>129.5145374823424</v>
       </c>
       <c r="P31">
-        <v>436.338308982711</v>
+        <v>433.5921472234941</v>
       </c>
       <c r="Q31">
-        <v>563.738308982711</v>
+        <v>560.9921472234942</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.132261182932335</v>
+        <v>0.1332802261255801</v>
       </c>
       <c r="T31">
-        <v>1.337527002011973</v>
+        <v>1.353291276116904</v>
       </c>
       <c r="U31">
         <v>0.07013097776675759</v>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.478973893330129</v>
+        <v>6.26300809688579</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4116,22 +4116,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1094964141520271</v>
+        <v>0.1096658410867793</v>
       </c>
       <c r="C32">
-        <v>3734.372737618995</v>
+        <v>3675.526755535137</v>
       </c>
       <c r="D32">
-        <v>4114.094063618512</v>
+        <v>4106.10212573464</v>
       </c>
       <c r="E32">
-        <v>-973.1830939988768</v>
+        <v>-922.3290497988928</v>
       </c>
       <c r="F32">
-        <v>1525.621325999518</v>
+        <v>1576.475370199502</v>
       </c>
       <c r="G32">
         <v>1145.9</v>
@@ -4152,45 +4152,45 @@
         <v>670.1</v>
       </c>
       <c r="M32">
-        <v>106.9933152941635</v>
+        <v>112.1362345075017</v>
       </c>
       <c r="N32">
-        <v>563.1066847058365</v>
+        <v>557.9637654924983</v>
       </c>
       <c r="O32">
-        <v>129.5145374823424</v>
+        <v>128.3316660632746</v>
       </c>
       <c r="P32">
-        <v>433.5921472234941</v>
+        <v>429.6320994292237</v>
       </c>
       <c r="Q32">
-        <v>560.9921472234942</v>
+        <v>557.0320994292236</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1332802261255801</v>
+        <v>0.1343288068026874</v>
       </c>
       <c r="T32">
-        <v>1.353291276116904</v>
+        <v>1.369512485703137</v>
       </c>
       <c r="U32">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V32">
         <v>0.23</v>
       </c>
       <c r="W32">
-        <v>0.05400085288040334</v>
+        <v>0.05477085288040334</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.26300809688579</v>
+        <v>5.975766913728242</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4198,22 +4198,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1096658410867793</v>
+        <v>0.1096042680215316</v>
       </c>
       <c r="C33">
-        <v>3675.526755535137</v>
+        <v>3627.5735438666</v>
       </c>
       <c r="D33">
-        <v>4106.10212573464</v>
+        <v>4109.002958266085</v>
       </c>
       <c r="E33">
-        <v>-922.3290497988928</v>
+        <v>-871.4750055989089</v>
       </c>
       <c r="F33">
-        <v>1576.475370199502</v>
+        <v>1627.329414399486</v>
       </c>
       <c r="G33">
         <v>1145.9</v>
@@ -4234,28 +4234,28 @@
         <v>670.1</v>
       </c>
       <c r="M33">
-        <v>112.1362345075017</v>
+        <v>115.7535323948405</v>
       </c>
       <c r="N33">
-        <v>557.9637654924983</v>
+        <v>554.3464676051595</v>
       </c>
       <c r="O33">
-        <v>128.3316660632746</v>
+        <v>127.4996875491867</v>
       </c>
       <c r="P33">
-        <v>429.6320994292237</v>
+        <v>426.8467800559728</v>
       </c>
       <c r="Q33">
-        <v>557.0320994292236</v>
+        <v>554.2467800559727</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1343288068026874</v>
+        <v>0.1354082280879449</v>
       </c>
       <c r="T33">
-        <v>1.369512485703137</v>
+        <v>1.386210789688965</v>
       </c>
       <c r="U33">
         <v>0.07113097776675759</v>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.975766913728242</v>
+        <v>5.789024197674235</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4280,22 +4280,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1096042680215316</v>
+        <v>0.1095426949562839</v>
       </c>
       <c r="C34">
-        <v>3627.5735438666</v>
+        <v>3579.624433790342</v>
       </c>
       <c r="D34">
-        <v>4109.002958266085</v>
+        <v>4111.907892389812</v>
       </c>
       <c r="E34">
-        <v>-871.4750055989089</v>
+        <v>-820.6209613989249</v>
       </c>
       <c r="F34">
-        <v>1627.329414399486</v>
+        <v>1678.18345859947</v>
       </c>
       <c r="G34">
         <v>1145.9</v>
@@ -4316,28 +4316,28 @@
         <v>670.1</v>
       </c>
       <c r="M34">
-        <v>115.7535323948405</v>
+        <v>119.3708302821793</v>
       </c>
       <c r="N34">
-        <v>554.3464676051595</v>
+        <v>550.7291697178207</v>
       </c>
       <c r="O34">
-        <v>127.4996875491867</v>
+        <v>126.6677090350988</v>
       </c>
       <c r="P34">
-        <v>426.8467800559728</v>
+        <v>424.0614606827219</v>
       </c>
       <c r="Q34">
-        <v>554.2467800559727</v>
+        <v>551.461460682722</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1354082280879449</v>
+        <v>0.1365198709041057</v>
       </c>
       <c r="T34">
-        <v>1.386210789688965</v>
+        <v>1.403407550510191</v>
       </c>
       <c r="U34">
         <v>0.07113097776675759</v>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.789024197674235</v>
+        <v>5.613599221987136</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4362,22 +4362,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1095426949562839</v>
+        <v>0.1094811218910362</v>
       </c>
       <c r="C35">
-        <v>3579.624433790342</v>
+        <v>3531.679434011605</v>
       </c>
       <c r="D35">
-        <v>4111.907892389812</v>
+        <v>4114.816936811059</v>
       </c>
       <c r="E35">
-        <v>-820.6209613989249</v>
+        <v>-769.7669171989407</v>
       </c>
       <c r="F35">
-        <v>1678.18345859947</v>
+        <v>1729.037502799454</v>
       </c>
       <c r="G35">
         <v>1145.9</v>
@@ -4398,28 +4398,28 @@
         <v>670.1</v>
       </c>
       <c r="M35">
-        <v>119.3708302821793</v>
+        <v>122.988128169518</v>
       </c>
       <c r="N35">
-        <v>550.7291697178207</v>
+        <v>547.111871830482</v>
       </c>
       <c r="O35">
-        <v>126.6677090350988</v>
+        <v>125.8357305210109</v>
       </c>
       <c r="P35">
-        <v>424.0614606827219</v>
+        <v>421.2761413094711</v>
       </c>
       <c r="Q35">
-        <v>551.461460682722</v>
+        <v>548.6761413094711</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1365198709041057</v>
+        <v>0.1376651998662107</v>
       </c>
       <c r="T35">
-        <v>1.403407550510191</v>
+        <v>1.421125425295696</v>
       </c>
       <c r="U35">
         <v>0.07113097776675759</v>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.613599221987136</v>
+        <v>5.448493362516926</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4444,22 +4444,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1094811218910362</v>
+        <v>0.1094195488257884</v>
       </c>
       <c r="C36">
-        <v>3531.679434011605</v>
+        <v>3483.738553260279</v>
       </c>
       <c r="D36">
-        <v>4114.816936811059</v>
+        <v>4117.730100259717</v>
       </c>
       <c r="E36">
-        <v>-769.7669171989407</v>
+        <v>-718.9128729989568</v>
       </c>
       <c r="F36">
-        <v>1729.037502799454</v>
+        <v>1779.891546999438</v>
       </c>
       <c r="G36">
         <v>1145.9</v>
@@ -4480,28 +4480,28 @@
         <v>670.1</v>
       </c>
       <c r="M36">
-        <v>122.988128169518</v>
+        <v>126.6054260568568</v>
       </c>
       <c r="N36">
-        <v>547.111871830482</v>
+        <v>543.4945739431432</v>
       </c>
       <c r="O36">
-        <v>125.8357305210109</v>
+        <v>125.003752006923</v>
       </c>
       <c r="P36">
-        <v>421.2761413094711</v>
+        <v>418.4908219362203</v>
       </c>
       <c r="Q36">
-        <v>548.6761413094711</v>
+        <v>545.8908219362203</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1376651998662107</v>
+        <v>0.1388457697194574</v>
       </c>
       <c r="T36">
-        <v>1.421125425295696</v>
+        <v>1.439388465459217</v>
       </c>
       <c r="U36">
         <v>0.07113097776675759</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.448493362516926</v>
+        <v>5.292822123587871</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4526,22 +4526,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1094195488257884</v>
+        <v>0.1093579757605407</v>
       </c>
       <c r="C37">
-        <v>3483.738553260279</v>
+        <v>3435.801800290996</v>
       </c>
       <c r="D37">
-        <v>4117.730100259717</v>
+        <v>4120.647391490417</v>
       </c>
       <c r="E37">
-        <v>-718.9128729989568</v>
+        <v>-668.0588287989729</v>
       </c>
       <c r="F37">
-        <v>1779.891546999438</v>
+        <v>1830.745591199422</v>
       </c>
       <c r="G37">
         <v>1145.9</v>
@@ -4562,28 +4562,28 @@
         <v>670.1</v>
       </c>
       <c r="M37">
-        <v>126.6054260568568</v>
+        <v>130.2227239441956</v>
       </c>
       <c r="N37">
-        <v>543.4945739431432</v>
+        <v>539.8772760558045</v>
       </c>
       <c r="O37">
-        <v>125.003752006923</v>
+        <v>124.171773492835</v>
       </c>
       <c r="P37">
-        <v>418.4908219362203</v>
+        <v>415.7055025629695</v>
       </c>
       <c r="Q37">
-        <v>545.8908219362203</v>
+        <v>543.1055025629694</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1388457697194574</v>
+        <v>0.140063232380618</v>
       </c>
       <c r="T37">
-        <v>1.439388465459217</v>
+        <v>1.458222225627848</v>
       </c>
       <c r="U37">
         <v>0.07113097776675759</v>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.292822123587871</v>
+        <v>5.145799286821542</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4608,22 +4608,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1093579757605407</v>
+        <v>0.109296402695293</v>
       </c>
       <c r="C38">
-        <v>3435.801800290994</v>
+        <v>3387.869183883212</v>
       </c>
       <c r="D38">
-        <v>4120.647391490416</v>
+        <v>4123.568819282618</v>
       </c>
       <c r="E38">
-        <v>-668.0588287989731</v>
+        <v>-617.2047845989891</v>
       </c>
       <c r="F38">
-        <v>1830.745591199422</v>
+        <v>1881.599635399406</v>
       </c>
       <c r="G38">
         <v>1145.9</v>
@@ -4644,28 +4644,28 @@
         <v>670.1</v>
       </c>
       <c r="M38">
-        <v>130.2227239441956</v>
+        <v>133.8400218315343</v>
       </c>
       <c r="N38">
-        <v>539.8772760558045</v>
+        <v>536.2599781684658</v>
       </c>
       <c r="O38">
-        <v>124.171773492835</v>
+        <v>123.3397949787471</v>
       </c>
       <c r="P38">
-        <v>415.7055025629695</v>
+        <v>412.9201831897186</v>
       </c>
       <c r="Q38">
-        <v>543.1055025629694</v>
+        <v>540.3201831897186</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.140063232380618</v>
+        <v>0.1413193446500695</v>
       </c>
       <c r="T38">
-        <v>1.458222225627848</v>
+        <v>1.47765388294469</v>
       </c>
       <c r="U38">
         <v>0.07113097776675759</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.145799286821542</v>
+        <v>5.00672363042096</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4690,22 +4690,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.109296402695293</v>
+        <v>0.1092348296300453</v>
       </c>
       <c r="C39">
-        <v>3387.869183883212</v>
+        <v>3339.940712841304</v>
       </c>
       <c r="D39">
-        <v>4123.568819282618</v>
+        <v>4126.494392440694</v>
       </c>
       <c r="E39">
-        <v>-617.2047845989891</v>
+        <v>-566.3507403990052</v>
       </c>
       <c r="F39">
-        <v>1881.599635399406</v>
+        <v>1932.45367959939</v>
       </c>
       <c r="G39">
         <v>1145.9</v>
@@ -4726,28 +4726,28 @@
         <v>670.1</v>
       </c>
       <c r="M39">
-        <v>133.8400218315343</v>
+        <v>137.4573197188731</v>
       </c>
       <c r="N39">
-        <v>536.2599781684658</v>
+        <v>532.6426802811269</v>
       </c>
       <c r="O39">
-        <v>123.3397949787471</v>
+        <v>122.5078164646592</v>
       </c>
       <c r="P39">
-        <v>412.9201831897186</v>
+        <v>410.1348638164677</v>
       </c>
       <c r="Q39">
-        <v>540.3201831897186</v>
+        <v>537.5348638164677</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1413193446500695</v>
+        <v>0.1426159766701484</v>
       </c>
       <c r="T39">
-        <v>1.47765388294469</v>
+        <v>1.497712367916913</v>
       </c>
       <c r="U39">
         <v>0.07113097776675759</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.00672363042096</v>
+        <v>4.874967745409881</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4772,22 +4772,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1092348296300453</v>
+        <v>0.1091732565647976</v>
       </c>
       <c r="C40">
-        <v>3339.940712841304</v>
+        <v>3292.016395994649</v>
       </c>
       <c r="D40">
-        <v>4126.494392440694</v>
+        <v>4129.424119794022</v>
       </c>
       <c r="E40">
-        <v>-566.3507403990052</v>
+        <v>-515.4966961990212</v>
       </c>
       <c r="F40">
-        <v>1932.45367959939</v>
+        <v>1983.307723799374</v>
       </c>
       <c r="G40">
         <v>1145.9</v>
@@ -4808,28 +4808,28 @@
         <v>670.1</v>
       </c>
       <c r="M40">
-        <v>137.4573197188731</v>
+        <v>141.0746176062119</v>
       </c>
       <c r="N40">
-        <v>532.6426802811269</v>
+        <v>529.0253823937882</v>
       </c>
       <c r="O40">
-        <v>122.5078164646592</v>
+        <v>121.6758379505713</v>
       </c>
       <c r="P40">
-        <v>410.1348638164677</v>
+        <v>407.3495444432169</v>
       </c>
       <c r="Q40">
-        <v>537.5348638164677</v>
+        <v>534.7495444432168</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1426159766701484</v>
+        <v>0.1439551212154759</v>
       </c>
       <c r="T40">
-        <v>1.497712367916913</v>
+        <v>1.518428508134128</v>
       </c>
       <c r="U40">
         <v>0.07113097776675759</v>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.874967745409881</v>
+        <v>4.749968572450654</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4854,22 +4854,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1091732565647976</v>
+        <v>0.1091116834995498</v>
       </c>
       <c r="C41">
-        <v>3292.016395994649</v>
+        <v>3244.096242197715</v>
       </c>
       <c r="D41">
-        <v>4129.424119794022</v>
+        <v>4132.358010197072</v>
       </c>
       <c r="E41">
-        <v>-515.4966961990212</v>
+        <v>-464.6426519990373</v>
       </c>
       <c r="F41">
-        <v>1983.307723799374</v>
+        <v>2034.161767999358</v>
       </c>
       <c r="G41">
         <v>1145.9</v>
@@ -4890,28 +4890,28 @@
         <v>670.1</v>
       </c>
       <c r="M41">
-        <v>141.0746176062119</v>
+        <v>144.6919154935506</v>
       </c>
       <c r="N41">
-        <v>529.0253823937882</v>
+        <v>525.4080845064494</v>
       </c>
       <c r="O41">
-        <v>121.6758379505713</v>
+        <v>120.8438594364834</v>
       </c>
       <c r="P41">
-        <v>407.3495444432169</v>
+        <v>404.564225069966</v>
       </c>
       <c r="Q41">
-        <v>534.7495444432168</v>
+        <v>531.964225069966</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1439551212154759</v>
+        <v>0.1453389039123142</v>
       </c>
       <c r="T41">
-        <v>1.518428508134128</v>
+        <v>1.539835186358582</v>
       </c>
       <c r="U41">
         <v>0.07113097776675759</v>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.749968572450654</v>
+        <v>4.631219358139388</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4936,22 +4936,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1091116834995498</v>
+        <v>0.1090501104343021</v>
       </c>
       <c r="C42">
-        <v>3244.096242197715</v>
+        <v>3196.180260330152</v>
       </c>
       <c r="D42">
-        <v>4132.358010197072</v>
+        <v>4135.296072529493</v>
       </c>
       <c r="E42">
-        <v>-464.6426519990373</v>
+        <v>-413.7886077990534</v>
       </c>
       <c r="F42">
-        <v>2034.161767999358</v>
+        <v>2085.015812199342</v>
       </c>
       <c r="G42">
         <v>1145.9</v>
@@ -4972,28 +4972,28 @@
         <v>670.1</v>
       </c>
       <c r="M42">
-        <v>144.6919154935506</v>
+        <v>148.3092133808894</v>
       </c>
       <c r="N42">
-        <v>525.4080845064494</v>
+        <v>521.7907866191106</v>
       </c>
       <c r="O42">
-        <v>120.8438594364834</v>
+        <v>120.0118809223954</v>
       </c>
       <c r="P42">
-        <v>404.564225069966</v>
+        <v>401.7789056967151</v>
       </c>
       <c r="Q42">
-        <v>531.964225069966</v>
+        <v>529.1789056967151</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1453389039123142</v>
+        <v>0.1467695944971809</v>
       </c>
       <c r="T42">
-        <v>1.539835186358582</v>
+        <v>1.561967514692341</v>
       </c>
       <c r="U42">
         <v>0.07113097776675759</v>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.631219358139388</v>
+        <v>4.51826278842867</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5018,22 +5018,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1090501104343021</v>
+        <v>0.1097970373690544</v>
       </c>
       <c r="C43">
-        <v>3196.180260330152</v>
+        <v>3109.964985840836</v>
       </c>
       <c r="D43">
-        <v>4135.296072529493</v>
+        <v>4099.934842240161</v>
       </c>
       <c r="E43">
-        <v>-413.7886077990534</v>
+        <v>-362.9345635990694</v>
       </c>
       <c r="F43">
-        <v>2085.015812199342</v>
+        <v>2135.869856399326</v>
       </c>
       <c r="G43">
         <v>1145.9</v>
@@ -5054,45 +5054,45 @@
         <v>670.1</v>
       </c>
       <c r="M43">
-        <v>148.3092133808894</v>
+        <v>157.2661859092264</v>
       </c>
       <c r="N43">
-        <v>521.7907866191106</v>
+        <v>512.8338140907736</v>
       </c>
       <c r="O43">
-        <v>120.0118809223954</v>
+        <v>117.9517772408779</v>
       </c>
       <c r="P43">
-        <v>401.7789056967151</v>
+        <v>394.8820368498957</v>
       </c>
       <c r="Q43">
-        <v>529.1789056967151</v>
+        <v>522.2820368498956</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1467695944971809</v>
+        <v>0.1482496192401466</v>
       </c>
       <c r="T43">
-        <v>1.561967514692341</v>
+        <v>1.584863026761746</v>
       </c>
       <c r="U43">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V43">
         <v>0.23</v>
       </c>
       <c r="W43">
-        <v>0.05477085288040334</v>
+        <v>0.05669585288040333</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.51826278842867</v>
+        <v>4.260928667697071</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5100,22 +5100,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1097970373690544</v>
+        <v>0.1097547143038067</v>
       </c>
       <c r="C44">
-        <v>3109.964985840836</v>
+        <v>3061.098441858706</v>
       </c>
       <c r="D44">
-        <v>4099.934842240161</v>
+        <v>4101.922342458015</v>
       </c>
       <c r="E44">
-        <v>-362.9345635990694</v>
+        <v>-312.0805193990855</v>
       </c>
       <c r="F44">
-        <v>2135.869856399326</v>
+        <v>2186.72390059931</v>
       </c>
       <c r="G44">
         <v>1145.9</v>
@@ -5136,28 +5136,28 @@
         <v>670.1</v>
       </c>
       <c r="M44">
-        <v>157.2661859092264</v>
+        <v>161.0106189070652</v>
       </c>
       <c r="N44">
-        <v>512.8338140907736</v>
+        <v>509.0893810929348</v>
       </c>
       <c r="O44">
-        <v>117.9517772408779</v>
+        <v>117.090557651375</v>
       </c>
       <c r="P44">
-        <v>394.8820368498957</v>
+        <v>391.9988234415598</v>
       </c>
       <c r="Q44">
-        <v>522.2820368498956</v>
+        <v>519.3988234415598</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1482496192401465</v>
+        <v>0.1497815746758478</v>
       </c>
       <c r="T44">
-        <v>1.584863026761746</v>
+        <v>1.608561890131832</v>
       </c>
       <c r="U44">
         <v>0.07363097776675757</v>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.260928667697071</v>
+        <v>4.161837303332022</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5182,22 +5182,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1097547143038067</v>
+        <v>0.109712391238559</v>
       </c>
       <c r="C45">
-        <v>3061.098441858706</v>
+        <v>3012.233825747673</v>
       </c>
       <c r="D45">
-        <v>4101.922342458015</v>
+        <v>4103.911770546966</v>
       </c>
       <c r="E45">
-        <v>-312.0805193990855</v>
+        <v>-261.2264751991015</v>
       </c>
       <c r="F45">
-        <v>2186.72390059931</v>
+        <v>2237.577944799294</v>
       </c>
       <c r="G45">
         <v>1145.9</v>
@@ -5218,28 +5218,28 @@
         <v>670.1</v>
       </c>
       <c r="M45">
-        <v>161.0106189070652</v>
+        <v>164.7550519049039</v>
       </c>
       <c r="N45">
-        <v>509.0893810929348</v>
+        <v>505.3449480950961</v>
       </c>
       <c r="O45">
-        <v>117.090557651375</v>
+        <v>116.2293380618721</v>
       </c>
       <c r="P45">
-        <v>391.9988234415598</v>
+        <v>389.115610033224</v>
       </c>
       <c r="Q45">
-        <v>519.3988234415598</v>
+        <v>516.515610033224</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1497815746758478</v>
+        <v>0.1513682428056812</v>
       </c>
       <c r="T45">
-        <v>1.608561890131832</v>
+        <v>1.633107141479422</v>
       </c>
       <c r="U45">
         <v>0.07363097776675757</v>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.161837303332022</v>
+        <v>4.067250091892658</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5264,22 +5264,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.109712391238559</v>
+        <v>0.1108828181733112</v>
       </c>
       <c r="C46">
-        <v>3012.233825747673</v>
+        <v>2907.064781220047</v>
       </c>
       <c r="D46">
-        <v>4103.911770546966</v>
+        <v>4049.596770219324</v>
       </c>
       <c r="E46">
-        <v>-261.2264751991015</v>
+        <v>-210.3724309991176</v>
       </c>
       <c r="F46">
-        <v>2237.577944799294</v>
+        <v>2288.431988999278</v>
       </c>
       <c r="G46">
         <v>1145.9</v>
@@ -5300,45 +5300,45 @@
         <v>670.1</v>
       </c>
       <c r="M46">
-        <v>164.7550519049039</v>
+        <v>176.5089968642401</v>
       </c>
       <c r="N46">
-        <v>505.3449480950961</v>
+        <v>493.5910031357599</v>
       </c>
       <c r="O46">
-        <v>116.2293380618721</v>
+        <v>113.5259307212248</v>
       </c>
       <c r="P46">
-        <v>389.115610033224</v>
+        <v>380.0650724145352</v>
       </c>
       <c r="Q46">
-        <v>516.515610033224</v>
+        <v>507.4650724145351</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1513682428056812</v>
+        <v>0.1530126079584177</v>
       </c>
       <c r="T46">
-        <v>1.633107141479422</v>
+        <v>1.658544947421468</v>
       </c>
       <c r="U46">
-        <v>0.07363097776675757</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V46">
         <v>0.23</v>
       </c>
       <c r="W46">
-        <v>0.05669585288040333</v>
+        <v>0.05939085288040333</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.067250091892658</v>
+        <v>3.796407049525073</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5346,22 +5346,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1108828181733112</v>
+        <v>0.1108674451080635</v>
       </c>
       <c r="C47">
-        <v>2907.064781220047</v>
+        <v>2856.914822223761</v>
       </c>
       <c r="D47">
-        <v>4049.596770219324</v>
+        <v>4050.300855423022</v>
       </c>
       <c r="E47">
-        <v>-210.3724309991176</v>
+        <v>-159.5183867991336</v>
       </c>
       <c r="F47">
-        <v>2288.431988999278</v>
+        <v>2339.286033199262</v>
       </c>
       <c r="G47">
         <v>1145.9</v>
@@ -5382,28 +5382,28 @@
         <v>670.1</v>
       </c>
       <c r="M47">
-        <v>176.5089968642401</v>
+        <v>180.4314190167788</v>
       </c>
       <c r="N47">
-        <v>493.5910031357599</v>
+        <v>489.6685809832213</v>
       </c>
       <c r="O47">
-        <v>113.5259307212248</v>
+        <v>112.6237736261409</v>
       </c>
       <c r="P47">
-        <v>380.0650724145352</v>
+        <v>377.0448073570803</v>
       </c>
       <c r="Q47">
-        <v>507.4650724145351</v>
+        <v>504.4448073570803</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1530126079584177</v>
+        <v>0.1547178755242185</v>
       </c>
       <c r="T47">
-        <v>1.658544947421468</v>
+        <v>1.684924894324332</v>
       </c>
       <c r="U47">
         <v>0.07713097776675758</v>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.796407049525073</v>
+        <v>3.713876461491919</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5428,22 +5428,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1108674451080635</v>
+        <v>0.1108520720428158</v>
       </c>
       <c r="C48">
-        <v>2856.914822223761</v>
+        <v>2806.765108102317</v>
       </c>
       <c r="D48">
-        <v>4050.300855423022</v>
+        <v>4051.005185501562</v>
       </c>
       <c r="E48">
-        <v>-159.5183867991336</v>
+        <v>-108.6643425991497</v>
       </c>
       <c r="F48">
-        <v>2339.286033199262</v>
+        <v>2390.140077399245</v>
       </c>
       <c r="G48">
         <v>1145.9</v>
@@ -5464,28 +5464,28 @@
         <v>670.1</v>
       </c>
       <c r="M48">
-        <v>180.4314190167788</v>
+        <v>184.3538411693174</v>
       </c>
       <c r="N48">
-        <v>489.6685809832213</v>
+        <v>485.7461588306826</v>
       </c>
       <c r="O48">
-        <v>112.6237736261409</v>
+        <v>111.721616531057</v>
       </c>
       <c r="P48">
-        <v>377.0448073570803</v>
+        <v>374.0245422996256</v>
       </c>
       <c r="Q48">
-        <v>504.4448073570803</v>
+        <v>501.4245422996256</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1547178755242185</v>
+        <v>0.1564874928094834</v>
       </c>
       <c r="T48">
-        <v>1.684924894324332</v>
+        <v>1.712300310921643</v>
       </c>
       <c r="U48">
         <v>0.07713097776675758</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.713876461491919</v>
+        <v>3.634857813375069</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5510,22 +5510,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1108520720428158</v>
+        <v>0.1108366989775681</v>
       </c>
       <c r="C49">
-        <v>2806.765108102317</v>
+        <v>2756.61563898348</v>
       </c>
       <c r="D49">
-        <v>4051.005185501562</v>
+        <v>4051.709760582709</v>
       </c>
       <c r="E49">
-        <v>-108.6643425991497</v>
+        <v>-57.81029839916573</v>
       </c>
       <c r="F49">
-        <v>2390.140077399245</v>
+        <v>2440.994121599229</v>
       </c>
       <c r="G49">
         <v>1145.9</v>
@@ -5546,28 +5546,28 @@
         <v>670.1</v>
       </c>
       <c r="M49">
-        <v>184.3538411693174</v>
+        <v>188.2762633218561</v>
       </c>
       <c r="N49">
-        <v>485.7461588306826</v>
+        <v>481.8237366781439</v>
       </c>
       <c r="O49">
-        <v>111.721616531057</v>
+        <v>110.8194594359731</v>
       </c>
       <c r="P49">
-        <v>374.0245422996256</v>
+        <v>371.0042772421708</v>
       </c>
       <c r="Q49">
-        <v>501.4245422996256</v>
+        <v>498.4042772421708</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1564874928094834</v>
+        <v>0.1583251722980278</v>
       </c>
       <c r="T49">
-        <v>1.712300310921643</v>
+        <v>1.740728628157313</v>
       </c>
       <c r="U49">
         <v>0.07713097776675758</v>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.634857813375069</v>
+        <v>3.559131608929755</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5592,22 +5592,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1108366989775681</v>
+        <v>0.1118777659123204</v>
       </c>
       <c r="C50">
-        <v>2756.61563898348</v>
+        <v>2658.594879886948</v>
       </c>
       <c r="D50">
-        <v>4051.709760582709</v>
+        <v>4004.543045686161</v>
       </c>
       <c r="E50">
-        <v>-57.81029839916573</v>
+        <v>-6.956254199181785</v>
       </c>
       <c r="F50">
-        <v>2440.994121599229</v>
+        <v>2491.848165799213</v>
       </c>
       <c r="G50">
         <v>1145.9</v>
@@ -5628,45 +5628,45 @@
         <v>670.1</v>
       </c>
       <c r="M50">
-        <v>188.2762633218561</v>
+        <v>199.1758603386326</v>
       </c>
       <c r="N50">
-        <v>481.8237366781439</v>
+        <v>470.9241396613675</v>
       </c>
       <c r="O50">
-        <v>110.8194594359731</v>
+        <v>108.3125521221145</v>
       </c>
       <c r="P50">
-        <v>371.0042772421708</v>
+        <v>362.6115875392529</v>
       </c>
       <c r="Q50">
-        <v>498.4042772421708</v>
+        <v>490.0115875392529</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1583251722980278</v>
+        <v>0.1602349176488681</v>
       </c>
       <c r="T50">
-        <v>1.740728628157313</v>
+        <v>1.770271781363009</v>
       </c>
       <c r="U50">
-        <v>0.07713097776675758</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V50">
         <v>0.23</v>
       </c>
       <c r="W50">
-        <v>0.05939085288040333</v>
+        <v>0.06154685288040335</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.559131608929755</v>
+        <v>3.364363527089663</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5674,22 +5674,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1118777659123204</v>
+        <v>0.1118839528470726</v>
       </c>
       <c r="C51">
-        <v>2658.594879886948</v>
+        <v>2607.463811871591</v>
       </c>
       <c r="D51">
-        <v>4004.543045686161</v>
+        <v>4004.266021870788</v>
       </c>
       <c r="E51">
-        <v>-6.956254199181785</v>
+        <v>43.89779000080216</v>
       </c>
       <c r="F51">
-        <v>2491.848165799213</v>
+        <v>2542.702209999197</v>
       </c>
       <c r="G51">
         <v>1145.9</v>
@@ -5710,28 +5710,28 @@
         <v>670.1</v>
       </c>
       <c r="M51">
-        <v>199.1758603386326</v>
+        <v>203.2406738149312</v>
       </c>
       <c r="N51">
-        <v>470.9241396613675</v>
+        <v>466.8593261850688</v>
       </c>
       <c r="O51">
-        <v>108.3125521221145</v>
+        <v>107.3776450225658</v>
       </c>
       <c r="P51">
-        <v>362.6115875392529</v>
+        <v>359.4816811625029</v>
       </c>
       <c r="Q51">
-        <v>490.0115875392529</v>
+        <v>486.8816811625029</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1602349176488681</v>
+        <v>0.1622210528137419</v>
       </c>
       <c r="T51">
-        <v>1.770271781363009</v>
+        <v>1.800996660696932</v>
       </c>
       <c r="U51">
         <v>0.07993097776675759</v>
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.364363527089663</v>
+        <v>3.297076256547869</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5756,22 +5756,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1118839528470726</v>
+        <v>0.1118901397818249</v>
       </c>
       <c r="C52">
-        <v>2607.463811871591</v>
+        <v>2556.332782181149</v>
       </c>
       <c r="D52">
-        <v>4004.266021870788</v>
+        <v>4003.98903638033</v>
       </c>
       <c r="E52">
-        <v>43.89779000080216</v>
+        <v>94.75183420078611</v>
       </c>
       <c r="F52">
-        <v>2542.702209999197</v>
+        <v>2593.556254199181</v>
       </c>
       <c r="G52">
         <v>1145.9</v>
@@ -5792,28 +5792,28 @@
         <v>670.1</v>
       </c>
       <c r="M52">
-        <v>203.2406738149312</v>
+        <v>207.3054872912298</v>
       </c>
       <c r="N52">
-        <v>466.8593261850688</v>
+        <v>462.7945127087702</v>
       </c>
       <c r="O52">
-        <v>107.3776450225658</v>
+        <v>106.4427379230171</v>
       </c>
       <c r="P52">
-        <v>359.4816811625029</v>
+        <v>356.351774785753</v>
       </c>
       <c r="Q52">
-        <v>486.8816811625029</v>
+        <v>483.751774785753</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1622210528137419</v>
+        <v>0.1642882547200392</v>
       </c>
       <c r="T52">
-        <v>1.800996660696932</v>
+        <v>1.832975616738363</v>
       </c>
       <c r="U52">
         <v>0.07993097776675759</v>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.297076256547869</v>
+        <v>3.232427702497911</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5838,22 +5838,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1118901397818249</v>
+        <v>0.1118963267165772</v>
       </c>
       <c r="C53">
-        <v>2556.332782181149</v>
+        <v>2505.20179080767</v>
       </c>
       <c r="D53">
-        <v>4003.98903638033</v>
+        <v>4003.712089206836</v>
       </c>
       <c r="E53">
-        <v>94.75183420078611</v>
+        <v>145.6058784007701</v>
       </c>
       <c r="F53">
-        <v>2593.556254199181</v>
+        <v>2644.410298399165</v>
       </c>
       <c r="G53">
         <v>1145.9</v>
@@ -5874,28 +5874,28 @@
         <v>670.1</v>
       </c>
       <c r="M53">
-        <v>207.3054872912298</v>
+        <v>211.3703007675285</v>
       </c>
       <c r="N53">
-        <v>462.7945127087702</v>
+        <v>458.7296992324715</v>
       </c>
       <c r="O53">
-        <v>106.4427379230171</v>
+        <v>105.5078308234685</v>
       </c>
       <c r="P53">
-        <v>356.351774785753</v>
+        <v>353.2218684090031</v>
       </c>
       <c r="Q53">
-        <v>483.751774785753</v>
+        <v>480.6218684090031</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1642882547200392</v>
+        <v>0.1664415900390989</v>
       </c>
       <c r="T53">
-        <v>1.832975616738363</v>
+        <v>1.86628702928152</v>
       </c>
       <c r="U53">
         <v>0.07993097776675759</v>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.232427702497911</v>
+        <v>3.170265631296028</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1118963267165772</v>
+        <v>0.1119025136513295</v>
       </c>
       <c r="C54">
-        <v>2505.20179080767</v>
+        <v>2454.070837743203</v>
       </c>
       <c r="D54">
-        <v>4003.712089206836</v>
+        <v>4003.435180342352</v>
       </c>
       <c r="E54">
-        <v>145.6058784007701</v>
+        <v>196.459922600754</v>
       </c>
       <c r="F54">
-        <v>2644.410298399165</v>
+        <v>2695.264342599149</v>
       </c>
       <c r="G54">
         <v>1145.9</v>
@@ -5956,28 +5956,28 @@
         <v>670.1</v>
       </c>
       <c r="M54">
-        <v>211.3703007675285</v>
+        <v>215.4351142438271</v>
       </c>
       <c r="N54">
-        <v>458.7296992324715</v>
+        <v>454.6648857561729</v>
       </c>
       <c r="O54">
-        <v>105.5078308234685</v>
+        <v>104.5729237239198</v>
       </c>
       <c r="P54">
-        <v>353.2218684090031</v>
+        <v>350.0919620322532</v>
       </c>
       <c r="Q54">
-        <v>480.6218684090031</v>
+        <v>477.4919620322531</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1664415900390989</v>
+        <v>0.1686865566483313</v>
       </c>
       <c r="T54">
-        <v>1.86628702928152</v>
+        <v>1.901015948741407</v>
       </c>
       <c r="U54">
         <v>0.07993097776675759</v>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.170265631296028</v>
+        <v>3.110449298630066</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6002,22 +6002,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1119025136513295</v>
+        <v>0.1119087005860817</v>
       </c>
       <c r="C55">
-        <v>2454.070837743203</v>
+        <v>2402.9399229798</v>
       </c>
       <c r="D55">
-        <v>4003.435180342352</v>
+        <v>4003.158309778933</v>
       </c>
       <c r="E55">
-        <v>196.459922600754</v>
+        <v>247.3139668007379</v>
       </c>
       <c r="F55">
-        <v>2695.264342599149</v>
+        <v>2746.118386799133</v>
       </c>
       <c r="G55">
         <v>1145.9</v>
@@ -6038,28 +6038,28 @@
         <v>670.1</v>
       </c>
       <c r="M55">
-        <v>215.4351142438271</v>
+        <v>219.4999277201257</v>
       </c>
       <c r="N55">
-        <v>454.6648857561729</v>
+        <v>450.6000722798743</v>
       </c>
       <c r="O55">
-        <v>104.5729237239198</v>
+        <v>103.6380166243711</v>
       </c>
       <c r="P55">
-        <v>350.0919620322532</v>
+        <v>346.9620556555032</v>
       </c>
       <c r="Q55">
-        <v>477.4919620322531</v>
+        <v>474.3620556555032</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1686865566483313</v>
+        <v>0.1710291305014434</v>
       </c>
       <c r="T55">
-        <v>1.901015948741407</v>
+        <v>1.937254821221289</v>
       </c>
       <c r="U55">
         <v>0.07993097776675759</v>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.110449298630066</v>
+        <v>3.052848385692472</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6084,22 +6084,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1119087005860817</v>
+        <v>0.115218187520834</v>
       </c>
       <c r="C56">
-        <v>2402.9399229798</v>
+        <v>2209.276832992536</v>
       </c>
       <c r="D56">
-        <v>4003.158309778933</v>
+        <v>3860.349263991653</v>
       </c>
       <c r="E56">
-        <v>247.3139668007379</v>
+        <v>298.1680110007219</v>
       </c>
       <c r="F56">
-        <v>2746.118386799133</v>
+        <v>2796.972430999117</v>
       </c>
       <c r="G56">
         <v>1145.9</v>
@@ -6120,45 +6120,45 @@
         <v>670.1</v>
       </c>
       <c r="M56">
-        <v>219.4999277201257</v>
+        <v>245.3811261582175</v>
       </c>
       <c r="N56">
-        <v>450.6000722798743</v>
+        <v>424.7188738417826</v>
       </c>
       <c r="O56">
-        <v>103.6380166243711</v>
+        <v>97.68534098360999</v>
       </c>
       <c r="P56">
-        <v>346.9620556555032</v>
+        <v>327.0335328581726</v>
       </c>
       <c r="Q56">
-        <v>474.3620556555032</v>
+        <v>454.4335328581726</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1710291305014434</v>
+        <v>0.1734758187480271</v>
       </c>
       <c r="T56">
-        <v>1.937254821221289</v>
+        <v>1.975104310255832</v>
       </c>
       <c r="U56">
-        <v>0.07993097776675759</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V56">
         <v>0.23</v>
       </c>
       <c r="W56">
-        <v>0.06154685288040335</v>
+        <v>0.06755285288040334</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.052848385692472</v>
+        <v>2.730853878174523</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6166,22 +6166,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.115218187520834</v>
+        <v>0.1152844344555863</v>
       </c>
       <c r="C57">
-        <v>2209.276832992536</v>
+        <v>2155.668086627763</v>
       </c>
       <c r="D57">
-        <v>3860.349263991653</v>
+        <v>3857.594561826865</v>
       </c>
       <c r="E57">
-        <v>298.1680110007219</v>
+        <v>349.0220552007063</v>
       </c>
       <c r="F57">
-        <v>2796.972430999117</v>
+        <v>2847.826475199101</v>
       </c>
       <c r="G57">
         <v>1145.9</v>
@@ -6202,28 +6202,28 @@
         <v>670.1</v>
       </c>
       <c r="M57">
-        <v>245.3811261582175</v>
+        <v>249.842601179276</v>
       </c>
       <c r="N57">
-        <v>424.7188738417826</v>
+        <v>420.257398820724</v>
       </c>
       <c r="O57">
-        <v>97.68534098360999</v>
+        <v>96.65920172876652</v>
       </c>
       <c r="P57">
-        <v>327.0335328581726</v>
+        <v>323.5981970919575</v>
       </c>
       <c r="Q57">
-        <v>454.4335328581726</v>
+        <v>450.9981970919575</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1734758187480271</v>
+        <v>0.1760337200967283</v>
       </c>
       <c r="T57">
-        <v>1.975104310255832</v>
+        <v>2.014674230610128</v>
       </c>
       <c r="U57">
         <v>0.08773097776675759</v>
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.730853878174523</v>
+        <v>2.682088630349977</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6248,22 +6248,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1152844344555863</v>
+        <v>0.1153506813903386</v>
       </c>
       <c r="C58">
-        <v>2155.668086627763</v>
+        <v>2102.063268909015</v>
       </c>
       <c r="D58">
-        <v>3857.594561826865</v>
+        <v>3854.8437883081</v>
       </c>
       <c r="E58">
-        <v>349.0220552007063</v>
+        <v>399.8760994006902</v>
       </c>
       <c r="F58">
-        <v>2847.826475199101</v>
+        <v>2898.680519399085</v>
       </c>
       <c r="G58">
         <v>1145.9</v>
@@ -6284,28 +6284,28 @@
         <v>670.1</v>
       </c>
       <c r="M58">
-        <v>249.842601179276</v>
+        <v>254.3040762003345</v>
       </c>
       <c r="N58">
-        <v>420.257398820724</v>
+        <v>415.7959237996655</v>
       </c>
       <c r="O58">
-        <v>96.65920172876652</v>
+        <v>95.63306247392308</v>
       </c>
       <c r="P58">
-        <v>323.5981970919575</v>
+        <v>320.1628613257424</v>
       </c>
       <c r="Q58">
-        <v>450.9981970919575</v>
+        <v>447.5628613257424</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1760337200967283</v>
+        <v>0.178710593601183</v>
       </c>
       <c r="T58">
-        <v>2.014674230610128</v>
+        <v>2.056084612376251</v>
       </c>
       <c r="U58">
         <v>0.08773097776675759</v>
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.682088630349977</v>
+        <v>2.635034443852609</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6330,22 +6330,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1153506813903386</v>
+        <v>0.1154169283250909</v>
       </c>
       <c r="C59">
-        <v>2102.063268909015</v>
+        <v>2048.462371437961</v>
       </c>
       <c r="D59">
-        <v>3854.8437883081</v>
+        <v>3852.09693503703</v>
       </c>
       <c r="E59">
-        <v>399.8760994006902</v>
+        <v>450.7301436006742</v>
       </c>
       <c r="F59">
-        <v>2898.680519399085</v>
+        <v>2949.534563599069</v>
       </c>
       <c r="G59">
         <v>1145.9</v>
@@ -6366,28 +6366,28 @@
         <v>670.1</v>
       </c>
       <c r="M59">
-        <v>254.3040762003345</v>
+        <v>258.765551221393</v>
       </c>
       <c r="N59">
-        <v>415.7959237996655</v>
+        <v>411.334448778607</v>
       </c>
       <c r="O59">
-        <v>95.63306247392308</v>
+        <v>94.60692321907962</v>
       </c>
       <c r="P59">
-        <v>320.1628613257424</v>
+        <v>316.7275255595274</v>
       </c>
       <c r="Q59">
-        <v>447.5628613257424</v>
+        <v>444.1275255595274</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.178710593601183</v>
+        <v>0.1815149372725165</v>
       </c>
       <c r="T59">
-        <v>2.056084612376251</v>
+        <v>2.099466917083618</v>
       </c>
       <c r="U59">
         <v>0.08773097776675759</v>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.635034443852609</v>
+        <v>2.589602815510323</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6412,22 +6412,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1154169283250909</v>
+        <v>0.1154831752598431</v>
       </c>
       <c r="C60">
-        <v>2048.46237143796</v>
+        <v>1994.865385840195</v>
       </c>
       <c r="D60">
-        <v>3852.096935037029</v>
+        <v>3849.353993639247</v>
       </c>
       <c r="E60">
-        <v>450.7301436006737</v>
+        <v>501.5841878006577</v>
       </c>
       <c r="F60">
-        <v>2949.534563599069</v>
+        <v>3000.388607799053</v>
       </c>
       <c r="G60">
         <v>1145.9</v>
@@ -6448,28 +6448,28 @@
         <v>670.1</v>
       </c>
       <c r="M60">
-        <v>258.765551221393</v>
+        <v>263.2270262424515</v>
       </c>
       <c r="N60">
-        <v>411.3344487786071</v>
+        <v>406.8729737575486</v>
       </c>
       <c r="O60">
-        <v>94.60692321907963</v>
+        <v>93.58078396423618</v>
       </c>
       <c r="P60">
-        <v>316.7275255595274</v>
+        <v>313.2921897933124</v>
       </c>
       <c r="Q60">
-        <v>444.1275255595274</v>
+        <v>440.6921897933124</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1815149372725165</v>
+        <v>0.1844560781961102</v>
       </c>
       <c r="T60">
-        <v>2.099466917083618</v>
+        <v>2.14496543177671</v>
       </c>
       <c r="U60">
         <v>0.08773097776675759</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.589602815510323</v>
+        <v>2.545711242366081</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6494,22 +6494,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1154831752598431</v>
+        <v>0.1155494221945954</v>
       </c>
       <c r="C61">
-        <v>1994.865385840195</v>
+        <v>1941.272303765144</v>
       </c>
       <c r="D61">
-        <v>3849.353993639247</v>
+        <v>3846.614955764181</v>
       </c>
       <c r="E61">
-        <v>501.5841878006577</v>
+        <v>552.4382320006416</v>
       </c>
       <c r="F61">
-        <v>3000.388607799053</v>
+        <v>3051.242651999037</v>
       </c>
       <c r="G61">
         <v>1145.9</v>
@@ -6530,28 +6530,28 @@
         <v>670.1</v>
       </c>
       <c r="M61">
-        <v>263.2270262424515</v>
+        <v>267.68850126351</v>
       </c>
       <c r="N61">
-        <v>406.8729737575486</v>
+        <v>402.41149873649</v>
       </c>
       <c r="O61">
-        <v>93.58078396423618</v>
+        <v>92.55464470939272</v>
       </c>
       <c r="P61">
-        <v>313.2921897933124</v>
+        <v>309.8568540270973</v>
       </c>
       <c r="Q61">
-        <v>440.6921897933124</v>
+        <v>437.2568540270973</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1844560781961102</v>
+        <v>0.1875442761658835</v>
       </c>
       <c r="T61">
-        <v>2.14496543177671</v>
+        <v>2.192738872204457</v>
       </c>
       <c r="U61">
         <v>0.08773097776675759</v>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.545711242366081</v>
+        <v>2.503282721659979</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6576,22 +6576,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1155494221945954</v>
+        <v>0.1174474991293477</v>
       </c>
       <c r="C62">
-        <v>1941.272303765144</v>
+        <v>1813.563297788368</v>
       </c>
       <c r="D62">
-        <v>3846.614955764181</v>
+        <v>3769.759993987388</v>
       </c>
       <c r="E62">
-        <v>552.4382320006416</v>
+        <v>603.2922762006256</v>
       </c>
       <c r="F62">
-        <v>3051.242651999037</v>
+        <v>3102.096696199021</v>
       </c>
       <c r="G62">
         <v>1145.9</v>
@@ -6612,45 +6612,45 @@
         <v>670.1</v>
       </c>
       <c r="M62">
-        <v>267.68850126351</v>
+        <v>284.2481533997446</v>
       </c>
       <c r="N62">
-        <v>402.41149873649</v>
+        <v>385.8518466002554</v>
       </c>
       <c r="O62">
-        <v>92.55464470939272</v>
+        <v>88.74592471805876</v>
       </c>
       <c r="P62">
-        <v>309.8568540270973</v>
+        <v>297.1059218821967</v>
       </c>
       <c r="Q62">
-        <v>437.2568540270973</v>
+        <v>424.5059218821967</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1875442761658835</v>
+        <v>0.190790843262312</v>
       </c>
       <c r="T62">
-        <v>2.192738872204457</v>
+        <v>2.24296223265414</v>
       </c>
       <c r="U62">
-        <v>0.08773097776675759</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V62">
         <v>0.23</v>
       </c>
       <c r="W62">
-        <v>0.06755285288040334</v>
+        <v>0.07055585288040334</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.503282721659979</v>
+        <v>2.357447153078329</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6658,22 +6658,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1174474991293477</v>
+        <v>0.1175437760641</v>
       </c>
       <c r="C63">
-        <v>1813.563297788368</v>
+        <v>1758.892664298146</v>
       </c>
       <c r="D63">
-        <v>3769.759993987388</v>
+        <v>3765.94340469715</v>
       </c>
       <c r="E63">
-        <v>603.2922762006256</v>
+        <v>654.1463204006095</v>
       </c>
       <c r="F63">
-        <v>3102.096696199021</v>
+        <v>3152.950740399005</v>
       </c>
       <c r="G63">
         <v>1145.9</v>
@@ -6694,28 +6694,28 @@
         <v>670.1</v>
       </c>
       <c r="M63">
-        <v>284.2481533997446</v>
+        <v>288.907959193183</v>
       </c>
       <c r="N63">
-        <v>385.8518466002554</v>
+        <v>381.192040806817</v>
       </c>
       <c r="O63">
-        <v>88.74592471805876</v>
+        <v>87.67416938556791</v>
       </c>
       <c r="P63">
-        <v>297.1059218821967</v>
+        <v>293.5178714212491</v>
       </c>
       <c r="Q63">
-        <v>424.5059218821967</v>
+        <v>420.9178714212491</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.190790843262312</v>
+        <v>0.194208282311184</v>
       </c>
       <c r="T63">
-        <v>2.24296223265414</v>
+        <v>2.295828927864332</v>
       </c>
       <c r="U63">
         <v>0.09163097776675758</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.357447153078329</v>
+        <v>2.319423811899646</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6740,22 +6740,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1175437760641</v>
+        <v>0.1176400529988523</v>
       </c>
       <c r="C64">
-        <v>1758.892664298146</v>
+        <v>1704.229750992469</v>
       </c>
       <c r="D64">
-        <v>3765.94340469715</v>
+        <v>3762.134535591458</v>
       </c>
       <c r="E64">
-        <v>654.1463204006095</v>
+        <v>705.0003646005935</v>
       </c>
       <c r="F64">
-        <v>3152.950740399005</v>
+        <v>3203.804784598989</v>
       </c>
       <c r="G64">
         <v>1145.9</v>
@@ -6776,28 +6776,28 @@
         <v>670.1</v>
       </c>
       <c r="M64">
-        <v>288.907959193183</v>
+        <v>293.5677649866215</v>
       </c>
       <c r="N64">
-        <v>381.192040806817</v>
+        <v>376.5322350133786</v>
       </c>
       <c r="O64">
-        <v>87.67416938556791</v>
+        <v>86.60241405307707</v>
       </c>
       <c r="P64">
-        <v>293.5178714212491</v>
+        <v>289.9298209603015</v>
       </c>
       <c r="Q64">
-        <v>420.9178714212491</v>
+        <v>417.3298209603015</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.194208282311184</v>
+        <v>0.1978104477951302</v>
       </c>
       <c r="T64">
-        <v>2.295828927864332</v>
+        <v>2.351553282275075</v>
       </c>
       <c r="U64">
         <v>0.09163097776675758</v>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.319423811899646</v>
+        <v>2.282607560917112</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6822,22 +6822,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1176400529988523</v>
+        <v>0.1177363299336045</v>
       </c>
       <c r="C65">
-        <v>1704.229750992469</v>
+        <v>1649.57453447046</v>
       </c>
       <c r="D65">
-        <v>3762.134535591458</v>
+        <v>3758.333363269433</v>
       </c>
       <c r="E65">
-        <v>705.0003646005935</v>
+        <v>755.8544088005774</v>
       </c>
       <c r="F65">
-        <v>3203.804784598989</v>
+        <v>3254.658828798973</v>
       </c>
       <c r="G65">
         <v>1145.9</v>
@@ -6858,28 +6858,28 @@
         <v>670.1</v>
       </c>
       <c r="M65">
-        <v>293.5677649866215</v>
+        <v>298.2275707800599</v>
       </c>
       <c r="N65">
-        <v>376.5322350133786</v>
+        <v>371.8724292199401</v>
       </c>
       <c r="O65">
-        <v>86.60241405307707</v>
+        <v>85.53065872058623</v>
       </c>
       <c r="P65">
-        <v>289.9298209603015</v>
+        <v>286.3417704993539</v>
       </c>
       <c r="Q65">
-        <v>417.3298209603015</v>
+        <v>413.7417704993538</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1978104477951302</v>
+        <v>0.20161273358374</v>
       </c>
       <c r="T65">
-        <v>2.351553282275075</v>
+        <v>2.410373434153082</v>
       </c>
       <c r="U65">
         <v>0.09163097776675758</v>
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.282607560917112</v>
+        <v>2.246941817777782</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6904,22 +6904,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1177363299336045</v>
+        <v>0.1178326068683568</v>
       </c>
       <c r="C66">
-        <v>1649.57453447046</v>
+        <v>1594.926991425717</v>
       </c>
       <c r="D66">
-        <v>3758.333363269433</v>
+        <v>3754.539864424674</v>
       </c>
       <c r="E66">
-        <v>755.8544088005774</v>
+        <v>806.7084530005613</v>
       </c>
       <c r="F66">
-        <v>3254.658828798973</v>
+        <v>3305.512872998956</v>
       </c>
       <c r="G66">
         <v>1145.9</v>
@@ -6940,28 +6940,28 @@
         <v>670.1</v>
       </c>
       <c r="M66">
-        <v>298.2275707800599</v>
+        <v>302.8873765734983</v>
       </c>
       <c r="N66">
-        <v>371.8724292199401</v>
+        <v>367.2126234265017</v>
       </c>
       <c r="O66">
-        <v>85.53065872058623</v>
+        <v>84.45890338809539</v>
       </c>
       <c r="P66">
-        <v>286.3417704993539</v>
+        <v>282.7537200384063</v>
       </c>
       <c r="Q66">
-        <v>413.7417704993538</v>
+        <v>410.1537200384063</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.20161273358374</v>
+        <v>0.2056322928459847</v>
       </c>
       <c r="T66">
-        <v>2.410373434153082</v>
+        <v>2.472554737566975</v>
       </c>
       <c r="U66">
         <v>0.09163097776675758</v>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.246941817777782</v>
+        <v>2.212373482119663</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6986,22 +6986,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1178326068683568</v>
+        <v>0.1179288838031091</v>
       </c>
       <c r="C67">
-        <v>1594.926991425717</v>
+        <v>1540.287098645846</v>
       </c>
       <c r="D67">
-        <v>3754.539864424674</v>
+        <v>3750.754015844785</v>
       </c>
       <c r="E67">
-        <v>806.7084530005613</v>
+        <v>857.5624972005453</v>
       </c>
       <c r="F67">
-        <v>3305.512872998956</v>
+        <v>3356.36691719894</v>
       </c>
       <c r="G67">
         <v>1145.9</v>
@@ -7022,28 +7022,28 @@
         <v>670.1</v>
       </c>
       <c r="M67">
-        <v>302.8873765734983</v>
+        <v>307.5471823669368</v>
       </c>
       <c r="N67">
-        <v>367.2126234265017</v>
+        <v>362.5528176330632</v>
       </c>
       <c r="O67">
-        <v>84.45890338809539</v>
+        <v>83.38714805560454</v>
       </c>
       <c r="P67">
-        <v>282.7537200384063</v>
+        <v>279.1656695774587</v>
       </c>
       <c r="Q67">
-        <v>410.1537200384063</v>
+        <v>406.5656695774587</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2056322928459847</v>
+        <v>0.2098882967707144</v>
       </c>
       <c r="T67">
-        <v>2.472554737566975</v>
+        <v>2.538393764711097</v>
       </c>
       <c r="U67">
         <v>0.09163097776675758</v>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.212373482119663</v>
+        <v>2.178852671784516</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7068,22 +7068,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1179288838031091</v>
+        <v>0.1180251607378613</v>
       </c>
       <c r="C68">
-        <v>1540.287098645846</v>
+        <v>1485.654833011976</v>
       </c>
       <c r="D68">
-        <v>3750.754015844785</v>
+        <v>3746.975794410901</v>
       </c>
       <c r="E68">
-        <v>857.5624972005453</v>
+        <v>908.4165414005292</v>
       </c>
       <c r="F68">
-        <v>3356.36691719894</v>
+        <v>3407.220961398924</v>
       </c>
       <c r="G68">
         <v>1145.9</v>
@@ -7104,28 +7104,28 @@
         <v>670.1</v>
       </c>
       <c r="M68">
-        <v>307.5471823669368</v>
+        <v>312.2069881603752</v>
       </c>
       <c r="N68">
-        <v>362.5528176330632</v>
+        <v>357.8930118396248</v>
       </c>
       <c r="O68">
-        <v>83.38714805560454</v>
+        <v>82.31539272311372</v>
       </c>
       <c r="P68">
-        <v>279.1656695774587</v>
+        <v>275.5776191165111</v>
       </c>
       <c r="Q68">
-        <v>406.5656695774587</v>
+        <v>402.9776191165111</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2098882967707144</v>
+        <v>0.2144022403272458</v>
       </c>
       <c r="T68">
-        <v>2.538393764711097</v>
+        <v>2.608223035924559</v>
       </c>
       <c r="U68">
         <v>0.09163097776675758</v>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.178852671784516</v>
+        <v>2.146332482653404</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7150,22 +7150,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1180251607378613</v>
+        <v>0.1181214376726136</v>
       </c>
       <c r="C69">
-        <v>1485.654833011976</v>
+        <v>1431.0301714983</v>
       </c>
       <c r="D69">
-        <v>3746.975794410901</v>
+        <v>3743.205177097209</v>
       </c>
       <c r="E69">
-        <v>908.4165414005292</v>
+        <v>959.2705856005136</v>
       </c>
       <c r="F69">
-        <v>3407.220961398924</v>
+        <v>3458.075005598909</v>
       </c>
       <c r="G69">
         <v>1145.9</v>
@@ -7186,28 +7186,28 @@
         <v>670.1</v>
       </c>
       <c r="M69">
-        <v>312.2069881603752</v>
+        <v>316.8667939538137</v>
       </c>
       <c r="N69">
-        <v>357.8930118396248</v>
+        <v>353.2332060461864</v>
       </c>
       <c r="O69">
-        <v>82.31539272311372</v>
+        <v>81.24363739062287</v>
       </c>
       <c r="P69">
-        <v>275.5776191165111</v>
+        <v>271.9895686555635</v>
       </c>
       <c r="Q69">
-        <v>402.9776191165111</v>
+        <v>399.3895686555635</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2144022403272458</v>
+        <v>0.2191983053560606</v>
       </c>
       <c r="T69">
-        <v>2.608223035924559</v>
+        <v>2.682416636588863</v>
       </c>
       <c r="U69">
         <v>0.09163097776675758</v>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.146332482653404</v>
+        <v>2.114768769673207</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7232,22 +7232,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1181214376726136</v>
+        <v>0.1182177146073659</v>
       </c>
       <c r="C70">
-        <v>1431.0301714983</v>
+        <v>1376.413091171602</v>
       </c>
       <c r="D70">
-        <v>3743.205177097209</v>
+        <v>3739.442140970495</v>
       </c>
       <c r="E70">
-        <v>959.2705856005136</v>
+        <v>1010.124629800498</v>
       </c>
       <c r="F70">
-        <v>3458.075005598909</v>
+        <v>3508.929049798893</v>
       </c>
       <c r="G70">
         <v>1145.9</v>
@@ -7268,28 +7268,28 @@
         <v>670.1</v>
       </c>
       <c r="M70">
-        <v>316.8667939538137</v>
+        <v>321.5265997472521</v>
       </c>
       <c r="N70">
-        <v>353.2332060461864</v>
+        <v>348.5734002527479</v>
       </c>
       <c r="O70">
-        <v>81.24363739062287</v>
+        <v>80.17188205813201</v>
       </c>
       <c r="P70">
-        <v>271.9895686555635</v>
+        <v>268.4015181946158</v>
       </c>
       <c r="Q70">
-        <v>399.3895686555635</v>
+        <v>395.8015181946158</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2191983053560606</v>
+        <v>0.2243037939351214</v>
       </c>
       <c r="T70">
-        <v>2.682416636588863</v>
+        <v>2.761396921166994</v>
       </c>
       <c r="U70">
         <v>0.09163097776675758</v>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.114768769673207</v>
+        <v>2.08411994692432</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7314,22 +7314,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1182177146073659</v>
+        <v>0.1183139915421182</v>
       </c>
       <c r="C71">
-        <v>1376.413091171602</v>
+        <v>1321.803569190792</v>
       </c>
       <c r="D71">
-        <v>3739.442140970495</v>
+        <v>3735.686663189669</v>
       </c>
       <c r="E71">
-        <v>1010.124629800498</v>
+        <v>1060.978674000482</v>
       </c>
       <c r="F71">
-        <v>3508.929049798893</v>
+        <v>3559.783093998877</v>
       </c>
       <c r="G71">
         <v>1145.9</v>
@@ -7350,28 +7350,28 @@
         <v>670.1</v>
       </c>
       <c r="M71">
-        <v>321.5265997472521</v>
+        <v>326.1864055406905</v>
       </c>
       <c r="N71">
-        <v>348.5734002527479</v>
+        <v>343.9135944593095</v>
       </c>
       <c r="O71">
-        <v>80.17188205813201</v>
+        <v>79.10012672564119</v>
       </c>
       <c r="P71">
-        <v>268.4015181946158</v>
+        <v>264.8134677336683</v>
       </c>
       <c r="Q71">
-        <v>395.8015181946158</v>
+        <v>392.2134677336683</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2243037939351214</v>
+        <v>0.2297496484194529</v>
       </c>
       <c r="T71">
-        <v>2.761396921166994</v>
+        <v>2.845642558050332</v>
       </c>
       <c r="U71">
         <v>0.09163097776675758</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.08411994692432</v>
+        <v>2.054346804825401</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7396,22 +7396,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1183139915421182</v>
+        <v>0.1184102684768705</v>
       </c>
       <c r="C72">
-        <v>1321.803569190792</v>
+        <v>1267.201582806442</v>
       </c>
       <c r="D72">
-        <v>3735.686663189669</v>
+        <v>3731.938721005302</v>
       </c>
       <c r="E72">
-        <v>1060.978674000482</v>
+        <v>1111.832718200465</v>
       </c>
       <c r="F72">
-        <v>3559.783093998877</v>
+        <v>3610.637138198861</v>
       </c>
       <c r="G72">
         <v>1145.9</v>
@@ -7432,28 +7432,28 @@
         <v>670.1</v>
       </c>
       <c r="M72">
-        <v>326.1864055406905</v>
+        <v>330.846211334129</v>
       </c>
       <c r="N72">
-        <v>343.9135944593095</v>
+        <v>339.253788665871</v>
       </c>
       <c r="O72">
-        <v>79.10012672564119</v>
+        <v>78.02837139315034</v>
       </c>
       <c r="P72">
-        <v>264.8134677336683</v>
+        <v>261.2254172727207</v>
       </c>
       <c r="Q72">
-        <v>392.2134677336683</v>
+        <v>388.6254172727207</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2297496484194529</v>
+        <v>0.2355710790751177</v>
       </c>
       <c r="T72">
-        <v>2.845642558050332</v>
+        <v>2.93569823885666</v>
       </c>
       <c r="U72">
         <v>0.09163097776675758</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.054346804825401</v>
+        <v>2.025412342785606</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7478,22 +7478,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1184102684768705</v>
+        <v>0.1263790254116227</v>
       </c>
       <c r="C73">
-        <v>1267.201582806441</v>
+        <v>930.2062618117361</v>
       </c>
       <c r="D73">
-        <v>3731.938721005301</v>
+        <v>3445.79744421058</v>
       </c>
       <c r="E73">
-        <v>1111.832718200465</v>
+        <v>1162.686762400449</v>
       </c>
       <c r="F73">
-        <v>3610.63713819886</v>
+        <v>3661.491182398844</v>
       </c>
       <c r="G73">
         <v>1145.9</v>
@@ -7514,45 +7514,45 @@
         <v>670.1</v>
       </c>
       <c r="M73">
-        <v>330.846211334129</v>
+        <v>387.499191917631</v>
       </c>
       <c r="N73">
-        <v>339.2537886658711</v>
+        <v>282.600808082369</v>
       </c>
       <c r="O73">
-        <v>78.02837139315035</v>
+        <v>64.99818585894488</v>
       </c>
       <c r="P73">
-        <v>261.2254172727207</v>
+        <v>217.6026222234242</v>
       </c>
       <c r="Q73">
-        <v>388.6254172727207</v>
+        <v>345.0026222234242</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2355710790751176</v>
+        <v>0.2418083262061869</v>
       </c>
       <c r="T73">
-        <v>2.935698238856659</v>
+        <v>3.032186468292009</v>
       </c>
       <c r="U73">
-        <v>0.09163097776675758</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V73">
         <v>0.23</v>
       </c>
       <c r="W73">
-        <v>0.07055585288040334</v>
+        <v>0.08148985288040334</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.025412342785606</v>
+        <v>1.729293928804993</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7560,22 +7560,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1263790254116227</v>
+        <v>0.126584642346375</v>
       </c>
       <c r="C74">
-        <v>930.2062618117361</v>
+        <v>872.5485092101881</v>
       </c>
       <c r="D74">
-        <v>3445.79744421058</v>
+        <v>3438.993735809016</v>
       </c>
       <c r="E74">
-        <v>1162.686762400449</v>
+        <v>1213.540806600433</v>
       </c>
       <c r="F74">
-        <v>3661.491182398844</v>
+        <v>3712.345226598828</v>
       </c>
       <c r="G74">
         <v>1145.9</v>
@@ -7596,28 +7596,28 @@
         <v>670.1</v>
       </c>
       <c r="M74">
-        <v>387.499191917631</v>
+        <v>392.8811251387092</v>
       </c>
       <c r="N74">
-        <v>282.600808082369</v>
+        <v>277.2188748612908</v>
       </c>
       <c r="O74">
-        <v>64.99818585894488</v>
+        <v>63.76034121809689</v>
       </c>
       <c r="P74">
-        <v>217.6026222234242</v>
+        <v>213.4585336431939</v>
       </c>
       <c r="Q74">
-        <v>345.0026222234242</v>
+        <v>340.8585336431939</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2418083262061869</v>
+        <v>0.2485075916432614</v>
       </c>
       <c r="T74">
-        <v>3.032186468292009</v>
+        <v>3.135821973981831</v>
       </c>
       <c r="U74">
         <v>0.1058309777667576</v>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.729293928804993</v>
+        <v>1.705604970876157</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7642,22 +7642,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.126584642346375</v>
+        <v>0.1267902592811273</v>
       </c>
       <c r="C75">
-        <v>872.5485092101881</v>
+        <v>814.9175714337362</v>
       </c>
       <c r="D75">
-        <v>3438.993735809016</v>
+        <v>3432.216842232548</v>
       </c>
       <c r="E75">
-        <v>1213.540806600433</v>
+        <v>1264.394850800417</v>
       </c>
       <c r="F75">
-        <v>3712.345226598828</v>
+        <v>3763.199270798812</v>
       </c>
       <c r="G75">
         <v>1145.9</v>
@@ -7678,28 +7678,28 @@
         <v>670.1</v>
       </c>
       <c r="M75">
-        <v>392.8811251387092</v>
+        <v>398.2630583597874</v>
       </c>
       <c r="N75">
-        <v>277.2188748612908</v>
+        <v>271.8369416402126</v>
       </c>
       <c r="O75">
-        <v>63.76034121809689</v>
+        <v>62.5224965772489</v>
       </c>
       <c r="P75">
-        <v>213.4585336431939</v>
+        <v>209.3144450629637</v>
       </c>
       <c r="Q75">
-        <v>340.8585336431939</v>
+        <v>336.7144450629637</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2485075916432614</v>
+        <v>0.2557221851908801</v>
       </c>
       <c r="T75">
-        <v>3.135821973981831</v>
+        <v>3.247429441647792</v>
       </c>
       <c r="U75">
         <v>0.1058309777667576</v>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.705604970876157</v>
+        <v>1.682556255053507</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7724,22 +7724,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1267902592811273</v>
+        <v>0.1269958762158796</v>
       </c>
       <c r="C76">
-        <v>814.9175714337362</v>
+        <v>757.3132902699754</v>
       </c>
       <c r="D76">
-        <v>3432.216842232548</v>
+        <v>3425.466605268771</v>
       </c>
       <c r="E76">
-        <v>1264.394850800417</v>
+        <v>1315.248895000401</v>
       </c>
       <c r="F76">
-        <v>3763.199270798812</v>
+        <v>3814.053314998796</v>
       </c>
       <c r="G76">
         <v>1145.9</v>
@@ -7760,28 +7760,28 @@
         <v>670.1</v>
       </c>
       <c r="M76">
-        <v>398.2630583597874</v>
+        <v>403.6449915808656</v>
       </c>
       <c r="N76">
-        <v>271.8369416402126</v>
+        <v>266.4550084191344</v>
       </c>
       <c r="O76">
-        <v>62.5224965772489</v>
+        <v>61.28465193640091</v>
       </c>
       <c r="P76">
-        <v>209.3144450629637</v>
+        <v>205.1703564827335</v>
       </c>
       <c r="Q76">
-        <v>336.7144450629637</v>
+        <v>332.5703564827335</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2557221851908801</v>
+        <v>0.2635139462223083</v>
       </c>
       <c r="T76">
-        <v>3.247429441647792</v>
+        <v>3.367965506727031</v>
       </c>
       <c r="U76">
         <v>0.1058309777667576</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.682556255053507</v>
+        <v>1.660122171652793</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7806,22 +7806,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1269958762158796</v>
+        <v>0.1272014931506319</v>
       </c>
       <c r="C77">
-        <v>757.3132902699754</v>
+        <v>699.7355087487049</v>
       </c>
       <c r="D77">
-        <v>3425.466605268771</v>
+        <v>3418.742867947485</v>
       </c>
       <c r="E77">
-        <v>1315.248895000401</v>
+        <v>1366.102939200385</v>
       </c>
       <c r="F77">
-        <v>3814.053314998796</v>
+        <v>3864.90735919878</v>
       </c>
       <c r="G77">
         <v>1145.9</v>
@@ -7842,28 +7842,28 @@
         <v>670.1</v>
       </c>
       <c r="M77">
-        <v>403.6449915808656</v>
+        <v>409.0269248019438</v>
       </c>
       <c r="N77">
-        <v>266.4550084191344</v>
+        <v>261.0730751980562</v>
       </c>
       <c r="O77">
-        <v>61.28465193640091</v>
+        <v>60.04680729555292</v>
       </c>
       <c r="P77">
-        <v>205.1703564827335</v>
+        <v>201.0262679025033</v>
       </c>
       <c r="Q77">
-        <v>332.5703564827335</v>
+        <v>328.4262679025032</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2635139462223083</v>
+        <v>0.2719550206730222</v>
       </c>
       <c r="T77">
-        <v>3.367965506727031</v>
+        <v>3.498546243896206</v>
       </c>
       <c r="U77">
         <v>0.1058309777667576</v>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.660122171652793</v>
+        <v>1.638278458867888</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7888,22 +7888,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1272014931506319</v>
+        <v>0.1274071100853841</v>
       </c>
       <c r="C78">
-        <v>699.7355087487049</v>
+        <v>642.1840711297564</v>
       </c>
       <c r="D78">
-        <v>3418.742867947485</v>
+        <v>3412.04547452852</v>
       </c>
       <c r="E78">
-        <v>1366.102939200385</v>
+        <v>1416.956983400369</v>
       </c>
       <c r="F78">
-        <v>3864.90735919878</v>
+        <v>3915.761403398764</v>
       </c>
       <c r="G78">
         <v>1145.9</v>
@@ -7924,28 +7924,28 @@
         <v>670.1</v>
       </c>
       <c r="M78">
-        <v>409.0269248019438</v>
+        <v>414.408858023022</v>
       </c>
       <c r="N78">
-        <v>261.0730751980562</v>
+        <v>255.691141976978</v>
       </c>
       <c r="O78">
-        <v>60.04680729555292</v>
+        <v>58.80896265470493</v>
       </c>
       <c r="P78">
-        <v>201.0262679025033</v>
+        <v>196.882179322273</v>
       </c>
       <c r="Q78">
-        <v>328.4262679025032</v>
+        <v>324.282179322273</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2719550206730222</v>
+        <v>0.2811301015977112</v>
       </c>
       <c r="T78">
-        <v>3.498546243896206</v>
+        <v>3.640481827775745</v>
       </c>
       <c r="U78">
         <v>0.1058309777667576</v>
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.638278458867888</v>
+        <v>1.617002115246227</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7970,22 +7970,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1274071100853841</v>
+        <v>0.1276127270201364</v>
       </c>
       <c r="C79">
-        <v>642.1840711297564</v>
+        <v>584.6588228909641</v>
       </c>
       <c r="D79">
-        <v>3412.04547452852</v>
+        <v>3405.374270489712</v>
       </c>
       <c r="E79">
-        <v>1416.956983400369</v>
+        <v>1467.811027600353</v>
       </c>
       <c r="F79">
-        <v>3915.761403398764</v>
+        <v>3966.615447598748</v>
       </c>
       <c r="G79">
         <v>1145.9</v>
@@ -8006,28 +8006,28 @@
         <v>670.1</v>
       </c>
       <c r="M79">
-        <v>414.408858023022</v>
+        <v>419.7907912441003</v>
       </c>
       <c r="N79">
-        <v>255.691141976978</v>
+        <v>250.3092087558998</v>
       </c>
       <c r="O79">
-        <v>58.80896265470493</v>
+        <v>57.57111801385695</v>
       </c>
       <c r="P79">
-        <v>196.882179322273</v>
+        <v>192.7380907420428</v>
       </c>
       <c r="Q79">
-        <v>324.282179322273</v>
+        <v>320.1380907420428</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2811301015977112</v>
+        <v>0.2911392807882811</v>
       </c>
       <c r="T79">
-        <v>3.640481827775745</v>
+        <v>3.795320646553423</v>
       </c>
       <c r="U79">
         <v>0.1058309777667576</v>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.617002115246227</v>
+        <v>1.596271318896916</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8052,22 +8052,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1276127270201364</v>
+        <v>0.1278183439548887</v>
       </c>
       <c r="C80">
-        <v>584.6588228909641</v>
+        <v>527.1596107162959</v>
       </c>
       <c r="D80">
-        <v>3405.374270489712</v>
+        <v>3398.729102515027</v>
       </c>
       <c r="E80">
-        <v>1467.811027600353</v>
+        <v>1518.665071800337</v>
       </c>
       <c r="F80">
-        <v>3966.615447598748</v>
+        <v>4017.469491798732</v>
       </c>
       <c r="G80">
         <v>1145.9</v>
@@ -8088,28 +8088,28 @@
         <v>670.1</v>
       </c>
       <c r="M80">
-        <v>419.7907912441003</v>
+        <v>425.1727244651785</v>
       </c>
       <c r="N80">
-        <v>250.3092087558998</v>
+        <v>244.9272755348215</v>
       </c>
       <c r="O80">
-        <v>57.57111801385695</v>
+        <v>56.33327337300896</v>
       </c>
       <c r="P80">
-        <v>192.7380907420428</v>
+        <v>188.5940021618126</v>
       </c>
       <c r="Q80">
-        <v>320.1380907420428</v>
+        <v>315.9940021618125</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2911392807882811</v>
+        <v>0.3021017151398575</v>
       </c>
       <c r="T80">
-        <v>3.795320646553423</v>
+        <v>3.964906019500403</v>
       </c>
       <c r="U80">
         <v>0.1058309777667576</v>
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.596271318896916</v>
+        <v>1.57606535283493</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8134,22 +8134,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1278183439548887</v>
+        <v>0.128023960889641</v>
       </c>
       <c r="C81">
-        <v>527.1596107162959</v>
+        <v>469.6862824840864</v>
       </c>
       <c r="D81">
-        <v>3398.729102515027</v>
+        <v>3392.109818482802</v>
       </c>
       <c r="E81">
-        <v>1518.665071800337</v>
+        <v>1569.519116000321</v>
       </c>
       <c r="F81">
-        <v>4017.469491798732</v>
+        <v>4068.323535998716</v>
       </c>
       <c r="G81">
         <v>1145.9</v>
@@ -8170,28 +8170,28 @@
         <v>670.1</v>
       </c>
       <c r="M81">
-        <v>425.1727244651785</v>
+        <v>430.5546576862567</v>
       </c>
       <c r="N81">
-        <v>244.9272755348215</v>
+        <v>239.5453423137433</v>
       </c>
       <c r="O81">
-        <v>56.33327337300896</v>
+        <v>55.09542873216097</v>
       </c>
       <c r="P81">
-        <v>188.5940021618126</v>
+        <v>184.4499135815824</v>
       </c>
       <c r="Q81">
-        <v>315.9940021618125</v>
+        <v>311.8499135815823</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3021017151398575</v>
+        <v>0.3141603929265916</v>
       </c>
       <c r="T81">
-        <v>3.964906019500403</v>
+        <v>4.151449929742082</v>
       </c>
       <c r="U81">
         <v>0.1058309777667576</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.57606535283493</v>
+        <v>1.556364535924494</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8216,22 +8216,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.128023960889641</v>
+        <v>0.1282295778243933</v>
       </c>
       <c r="C82">
-        <v>469.6862824840864</v>
+        <v>412.2386872554525</v>
       </c>
       <c r="D82">
-        <v>3392.109818482802</v>
+        <v>3385.516267454152</v>
       </c>
       <c r="E82">
-        <v>1569.519116000321</v>
+        <v>1620.373160200304</v>
       </c>
       <c r="F82">
-        <v>4068.323535998716</v>
+        <v>4119.1775801987</v>
       </c>
       <c r="G82">
         <v>1145.9</v>
@@ -8252,28 +8252,28 @@
         <v>670.1</v>
       </c>
       <c r="M82">
-        <v>430.5546576862567</v>
+        <v>435.9365909073348</v>
       </c>
       <c r="N82">
-        <v>239.5453423137433</v>
+        <v>234.1634090926652</v>
       </c>
       <c r="O82">
-        <v>55.09542873216097</v>
+        <v>53.85758409131299</v>
       </c>
       <c r="P82">
-        <v>184.4499135815824</v>
+        <v>180.3058250013522</v>
       </c>
       <c r="Q82">
-        <v>311.8499135815823</v>
+        <v>307.7058250013522</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3141603929265916</v>
+        <v>0.3274884052171925</v>
       </c>
       <c r="T82">
-        <v>4.151449929742082</v>
+        <v>4.357630041061832</v>
       </c>
       <c r="U82">
         <v>0.1058309777667576</v>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.556364535924494</v>
+        <v>1.537150158937771</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8298,22 +8298,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1282295778243933</v>
+        <v>0.1284351947591455</v>
       </c>
       <c r="C83">
-        <v>412.2386872554525</v>
+        <v>354.8166752628003</v>
       </c>
       <c r="D83">
-        <v>3385.516267454152</v>
+        <v>3378.948299661483</v>
       </c>
       <c r="E83">
-        <v>1620.373160200304</v>
+        <v>1671.227204400288</v>
       </c>
       <c r="F83">
-        <v>4119.1775801987</v>
+        <v>4170.031624398684</v>
       </c>
       <c r="G83">
         <v>1145.9</v>
@@ -8334,28 +8334,28 @@
         <v>670.1</v>
       </c>
       <c r="M83">
-        <v>435.9365909073348</v>
+        <v>441.3185241284131</v>
       </c>
       <c r="N83">
-        <v>234.1634090926652</v>
+        <v>228.781475871587</v>
       </c>
       <c r="O83">
-        <v>53.85758409131299</v>
+        <v>52.619739450465</v>
       </c>
       <c r="P83">
-        <v>180.3058250013522</v>
+        <v>176.161736421122</v>
       </c>
       <c r="Q83">
-        <v>307.7058250013522</v>
+        <v>303.561736421122</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3274884052171925</v>
+        <v>0.3422973077623045</v>
       </c>
       <c r="T83">
-        <v>4.357630041061832</v>
+        <v>4.586719053639332</v>
       </c>
       <c r="U83">
         <v>0.1058309777667576</v>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.537150158937771</v>
+        <v>1.518404425292189</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8380,22 +8380,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1284351947591455</v>
+        <v>0.1286408116938978</v>
       </c>
       <c r="C84">
-        <v>354.8166752628003</v>
+        <v>297.4200978984954</v>
       </c>
       <c r="D84">
-        <v>3378.948299661483</v>
+        <v>3372.405766497163</v>
       </c>
       <c r="E84">
-        <v>1671.227204400288</v>
+        <v>1722.081248600272</v>
       </c>
       <c r="F84">
-        <v>4170.031624398684</v>
+        <v>4220.885668598668</v>
       </c>
       <c r="G84">
         <v>1145.9</v>
@@ -8416,28 +8416,28 @@
         <v>670.1</v>
       </c>
       <c r="M84">
-        <v>441.3185241284131</v>
+        <v>446.7004573494913</v>
       </c>
       <c r="N84">
-        <v>228.781475871587</v>
+        <v>223.3995426505087</v>
       </c>
       <c r="O84">
-        <v>52.619739450465</v>
+        <v>51.38189480961702</v>
       </c>
       <c r="P84">
-        <v>176.161736421122</v>
+        <v>172.0176478408917</v>
       </c>
       <c r="Q84">
-        <v>303.561736421122</v>
+        <v>299.4176478408917</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3422973077623045</v>
+        <v>0.3588484341362534</v>
       </c>
       <c r="T84">
-        <v>4.586719053639332</v>
+        <v>4.842759714755362</v>
       </c>
       <c r="U84">
         <v>0.1058309777667576</v>
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.518404425292189</v>
+        <v>1.500110396071801</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8462,22 +8462,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1286408116938978</v>
+        <v>0.1671483366274258</v>
       </c>
       <c r="C85">
-        <v>297.4200978984954</v>
+        <v>-650.8965187800709</v>
       </c>
       <c r="D85">
-        <v>3372.405766497163</v>
+        <v>2474.94319401858</v>
       </c>
       <c r="E85">
-        <v>1722.081248600272</v>
+        <v>1772.935292800256</v>
       </c>
       <c r="F85">
-        <v>4220.885668598668</v>
+        <v>4271.739712798651</v>
       </c>
       <c r="G85">
         <v>1145.9</v>
@@ -8498,45 +8498,45 @@
         <v>670.1</v>
       </c>
       <c r="M85">
-        <v>446.7004573494913</v>
+        <v>694.7172062575329</v>
       </c>
       <c r="N85">
-        <v>223.3995426505087</v>
+        <v>-24.61720625753287</v>
       </c>
       <c r="O85">
-        <v>51.38189480961702</v>
+        <v>-5.661957439232561</v>
       </c>
       <c r="P85">
-        <v>172.0176478408917</v>
+        <v>-18.95524881830031</v>
       </c>
       <c r="Q85">
-        <v>299.4176478408917</v>
+        <v>108.4447511816997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3588484341362534</v>
+        <v>0.3802827883340885</v>
       </c>
       <c r="T85">
-        <v>4.842759714755362</v>
+        <v>5.174342357254363</v>
       </c>
       <c r="U85">
-        <v>0.1058309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V85">
-        <v>0.23</v>
+        <v>0.2218499824270458</v>
       </c>
       <c r="W85">
-        <v>0.08148985288040334</v>
+        <v>0.1265512982071091</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.500110396071801</v>
+        <v>0.9645651409871555</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8544,22 +8544,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1671483366274258</v>
+        <v>0.1683166464050934</v>
       </c>
       <c r="C86">
-        <v>-650.8965187800704</v>
+        <v>-721.5732146231298</v>
       </c>
       <c r="D86">
-        <v>2474.943194018581</v>
+        <v>2455.120542375505</v>
       </c>
       <c r="E86">
-        <v>1772.935292800256</v>
+        <v>1823.78933700024</v>
       </c>
       <c r="F86">
-        <v>4271.739712798651</v>
+        <v>4322.593756998635</v>
       </c>
       <c r="G86">
         <v>1145.9</v>
@@ -8580,37 +8580,37 @@
         <v>670.1</v>
       </c>
       <c r="M86">
-        <v>694.7172062575329</v>
+        <v>702.9876491891702</v>
       </c>
       <c r="N86">
-        <v>-24.61720625753287</v>
+        <v>-32.88764918917013</v>
       </c>
       <c r="O86">
-        <v>-5.661957439232561</v>
+        <v>-7.564159313509131</v>
       </c>
       <c r="P86">
-        <v>-18.95524881830031</v>
+        <v>-25.323489875661</v>
       </c>
       <c r="Q86">
-        <v>108.4447511816997</v>
+        <v>102.076510124339</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3802827883340882</v>
+        <v>0.4025816408896941</v>
       </c>
       <c r="T86">
-        <v>5.17434235725436</v>
+        <v>5.51929851440465</v>
       </c>
       <c r="U86">
         <v>0.1626309777667576</v>
       </c>
       <c r="V86">
-        <v>0.2218499824270458</v>
+        <v>0.2192399826337864</v>
       </c>
       <c r="W86">
-        <v>0.1265512982071091</v>
+        <v>0.126975765025458</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9645651409871555</v>
+        <v>0.9532173157990714</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8626,22 +8626,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1683166464050934</v>
+        <v>0.169484956182761</v>
       </c>
       <c r="C87">
-        <v>-721.5732146231298</v>
+        <v>-791.9349009282428</v>
       </c>
       <c r="D87">
-        <v>2455.120542375505</v>
+        <v>2435.612900270376</v>
       </c>
       <c r="E87">
-        <v>1823.78933700024</v>
+        <v>1874.643381200224</v>
       </c>
       <c r="F87">
-        <v>4322.593756998635</v>
+        <v>4373.447801198619</v>
       </c>
       <c r="G87">
         <v>1145.9</v>
@@ -8662,37 +8662,37 @@
         <v>670.1</v>
       </c>
       <c r="M87">
-        <v>702.9876491891702</v>
+        <v>711.2580921208075</v>
       </c>
       <c r="N87">
-        <v>-32.88764918917013</v>
+        <v>-41.15809212080751</v>
       </c>
       <c r="O87">
-        <v>-7.564159313509131</v>
+        <v>-9.466361187785727</v>
       </c>
       <c r="P87">
-        <v>-25.323489875661</v>
+        <v>-31.69173093302178</v>
       </c>
       <c r="Q87">
-        <v>102.076510124339</v>
+        <v>95.7082690669782</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4025816408896941</v>
+        <v>0.4280660438103865</v>
       </c>
       <c r="T87">
-        <v>5.51929851440465</v>
+        <v>5.913534122576411</v>
       </c>
       <c r="U87">
         <v>0.1626309777667576</v>
       </c>
       <c r="V87">
-        <v>0.2192399826337864</v>
+        <v>0.2166906805101377</v>
       </c>
       <c r="W87">
-        <v>0.126975765025458</v>
+        <v>0.1273903605224498</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9532173157990714</v>
+        <v>0.9421333935223379</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8708,22 +8708,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.169484956182761</v>
+        <v>0.1706532659604285</v>
       </c>
       <c r="C88">
-        <v>-791.9349009282428</v>
+        <v>-861.9890274125405</v>
       </c>
       <c r="D88">
-        <v>2435.612900270376</v>
+        <v>2416.412817986063</v>
       </c>
       <c r="E88">
-        <v>1874.643381200224</v>
+        <v>1925.497425400208</v>
       </c>
       <c r="F88">
-        <v>4373.447801198619</v>
+        <v>4424.301845398603</v>
       </c>
       <c r="G88">
         <v>1145.9</v>
@@ -8744,37 +8744,37 @@
         <v>670.1</v>
       </c>
       <c r="M88">
-        <v>711.2580921208075</v>
+        <v>719.5285350524448</v>
       </c>
       <c r="N88">
-        <v>-41.15809212080751</v>
+        <v>-49.42853505244477</v>
       </c>
       <c r="O88">
-        <v>-9.466361187785727</v>
+        <v>-11.3685630620623</v>
       </c>
       <c r="P88">
-        <v>-31.69173093302178</v>
+        <v>-38.05997199038247</v>
       </c>
       <c r="Q88">
-        <v>95.7082690669782</v>
+        <v>89.3400280096175</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4280660438103865</v>
+        <v>0.4574711241034932</v>
       </c>
       <c r="T88">
-        <v>5.913534122576411</v>
+        <v>6.368421362774597</v>
       </c>
       <c r="U88">
         <v>0.1626309777667576</v>
       </c>
       <c r="V88">
-        <v>0.2166906805101377</v>
+        <v>0.2141999830330097</v>
       </c>
       <c r="W88">
-        <v>0.1273903605224498</v>
+        <v>0.1277954250884763</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9421333935223379</v>
+        <v>0.9313042740565639</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8790,22 +8790,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1706532659604285</v>
+        <v>0.1718215757380961</v>
       </c>
       <c r="C89">
-        <v>-861.9890274125405</v>
+        <v>-931.7428107241858</v>
       </c>
       <c r="D89">
-        <v>2416.412817986063</v>
+        <v>2397.513078874401</v>
       </c>
       <c r="E89">
-        <v>1925.497425400208</v>
+        <v>1976.351469600192</v>
       </c>
       <c r="F89">
-        <v>4424.301845398603</v>
+        <v>4475.155889598587</v>
       </c>
       <c r="G89">
         <v>1145.9</v>
@@ -8826,37 +8826,37 @@
         <v>670.1</v>
       </c>
       <c r="M89">
-        <v>719.5285350524448</v>
+        <v>727.7989779840821</v>
       </c>
       <c r="N89">
-        <v>-49.42853505244477</v>
+        <v>-57.69897798408203</v>
       </c>
       <c r="O89">
-        <v>-11.3685630620623</v>
+        <v>-13.27076493633887</v>
       </c>
       <c r="P89">
-        <v>-38.05997199038247</v>
+        <v>-44.42821304774316</v>
       </c>
       <c r="Q89">
-        <v>89.3400280096175</v>
+        <v>82.97178695225682</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4574711241034932</v>
+        <v>0.4917770511121178</v>
       </c>
       <c r="T89">
-        <v>6.368421362774597</v>
+        <v>6.899123143005815</v>
       </c>
       <c r="U89">
         <v>0.1626309777667576</v>
       </c>
       <c r="V89">
-        <v>0.2141999830330097</v>
+        <v>0.2117658923167255</v>
       </c>
       <c r="W89">
-        <v>0.1277954250884763</v>
+        <v>0.1281912836416386</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9313042740565639</v>
+        <v>0.9207212709422848</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8872,22 +8872,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1718215757380961</v>
+        <v>0.1729898855157637</v>
       </c>
       <c r="C90">
-        <v>-931.7428107241858</v>
+        <v>-1001.20324348627</v>
       </c>
       <c r="D90">
-        <v>2397.513078874401</v>
+        <v>2378.906690312301</v>
       </c>
       <c r="E90">
-        <v>1976.351469600192</v>
+        <v>2027.205513800176</v>
       </c>
       <c r="F90">
-        <v>4475.155889598587</v>
+        <v>4526.009933798571</v>
       </c>
       <c r="G90">
         <v>1145.9</v>
@@ -8908,37 +8908,37 @@
         <v>670.1</v>
       </c>
       <c r="M90">
-        <v>727.7989779840821</v>
+        <v>736.0694209157194</v>
       </c>
       <c r="N90">
-        <v>-57.69897798408203</v>
+        <v>-65.96942091571941</v>
       </c>
       <c r="O90">
-        <v>-13.27076493633887</v>
+        <v>-15.17296681061547</v>
       </c>
       <c r="P90">
-        <v>-44.42821304774316</v>
+        <v>-50.79645410510395</v>
       </c>
       <c r="Q90">
-        <v>82.97178695225682</v>
+        <v>76.60354589489603</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4917770511121178</v>
+        <v>0.5323204193950375</v>
       </c>
       <c r="T90">
-        <v>6.899123143005815</v>
+        <v>7.526316156006343</v>
       </c>
       <c r="U90">
         <v>0.1626309777667576</v>
       </c>
       <c r="V90">
-        <v>0.2117658923167255</v>
+        <v>0.209386500268223</v>
       </c>
       <c r="W90">
-        <v>0.1281912836416386</v>
+        <v>0.128578246496977</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9207212709422848</v>
+        <v>0.9103760881227085</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8954,22 +8954,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1729898855157637</v>
+        <v>0.1741581952934312</v>
       </c>
       <c r="C91">
-        <v>-1001.20324348627</v>
+        <v>-1070.377102922829</v>
       </c>
       <c r="D91">
-        <v>2378.906690312301</v>
+        <v>2360.586875075726</v>
       </c>
       <c r="E91">
-        <v>2027.205513800176</v>
+        <v>2078.05955800016</v>
       </c>
       <c r="F91">
-        <v>4526.009933798571</v>
+        <v>4576.863977998555</v>
       </c>
       <c r="G91">
         <v>1145.9</v>
@@ -8990,37 +8990,37 @@
         <v>670.1</v>
       </c>
       <c r="M91">
-        <v>736.0694209157194</v>
+        <v>744.3398638473567</v>
       </c>
       <c r="N91">
-        <v>-65.96942091571941</v>
+        <v>-74.23986384735667</v>
       </c>
       <c r="O91">
-        <v>-15.17296681061547</v>
+        <v>-17.07516868489203</v>
       </c>
       <c r="P91">
-        <v>-50.79645410510395</v>
+        <v>-57.16469516246464</v>
       </c>
       <c r="Q91">
-        <v>76.60354589489603</v>
+        <v>70.23530483753534</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5323204193950375</v>
+        <v>0.5809724613345413</v>
       </c>
       <c r="T91">
-        <v>7.526316156006343</v>
+        <v>8.278947771606978</v>
       </c>
       <c r="U91">
         <v>0.1626309777667576</v>
       </c>
       <c r="V91">
-        <v>0.209386500268223</v>
+        <v>0.2070599835985761</v>
       </c>
       <c r="W91">
-        <v>0.128578246496977</v>
+        <v>0.1289566101777524</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9103760881227085</v>
+        <v>0.9002607982546784</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9036,22 +9036,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1741581952934312</v>
+        <v>0.1753265050710988</v>
       </c>
       <c r="C92">
-        <v>-1070.377102922829</v>
+        <v>-1139.270959089339</v>
       </c>
       <c r="D92">
-        <v>2360.586875075726</v>
+        <v>2342.5470631092</v>
       </c>
       <c r="E92">
-        <v>2078.05955800016</v>
+        <v>2128.913602200144</v>
       </c>
       <c r="F92">
-        <v>4576.863977998555</v>
+        <v>4627.718022198539</v>
       </c>
       <c r="G92">
         <v>1145.9</v>
@@ -9072,37 +9072,37 @@
         <v>670.1</v>
       </c>
       <c r="M92">
-        <v>744.3398638473567</v>
+        <v>752.610306778994</v>
       </c>
       <c r="N92">
-        <v>-74.23986384735667</v>
+        <v>-82.51030677899394</v>
       </c>
       <c r="O92">
-        <v>-17.07516868489203</v>
+        <v>-18.97737055916861</v>
       </c>
       <c r="P92">
-        <v>-57.16469516246464</v>
+        <v>-63.53293621982533</v>
       </c>
       <c r="Q92">
-        <v>70.23530483753534</v>
+        <v>63.86706378017465</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5809724613345413</v>
+        <v>0.6404360681494904</v>
       </c>
       <c r="T92">
-        <v>8.278947771606978</v>
+        <v>9.198830857341088</v>
       </c>
       <c r="U92">
         <v>0.1626309777667576</v>
       </c>
       <c r="V92">
-        <v>0.2070599835985761</v>
+        <v>0.2047845991634269</v>
       </c>
       <c r="W92">
-        <v>0.1289566101777524</v>
+        <v>0.1293266581732359</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9002607982546784</v>
+        <v>0.890367822449682</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9118,22 +9118,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1753265050710988</v>
+        <v>0.1764948148487664</v>
       </c>
       <c r="C93">
-        <v>-1139.270959089339</v>
+        <v>-1207.891182728676</v>
       </c>
       <c r="D93">
-        <v>2342.5470631092</v>
+        <v>2324.780883669847</v>
       </c>
       <c r="E93">
-        <v>2128.913602200144</v>
+        <v>2179.767646400128</v>
       </c>
       <c r="F93">
-        <v>4627.718022198539</v>
+        <v>4678.572066398523</v>
       </c>
       <c r="G93">
         <v>1145.9</v>
@@ -9154,37 +9154,37 @@
         <v>670.1</v>
       </c>
       <c r="M93">
-        <v>752.610306778994</v>
+        <v>760.8807497106313</v>
       </c>
       <c r="N93">
-        <v>-82.51030677899394</v>
+        <v>-90.78074971063131</v>
       </c>
       <c r="O93">
-        <v>-18.97737055916861</v>
+        <v>-20.8795724334452</v>
       </c>
       <c r="P93">
-        <v>-63.53293621982533</v>
+        <v>-69.90117727718611</v>
       </c>
       <c r="Q93">
-        <v>63.86706378017465</v>
+        <v>57.49882272281387</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6404360681494904</v>
+        <v>0.7147655766681769</v>
       </c>
       <c r="T93">
-        <v>9.198830857341088</v>
+        <v>10.34868471450873</v>
       </c>
       <c r="U93">
         <v>0.1626309777667576</v>
       </c>
       <c r="V93">
-        <v>0.2047845991634269</v>
+        <v>0.2025586796073026</v>
       </c>
       <c r="W93">
-        <v>0.1293266581732359</v>
+        <v>0.1296886616470786</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.890367822449682</v>
+        <v>0.8806899113360984</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9200,22 +9200,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1764948148487664</v>
+        <v>0.177663124626434</v>
       </c>
       <c r="C94">
-        <v>-1207.891182728676</v>
+        <v>-1276.243952772295</v>
       </c>
       <c r="D94">
-        <v>2324.780883669847</v>
+        <v>2307.282157826212</v>
       </c>
       <c r="E94">
-        <v>2179.767646400128</v>
+        <v>2230.621690600112</v>
       </c>
       <c r="F94">
-        <v>4678.572066398523</v>
+        <v>4729.426110598507</v>
       </c>
       <c r="G94">
         <v>1145.9</v>
@@ -9236,37 +9236,37 @@
         <v>670.1</v>
       </c>
       <c r="M94">
-        <v>760.8807497106313</v>
+        <v>769.1511926422686</v>
       </c>
       <c r="N94">
-        <v>-90.78074971063131</v>
+        <v>-99.05119264226857</v>
       </c>
       <c r="O94">
-        <v>-20.8795724334452</v>
+        <v>-22.78177430772177</v>
       </c>
       <c r="P94">
-        <v>-69.90117727718611</v>
+        <v>-76.2694183345468</v>
       </c>
       <c r="Q94">
-        <v>57.49882272281387</v>
+        <v>51.13058166545318</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7147655766681769</v>
+        <v>0.8103320876207738</v>
       </c>
       <c r="T94">
-        <v>10.34868471450873</v>
+        <v>11.82706824515283</v>
       </c>
       <c r="U94">
         <v>0.1626309777667576</v>
       </c>
       <c r="V94">
-        <v>0.2025586796073026</v>
+        <v>0.2003806292889446</v>
       </c>
       <c r="W94">
-        <v>0.1296886616470786</v>
+        <v>0.1300428800999784</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8806899113360984</v>
+        <v>0.8712201273432372</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9282,22 +9282,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.177663124626434</v>
+        <v>0.1788314344041016</v>
       </c>
       <c r="C95">
-        <v>-1276.243952772295</v>
+        <v>-1344.335263505156</v>
       </c>
       <c r="D95">
-        <v>2307.282157826212</v>
+        <v>2290.044891293334</v>
       </c>
       <c r="E95">
-        <v>2230.621690600112</v>
+        <v>2281.475734800096</v>
       </c>
       <c r="F95">
-        <v>4729.426110598507</v>
+        <v>4780.280154798491</v>
       </c>
       <c r="G95">
         <v>1145.9</v>
@@ -9318,37 +9318,37 @@
         <v>670.1</v>
       </c>
       <c r="M95">
-        <v>769.1511926422686</v>
+        <v>777.4216355739059</v>
       </c>
       <c r="N95">
-        <v>-99.05119264226857</v>
+        <v>-107.3216355739058</v>
       </c>
       <c r="O95">
-        <v>-22.78177430772177</v>
+        <v>-24.68397618199834</v>
       </c>
       <c r="P95">
-        <v>-76.2694183345468</v>
+        <v>-82.63765939190749</v>
       </c>
       <c r="Q95">
-        <v>51.13058166545318</v>
+        <v>44.76234060809249</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8103320876207738</v>
+        <v>0.9377541022242362</v>
       </c>
       <c r="T95">
-        <v>11.82706824515283</v>
+        <v>13.79824628601164</v>
       </c>
       <c r="U95">
         <v>0.1626309777667576</v>
       </c>
       <c r="V95">
-        <v>0.2003806292889446</v>
+        <v>0.1982489204667218</v>
       </c>
       <c r="W95">
-        <v>0.1300428800999784</v>
+        <v>0.1303895619900505</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8712201273432372</v>
+        <v>0.8619518281161815</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9364,22 +9364,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1788314344041016</v>
+        <v>0.1799997441817691</v>
       </c>
       <c r="C96">
-        <v>-1344.335263505156</v>
+        <v>-1412.170931411883</v>
       </c>
       <c r="D96">
-        <v>2290.044891293334</v>
+        <v>2273.063267586591</v>
       </c>
       <c r="E96">
-        <v>2281.475734800096</v>
+        <v>2332.32977900008</v>
       </c>
       <c r="F96">
-        <v>4780.280154798491</v>
+        <v>4831.134198998475</v>
       </c>
       <c r="G96">
         <v>1145.9</v>
@@ -9400,37 +9400,37 @@
         <v>670.1</v>
       </c>
       <c r="M96">
-        <v>777.4216355739059</v>
+        <v>785.6920785055431</v>
       </c>
       <c r="N96">
-        <v>-107.3216355739058</v>
+        <v>-115.5920785055431</v>
       </c>
       <c r="O96">
-        <v>-24.68397618199834</v>
+        <v>-26.58617805627491</v>
       </c>
       <c r="P96">
-        <v>-82.63765939190749</v>
+        <v>-89.00590044926818</v>
       </c>
       <c r="Q96">
-        <v>44.76234060809249</v>
+        <v>38.3940995507318</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9377541022242362</v>
+        <v>1.116144922669084</v>
       </c>
       <c r="T96">
-        <v>13.79824628601164</v>
+        <v>16.55789554321398</v>
       </c>
       <c r="U96">
         <v>0.1626309777667576</v>
       </c>
       <c r="V96">
-        <v>0.1982489204667218</v>
+        <v>0.1961620897249668</v>
       </c>
       <c r="W96">
-        <v>0.1303895619900505</v>
+        <v>0.1307289453140158</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8619518281161815</v>
+        <v>0.8528786509781165</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9446,22 +9446,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1799997441817691</v>
+        <v>0.1811680539594367</v>
       </c>
       <c r="C97">
-        <v>-1412.170931411883</v>
+        <v>-1479.756601720539</v>
       </c>
       <c r="D97">
-        <v>2273.063267586591</v>
+        <v>2256.331641477919</v>
       </c>
       <c r="E97">
-        <v>2332.32977900008</v>
+        <v>2383.183823200064</v>
       </c>
       <c r="F97">
-        <v>4831.134198998475</v>
+        <v>4881.988243198459</v>
       </c>
       <c r="G97">
         <v>1145.9</v>
@@ -9482,37 +9482,37 @@
         <v>670.1</v>
       </c>
       <c r="M97">
-        <v>785.6920785055431</v>
+        <v>793.9625214371805</v>
       </c>
       <c r="N97">
-        <v>-115.5920785055431</v>
+        <v>-123.8625214371805</v>
       </c>
       <c r="O97">
-        <v>-26.58617805627491</v>
+        <v>-28.48837993055151</v>
       </c>
       <c r="P97">
-        <v>-89.00590044926818</v>
+        <v>-95.37414150662897</v>
       </c>
       <c r="Q97">
-        <v>38.3940995507318</v>
+        <v>32.025858493371</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.116144922669084</v>
+        <v>1.383731153336355</v>
       </c>
       <c r="T97">
-        <v>16.55789554321398</v>
+        <v>20.69736942901748</v>
       </c>
       <c r="U97">
         <v>0.1626309777667576</v>
       </c>
       <c r="V97">
-        <v>0.1961620897249668</v>
+        <v>0.1941187346236651</v>
       </c>
       <c r="W97">
-        <v>0.1307289453140158</v>
+        <v>0.1310612581520652</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8528786509781165</v>
+        <v>0.8439944983637611</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9528,22 +9528,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1811680539594367</v>
+        <v>0.1823363637371043</v>
       </c>
       <c r="C98">
-        <v>-1479.756601720539</v>
+        <v>-1547.097754659528</v>
       </c>
       <c r="D98">
-        <v>2256.33164147792</v>
+        <v>2239.844532738914</v>
       </c>
       <c r="E98">
-        <v>2383.183823200064</v>
+        <v>2434.037867400048</v>
       </c>
       <c r="F98">
-        <v>4881.988243198459</v>
+        <v>4932.842287398443</v>
       </c>
       <c r="G98">
         <v>1145.9</v>
@@ -9564,37 +9564,37 @@
         <v>670.1</v>
       </c>
       <c r="M98">
-        <v>793.9625214371805</v>
+        <v>802.2329643688178</v>
       </c>
       <c r="N98">
-        <v>-123.8625214371805</v>
+        <v>-132.1329643688177</v>
       </c>
       <c r="O98">
-        <v>-28.48837993055151</v>
+        <v>-30.39058180482808</v>
       </c>
       <c r="P98">
-        <v>-95.37414150662897</v>
+        <v>-101.7423825639897</v>
       </c>
       <c r="Q98">
-        <v>32.025858493371</v>
+        <v>25.65761743601033</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.383731153336352</v>
+        <v>1.829708204448469</v>
       </c>
       <c r="T98">
-        <v>20.69736942901742</v>
+        <v>27.59649257202323</v>
       </c>
       <c r="U98">
         <v>0.1626309777667576</v>
       </c>
       <c r="V98">
-        <v>0.1941187346236651</v>
+        <v>0.1921175105553798</v>
       </c>
       <c r="W98">
-        <v>0.1310612581520652</v>
+        <v>0.1313867191790208</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8439944983637611</v>
+        <v>0.8352935241538254</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9610,22 +9610,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1823363637371043</v>
+        <v>0.1835046735147719</v>
       </c>
       <c r="C99">
-        <v>-1547.097754659528</v>
+        <v>-1614.199711442163</v>
       </c>
       <c r="D99">
-        <v>2239.844532738914</v>
+        <v>2223.596620156263</v>
       </c>
       <c r="E99">
-        <v>2434.037867400048</v>
+        <v>2484.891911600032</v>
       </c>
       <c r="F99">
-        <v>4932.842287398443</v>
+        <v>4983.696331598427</v>
       </c>
       <c r="G99">
         <v>1145.9</v>
@@ -9646,37 +9646,37 @@
         <v>670.1</v>
       </c>
       <c r="M99">
-        <v>802.2329643688178</v>
+        <v>810.503407300455</v>
       </c>
       <c r="N99">
-        <v>-132.1329643688177</v>
+        <v>-140.403407300455</v>
       </c>
       <c r="O99">
-        <v>-30.39058180482808</v>
+        <v>-32.29278367910465</v>
       </c>
       <c r="P99">
-        <v>-101.7423825639897</v>
+        <v>-108.1106236213504</v>
       </c>
       <c r="Q99">
-        <v>25.65761743601033</v>
+        <v>19.28937637864962</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.829708204448469</v>
+        <v>2.721662306672704</v>
       </c>
       <c r="T99">
-        <v>27.59649257202323</v>
+        <v>41.39473885803485</v>
       </c>
       <c r="U99">
         <v>0.1626309777667576</v>
       </c>
       <c r="V99">
-        <v>0.1921175105553798</v>
+        <v>0.1901571277946107</v>
       </c>
       <c r="W99">
-        <v>0.1313867191790208</v>
+        <v>0.1317055381442018</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8352935241538254</v>
+        <v>0.8267701208461333</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9692,22 +9692,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1835046735147719</v>
+        <v>0.1846729832924394</v>
       </c>
       <c r="C100">
-        <v>-1614.199711442163</v>
+        <v>-1681.06763999263</v>
       </c>
       <c r="D100">
-        <v>2223.596620156263</v>
+        <v>2207.582735805781</v>
       </c>
       <c r="E100">
-        <v>2484.891911600032</v>
+        <v>2535.745955800016</v>
       </c>
       <c r="F100">
-        <v>4983.696331598427</v>
+        <v>5034.550375798411</v>
       </c>
       <c r="G100">
         <v>1145.9</v>
@@ -9728,37 +9728,37 @@
         <v>670.1</v>
       </c>
       <c r="M100">
-        <v>810.503407300455</v>
+        <v>818.7738502320924</v>
       </c>
       <c r="N100">
-        <v>-140.403407300455</v>
+        <v>-148.6738502320924</v>
       </c>
       <c r="O100">
-        <v>-32.29278367910465</v>
+        <v>-34.19498555338125</v>
       </c>
       <c r="P100">
-        <v>-108.1106236213504</v>
+        <v>-114.4788646787111</v>
       </c>
       <c r="Q100">
-        <v>19.28937637864962</v>
+        <v>12.92113532128886</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.721662306672704</v>
+        <v>5.397524613345408</v>
       </c>
       <c r="T100">
-        <v>41.39473885803485</v>
+        <v>82.7894777160697</v>
       </c>
       <c r="U100">
         <v>0.1626309777667576</v>
       </c>
       <c r="V100">
-        <v>0.1901571277946107</v>
+        <v>0.1882363487259782</v>
       </c>
       <c r="W100">
-        <v>0.1317055381442018</v>
+        <v>0.1320179163222074</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9766,91 +9766,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8267701208461333</v>
+        <v>0.8184189075042532</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1846729832924394</v>
-      </c>
-      <c r="C101">
-        <v>-1681.06763999263</v>
-      </c>
-      <c r="D101">
-        <v>2207.582735805781</v>
-      </c>
-      <c r="E101">
-        <v>2535.745955800016</v>
-      </c>
-      <c r="F101">
-        <v>5034.550375798411</v>
-      </c>
-      <c r="G101">
-        <v>1145.9</v>
-      </c>
-      <c r="H101">
-        <v>2586.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>797.5</v>
-      </c>
-      <c r="K101">
-        <v>127.4</v>
-      </c>
-      <c r="L101">
-        <v>670.1</v>
-      </c>
-      <c r="M101">
-        <v>818.7738502320924</v>
-      </c>
-      <c r="N101">
-        <v>-148.6738502320924</v>
-      </c>
-      <c r="O101">
-        <v>-34.19498555338125</v>
-      </c>
-      <c r="P101">
-        <v>-114.4788646787111</v>
-      </c>
-      <c r="Q101">
-        <v>12.92113532128886</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.397524613345408</v>
-      </c>
-      <c r="T101">
-        <v>82.7894777160697</v>
-      </c>
-      <c r="U101">
-        <v>0.1626309777667576</v>
-      </c>
-      <c r="V101">
-        <v>0.1882363487259782</v>
-      </c>
-      <c r="W101">
-        <v>0.1320179163222074</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8184189075042532</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
